--- a/docs/misrac/ethfw_SA_Report.xlsx
+++ b/docs/misrac/ethfw_SA_Report.xlsx
@@ -26,7 +26,7 @@
     <sheet name="Klocwork Project Modules" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="10" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$T$7</definedName>
+    <definedName hidden="1" localSheetId="10" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$T$4</definedName>
     <definedName hidden="1" localSheetId="11" name="_xlnm._FilterDatabase">'Guideline Enforcement Plan'!$A$1:$I$255</definedName>
     <definedName hidden="1" localSheetId="14" name="_xlnm._FilterDatabase">'Active Deviation Permits'!$A$1:$J$67</definedName>
     <definedName hidden="1" localSheetId="15" name="_xlnm._FilterDatabase">'Taxonomy Checkers'!$A$1:$F$1126</definedName>
@@ -38,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
     </font>
     <font>
       <color rgb="00ffffff"/>
@@ -130,15 +134,24 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf applyAlignment="1" borderId="1" fillId="5" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,7 +178,7 @@
     <xf applyAlignment="1" borderId="0" fillId="7" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="11" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="11" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf applyAlignment="1" borderId="1" fillId="10" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
@@ -468,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="10"/>
@@ -479,276 +492,303 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>TI Information - Selective Disclosure</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Copyright (C) 2023 Texas Instruments Incorporated</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
           <t>Sheet No.</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Purpose</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Table of Contents</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Provides an overview of the contents of the complete report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Script Input Parameters</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Displays the input parameters provided to generate this report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Klocwork Build Configuration</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Provides an overview on the build in the Klocwork project for which this report has been generated.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MISRA Summary by Metrics</t>
+          <t>Table of Contents</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Provides a short summary which was earlier part of HIS Summary by Metrics report in FoQus-generated HIS Reports.</t>
+          <t>Provides an overview of the contents of the complete report.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>MISRA Summary by Severity</t>
+          <t>Script Input Parameters</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Provides MISRA Summary Report by Severity on the issues identified.</t>
+          <t>Displays the input parameters provided to generate this report.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MISRA Summary by Modules</t>
+          <t>Klocwork Build Configuration</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Provides MISRA Summary Report by Modules. These modules are defined in the Klocwork project. Each module can have multiple file paths included in it.</t>
+          <t>Provides an overview on the build in the Klocwork project for which this report has been generated.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>HIS Summary by Metrics</t>
+          <t>MISRA Summary by Metrics</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Provides HIS Summary Report by Metrics.</t>
+          <t>Provides a short summary which was earlier part of HIS Summary by Metrics report in FoQus-generated HIS Reports.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>HIS Summary by Modules</t>
+          <t>MISRA Summary by Severity</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Provides HIS Summary Report by Modules for each HIS Metric.</t>
+          <t>Provides MISRA Summary Report by Severity on the issues identified.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>SA Summary by Severity</t>
+          <t>MISRA Summary by Modules</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Provides Static Analysis (SA) Summary Report by Severity on the issues identified.</t>
+          <t>Provides MISRA Summary Report by Modules. These modules are defined in the Klocwork project. Each module can have multiple file paths included in it.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>SA Summary by Modules</t>
+          <t>HIS Summary by Metrics</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Provides Static Analysis (SA) Summary Report by Modules. These modules are defined in the Klocwork project. Each module can have multiple file paths included in it.</t>
+          <t>Provides HIS Summary Report by Metrics.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Raw Issue Details</t>
+          <t>HIS Summary by Modules</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Provides raw issue details from Klocwork. If you provided MISRA taxonomy as input parameter, it will also consist of Waiver details.</t>
+          <t>Provides HIS Summary Report by Modules for each HIS Metric.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Guideline Enforcement Plan</t>
+          <t>SA Summary by Severity</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Provides MISRA Guideline Enforcement Plan.</t>
+          <t>Provides Static Analysis (SA) Summary Report by Severity on the issues identified.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Deviation Summary by Type &amp; Category</t>
+          <t>SA Summary by Modules</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Provides MISRA Active Deviation Summary by Category for Deviation Types.</t>
+          <t>Provides Static Analysis (SA) Summary Report by Modules. These modules are defined in the Klocwork project. Each module can have multiple file paths included in it.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Deviation Summary by Classification</t>
+          <t>Raw Issue Details</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Provides MISRA Active Deviation Summary by Classification</t>
+          <t>Provides raw issue details from Klocwork. If you provided MISRA taxonomy as input parameter, it will also consist of Waiver details.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Active Deviation Permits</t>
+          <t>Guideline Enforcement Plan</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Provides MISRA Active Deviation Permit details from Jira including both EP-wide and project-specific Waivers.</t>
+          <t>Provides MISRA Guideline Enforcement Plan.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Taxonomy Checkers</t>
+          <t>Deviation Summary by Type &amp; Category</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Provides the list of checkers from the taxonomy/taxonomies in Klocwork.</t>
+          <t>Provides MISRA Active Deviation Summary by Category for Deviation Types.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Deviation Summary by Classification</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Provides MISRA Active Deviation Summary by Classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Active Deviation Permits</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Provides MISRA Active Deviation Permit details from Jira including both EP-wide and project-specific Waivers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Taxonomy Checkers</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Provides the list of checkers from the taxonomy/taxonomies in Klocwork.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Klocwork Project Modules</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Provides the list of modules defined the Klocwork project along with the file paths included in them.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
@@ -778,74 +818,74 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Module name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>State: New</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>State: New AND need to be Analyzed or Fixed</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>State: Existing</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>State: Existing AND need to be Analyzed or Fixed</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Status: Analyze</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Status: Ignore</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Status: Not a Problem</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Status: Defer</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Status: Fix</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Status: Fix in Next Release</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Status: Fix in Later Release</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Status: Filter</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
@@ -888,45 +928,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="n">
+      <c r="B3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="11" t="n">
+      <c r="E3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="11" t="n">
+      <c r="H3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -941,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="18"/>
@@ -967,102 +1007,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>file</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>line</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>message</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>severityCode</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>taxonomyName</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Waiver ID</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Waiver Classification</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>Deviation Type</t>
         </is>
       </c>
-      <c r="R1" s="12" t="inlineStr">
+      <c r="R1" s="15" t="inlineStr">
         <is>
           <t>MISRA Rule</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="6" t="inlineStr">
         <is>
           <t>Waiver ID/ Comment Validation</t>
         </is>
@@ -1088,7 +1128,7 @@
         <v>148377</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1366</v>
+        <v>1376</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -1129,7 +1169,7 @@
         </is>
       </c>
       <c r="N2" s="3">
-        <f>HYPERLINK("https://klocwork.india.ti.com:443/review/insight-review.html#issuedetails_goto:problemid=148377,project=ETHSWITCHFW,searchquery=taxonomy:'' build:KW_Build_Label_Dec_04_2022_12_26_AM grouping:off status:'Not a Problem',Ignore severity:'Error','Critical'","KW Issue Link")</f>
+        <f>HYPERLINK("https://klocwork.india.ti.com:443/review/insight-review.html#issuedetails_goto:problemid=148377,project=ETHSWITCHFW,searchquery=taxonomy:'' build:KW_Build_Label_Feb_15_2023_12_21_PM grouping:off status:'Not a Problem',Ignore severity:'Error','Critical' module:+'EthFw'","KW Issue Link")</f>
         <v/>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -1146,33 +1186,33 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>RH.LEAK</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Specific EnetTypes are checked in lines 487-488 that would prevent the buffer overflow from happening.</t>
+          <t>Permitted as per deviation record PSDKRA_SA_DR_011.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>/data/adasuser_bangvideoapps02/ethfw_jenkin_build/kw_build/ethfw/ethfw/src/ethfw.c</t>
+          <t>/data/adasuser_bangvideoapps02/ethfw_jenkin_build/kw_build/ethfw/utils/console_io/src/app_log_printf_ticgt_rtos.c</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>423723</v>
+        <v>1086257</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1159</v>
+        <v>243</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Array 'gMcmObj' of size 7 may use index value(s) 0..7</t>
+          <t>Resource acquired to 'freopen("appLog:", "w",  ( &amp;_ftable[1] ) )' at line 243 may be lost here.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>EthFw_initMcm</t>
+          <t>appLogCioInit</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1182,11 +1222,11 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -1195,7 +1235,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Ignore</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -1204,7 +1244,7 @@
         </is>
       </c>
       <c r="N3" s="3">
-        <f>HYPERLINK("https://klocwork.india.ti.com:443/review/insight-review.html#issuedetails_goto:problemid=423723,project=ETHSWITCHFW,searchquery=taxonomy:'' build:KW_Build_Label_Dec_04_2022_12_26_AM grouping:off status:'Not a Problem',Ignore severity:'Error','Critical'","KW Issue Link")</f>
+        <f>HYPERLINK("https://klocwork.india.ti.com:443/review/insight-review.html#issuedetails_goto:problemid=1086257,project=ETHSWITCHFW,searchquery=taxonomy:'' build:KW_Build_Label_Feb_15_2023_12_21_PM grouping:off status:'Not a Problem',Ignore severity:'Error','Critical' module:+'EthFw'","KW Issue Link")</f>
         <v/>
       </c>
       <c r="O3" s="3" t="inlineStr"/>
@@ -1213,7 +1253,7 @@
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>*default*</t>
+          <t>*default*, EthFw</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
@@ -1226,19 +1266,19 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>This is called by EthFw which runs forever and is not expected to be terminated.</t>
+          <t>Permitted as per deviation record PSDKRA_SA_DR_006.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>/data/adasuser_bangvideoapps02/ethfw_jenkin_build/kw_build/pdk/packages/ti/drv/enet/enet_cfgserver/enet_cfgserver.c</t>
+          <t>/data/adasuser_bangvideoapps02/ethfw_jenkin_build/kw_build/ethfw/apps/app_remoteswitchcfg_server/mcu_2_0/main.c</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>700252</v>
+        <v>1087079</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>442</v>
+        <v>1152</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1247,7 +1287,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>EnetCfgServer_networkTask</t>
+          <t>EthApp_traceBufFlush</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1270,7 +1310,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Ignore</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -1279,7 +1319,7 @@
         </is>
       </c>
       <c r="N4" s="3">
-        <f>HYPERLINK("https://klocwork.india.ti.com:443/review/insight-review.html#issuedetails_goto:problemid=700252,project=ETHSWITCHFW,searchquery=taxonomy:'' build:KW_Build_Label_Dec_04_2022_12_26_AM grouping:off status:'Not a Problem',Ignore severity:'Error','Critical'","KW Issue Link")</f>
+        <f>HYPERLINK("https://klocwork.india.ti.com:443/review/insight-review.html#issuedetails_goto:problemid=1087079,project=ETHSWITCHFW,searchquery=taxonomy:'' build:KW_Build_Label_Feb_15_2023_12_21_PM grouping:off status:'Not a Problem',Ignore severity:'Error','Critical' module:+'EthFw'","KW Issue Link")</f>
         <v/>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
@@ -1288,238 +1328,13 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>*default*</t>
+          <t>*default*, EthFw</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>INFINITE_LOOP.LOCAL</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>This is called by EthFw which runs forever and is not expected to be terminated.</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>/data/adasuser_bangvideoapps02/ethfw_jenkin_build/kw_build/pdk/packages/ti/drv/enet/enet_cfgserver/enet_cfgserver.c</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>700253</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>496</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Infinite loop</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>EnetCfgServer_dispatcherTask</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Not a Problem</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N5" s="3">
-        <f>HYPERLINK("https://klocwork.india.ti.com:443/review/insight-review.html#issuedetails_goto:problemid=700253,project=ETHSWITCHFW,searchquery=taxonomy:'' build:KW_Build_Label_Dec_04_2022_12_26_AM grouping:off status:'Not a Problem',Ignore severity:'Error','Critical'","KW Issue Link")</f>
-        <v/>
-      </c>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>*default*</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>RH.LEAK</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Permitted as per deviation record PSDKRA_SA_DR_011.</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>/data/adasuser_bangvideoapps02/ethfw_jenkin_build/kw_build/ethfw/utils/console_io/src/app_log_printf_ticgt_rtos.c</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1086257</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Resource acquired to 'freopen("appLog:", "w",  ( &amp;_ftable[1] ) )' at line 243 may be lost here.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>appLogCioInit</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N6" s="3">
-        <f>HYPERLINK("https://klocwork.india.ti.com:443/review/insight-review.html#issuedetails_goto:problemid=1086257,project=ETHSWITCHFW,searchquery=taxonomy:'' build:KW_Build_Label_Dec_04_2022_12_26_AM grouping:off status:'Not a Problem',Ignore severity:'Error','Critical'","KW Issue Link")</f>
-        <v/>
-      </c>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>*default*, EthFw</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>INFINITE_LOOP.LOCAL</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Permitted as per deviation record PSDKRA_SA_DR_006.</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>/data/adasuser_bangvideoapps02/ethfw_jenkin_build/kw_build/ethfw/apps/app_remoteswitchcfg_server/mcu_2_0/main.c</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>1087079</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1133</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Infinite loop</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>EthApp_traceBufFlush</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N7" s="3">
-        <f>HYPERLINK("https://klocwork.india.ti.com:443/review/insight-review.html#issuedetails_goto:problemid=1087079,project=ETHSWITCHFW,searchquery=taxonomy:'' build:KW_Build_Label_Dec_04_2022_12_26_AM grouping:off status:'Not a Problem',Ignore severity:'Error','Critical'","KW Issue Link")</f>
-        <v/>
-      </c>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>*default*, EthFw</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T7"/>
+  <autoFilter ref="A1:T4"/>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
@@ -1545,47 +1360,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>MISRA Rule</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Decidable?</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Rule Description</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Checker Code</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Alternate Checker - Compiler/Linker</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>Alternate Checker - Manual Review</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Waiver ID</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Waiver Link</t>
         </is>
@@ -9782,17 +9597,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Deviation Type | Category</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Advisory</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9838,15 +9653,15 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Total Active Deviation Permits</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="14" t="n">
         <v>40</v>
       </c>
     </row>
@@ -9869,12 +9684,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Waiver Classification</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>No. of Active Deviation Permits</t>
         </is>
@@ -9961,12 +9776,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Total Active Deviation Permits</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="14" t="n">
         <v>66</v>
       </c>
     </row>
@@ -9997,52 +9812,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Waiver ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Waiver Link</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Deviation Type</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Waiver Classification</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Waiver Use-Case</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>MISRA Rule</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Decidable?</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Rule Description</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Checker Code</t>
         </is>
@@ -14565,32 +14380,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>supportLevel</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Taxonomy Name</t>
         </is>
@@ -43794,12 +43609,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>paths</t>
         </is>
@@ -43840,32 +43655,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Klocwork Project</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Taxonomy</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Advanced Query</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Jira Project Key</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Report generated on</t>
         </is>
@@ -43880,12 +43695,12 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>KW_Build_Label_Dec_04_2022_12_26_AM</t>
+          <t>KW_Build_Label_Feb_15_2023_12_21_PM</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>status:'Not a Problem',Ignore severity:'Error','Critical'</t>
+          <t>status:'Not a Problem',Ignore severity:'Error','Critical' module:+'EthFw'</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -43895,7 +43710,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022-12-08 23:22:46.565546-06:00 CDT</t>
+          <t>2023-02-15 02:47:07.084259-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -43928,62 +43743,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>build</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>cFilesAnalyzed</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>creationDate</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>linesOfCode</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>linesOfComments</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>numberOfClasses</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>numberOfEntities</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>numberOfFiles</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>numberOfFunctions</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>systemFilesAnalyzed</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>taxonomies</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>version</t>
         </is>
@@ -43992,7 +43807,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>KW_Build_Label_Dec_04_2022_12_26_AM</t>
+          <t>KW_Build_Label_Feb_15_2023_12_21_PM</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -44000,26 +43815,26 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Sun Dec 04 01:05:35 IST 2022</t>
+          <t>Wed Feb 15 13:10:14 IST 2023</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>531520</v>
+        <v>532922</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>430758</v>
+        <v>430865</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6518</v>
+        <v>6519</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1000096</v>
+        <v>1000241</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>2524</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>11397</v>
+        <v>11413</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>56</v>
@@ -44057,27 +43872,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>MISRA Metrics</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Default Range</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Number of Issues</t>
         </is>
@@ -44097,7 +43912,7 @@
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Compiled</t>
         </is>
@@ -44120,7 +43935,7 @@
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Compiled</t>
         </is>
@@ -44162,89 +43977,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Status: Ignore</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Status: Ignore without Waiver ID</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Status: Not a Problem</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Status: Not a Problem without Waiver ID</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>State: Existing</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>State: Existing AND need to be Analyzed or Fixed</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>State: New</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>State: New AND need to be Analyzed or Fixed</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Disapplied</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Permitted</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Permitted - Adopted Code</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Permitted - Module Specific</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Permitted - Tool Issue</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Tool Unsupported</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: No plan to fix</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>MISRA Mandatory</t>
         </is>
@@ -44296,7 +44111,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>MISRA Required</t>
         </is>
@@ -44348,7 +44163,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>MISRA Advisory</t>
         </is>
@@ -44400,54 +44215,54 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="11" t="n">
+      <c r="B5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44484,89 +44299,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Module name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Status: Ignore</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Status: Ignore without Waiver ID</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Status: Not a Problem</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Status: Not a Problem without Waiver ID</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>State: Existing</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>State: Existing AND need to be Analyzed or Fixed</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>State: New</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>State: New AND need to be Analyzed or Fixed</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Disapplied</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Permitted</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Permitted - Adopted Code</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Permitted - Module Specific</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Permitted - Tool Issue</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: Tool Unsupported</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>Deviation Type: No plan to fix</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
@@ -44618,54 +44433,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="11" t="n">
+      <c r="B3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44691,27 +44506,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>HIS Metrics</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Default Range</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Number of Issues</t>
         </is>
@@ -44733,7 +44548,7 @@
           <t>0-80</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Compiled</t>
         </is>
@@ -44758,7 +44573,7 @@
           <t>0-10</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Compiled</t>
         </is>
@@ -44783,7 +44598,7 @@
           <t>0-5</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Compiled</t>
         </is>
@@ -44808,7 +44623,7 @@
           <t>0-4</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Compiled</t>
         </is>
@@ -44818,15 +44633,15 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr"/>
-      <c r="C6" s="11" t="inlineStr"/>
-      <c r="D6" s="11" t="inlineStr"/>
-      <c r="E6" s="11" t="n">
+      <c r="B6" s="14" t="inlineStr"/>
+      <c r="C6" s="14" t="inlineStr"/>
+      <c r="D6" s="14" t="inlineStr"/>
+      <c r="E6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44852,27 +44667,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Module name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Number of Paths</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Cyclomatic Complexity</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Number of Function Parameters</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Number of Call Levels</t>
         </is>
@@ -44898,21 +44713,21 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="11" t="n">
+      <c r="B3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44946,74 +44761,74 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>State: New</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>State: New AND need to be Analyzed or Fixed</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>State: Existing</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>State: Existing AND need to be Analyzed or Fixed</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Status: Analyze</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Status: Ignore</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Status: Not a Problem</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Status: Defer</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Status: Fix</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Status: Fix in Next Release</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Status: Fix in Later Release</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Status: Filter</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>MISRA Mandatory</t>
         </is>
@@ -45056,7 +44871,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>MISRA Required</t>
         </is>
@@ -45099,7 +44914,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>MISRA Advisory</t>
         </is>
@@ -45142,7 +44957,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -45154,7 +44969,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -45166,7 +44981,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0</v>
@@ -45185,7 +45000,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
@@ -45197,7 +45012,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -45209,7 +45024,7 @@
         <v>3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -45228,7 +45043,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
@@ -45271,7 +45086,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -45314,7 +45129,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>HIS METRICS</t>
         </is>
@@ -45357,45 +45172,45 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11" t="n">
+      <c r="B10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="11" t="n">
+      <c r="H10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/docs/misrac/ethfw_SA_Report.xlsx
+++ b/docs/misrac/ethfw_SA_Report.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Template Revision History" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$O$10</definedName>
+    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$O$9</definedName>
     <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">'Taxonomy Checkers'!$A$1:$F$294</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW_KW_BUILD_Jul_19_2023_07_15_AM</t>
+          <t>ETHFW_KW_BUILD_Nov_22_2023_04_26_PM</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>status:'Not a Problem',Ignore severity:'Error','Critical'</t>
+          <t>severity:'Error','Critical'</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26 05:58:24.922948-05:00 CDT</t>
+          <t>2023-11-22 11:31:15.759823-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -885,37 +885,37 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW_KW_BUILD_Jul_19_2023_07_15_AM</t>
+          <t>ETHFW_KW_BUILD_Nov_22_2023_04_26_PM</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1623</v>
+        <v>492</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Wed Jul 19 13:11:54 IST 2023</t>
+          <t>Wed Nov 22 22:37:40 IST 2023</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>275014</v>
+        <v>32785</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>281423</v>
+        <v>98448</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5173</v>
+        <v>2475</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>253479</v>
+        <v>150495</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1681</v>
+        <v>565</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>8680</v>
+        <v>876</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>2</v>
@@ -1381,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>0</v>
@@ -1390,10 +1390,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I10" s="11" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -1572,10 +1572,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>0</v>
@@ -1615,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I4" s="11" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="18"/>
@@ -1752,33 +1752,29 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>INFINITE_LOOP.LOCAL</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Permitted by deviation: ID:PSDKRA_SA_DR_006</t>
-        </is>
-      </c>
+          <t>RH.LEAK</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/remote_device_server_ethswitch.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/console_io/src/app_log_printf_ticgt_rtos.c</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>148377</v>
+        <v>1086257</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1376</v>
+        <v>243</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Infinite loop</t>
+          <t>Resource acquired to 'freopen("appLog:", "w", (&amp;_ftable[1]))' at line 243 may be lost here.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>rdevEthSwitchServerSenderTaskFn</t>
+          <t>appLogCioInit</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -1801,7 +1797,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Ignore</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -1823,33 +1819,29 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Specific EnetTypes are checked in lines 487-488 that would prevent the buffer overflow from happening.</t>
-        </is>
-      </c>
+          <t>INFINITE_LOOP.LOCAL</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethfw/src/ethfw.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/app_remoteswitchcfg_server/mcu_2_0/main.c</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>423723</v>
+        <v>1087079</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1342</v>
+        <v>1529</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Array 'gMcmObj' of size 7 may use index value(s) 0..7</t>
+          <t>Infinite loop</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>EthFw_initMcm</t>
+          <t>EthApp_traceBufFlush</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1859,11 +1851,11 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -1887,40 +1879,40 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>INFINITE_LOOP.LOCAL</t>
+          <t>UNINIT.STACK.MUST</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>This is called by EthFw which runs forever and is not expected to be terminated.</t>
+          <t>Waiver id: PSDKRA_SA_DR_012</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_j7200_09_00_00_00/packages/ti/drv/enet/enet_cfgserver/enet_cfgserver.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/console_io/src/app_cli_rtos.c</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>700252</v>
+        <v>1240036</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Infinite loop</t>
+          <t>'args.__ap' is used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>EnetCfgServer_networkTask</t>
+          <t>appCliPrintf</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1930,11 +1922,11 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -1958,40 +1950,41 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>INFINITE_LOOP.LOCAL</t>
+          <t>UNINIT.STACK.MUST</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>This is called by EthFw which runs forever and is not expected to be terminated.</t>
+          <t>Waiver id: PSDKRA_SA_DR_012
+reference: https://confluence.itg.ti.com/pages/viewpage.action?spaceKey=J7TDA4xSW&amp;title=PSDKRA+Static+Analysis+Policy</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_j7200_09_00_00_00/packages/ti/drv/enet/enet_cfgserver/enet_cfgserver.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/ipc_cfg/ipc_trace.c</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>700253</v>
+        <v>1240469</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>514</v>
+        <v>63</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Infinite loop</t>
+          <t>'args.__ap' is used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>EnetCfgServer_dispatcherTask</t>
+          <t>Ipc_Trace_printf</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2001,11 +1994,11 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -2029,40 +2022,40 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>RH.LEAK</t>
+          <t>UNINIT.STACK.MUST</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Permitted as per deviation record PSDKRA_SA_DR_011.</t>
+          <t>Waiver id: PSDKRA_SA_DR_012</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/console_io/src/app_log_printf_ticgt_rtos.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/app_remoteswitchcfg_client/mcu_2_1/main.c</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1086257</v>
+        <v>1240569</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>243</v>
+        <v>499</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'freopen("appLog:", "w", (&amp;_ftable[1]))' at line 243 may be lost here.</t>
+          <t>'args.__ap' is used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>appLogCioInit</t>
+          <t>appLogPrintf</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2072,11 +2065,11 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -2085,7 +2078,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Ignore</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -2107,33 +2100,34 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>INFINITE_LOOP.LOCAL</t>
+          <t>UNINIT.STACK.MUST</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Permitted as per deviation record PSDKRA_SA_DR_006.</t>
+          <t>Waiver id: PSDKRA_SA_DR_012
+reference: https://confluence.itg.ti.com/pages/viewpage.action?spaceKey=J7TDA4xSW&amp;title=PSDKRA+Static+Analysis+Policy</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/app_remoteswitchcfg_server/mcu_2_0/main.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/console_io/src/app_log_writer.c</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1087079</v>
+        <v>1256325</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1309</v>
+        <v>266</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Infinite loop</t>
+          <t>'va_args_ptr.__ap' is used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>EthApp_traceBufFlush</t>
+          <t>appLogPrintf</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2143,11 +2137,11 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -2156,7 +2150,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Ignore</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -2183,28 +2177,29 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Waiver id: PSDKRA_SA_DR_012</t>
+          <t>Waiver id: PSDKRA_SA_DR_012
+reference: https://confluence.itg.ti.com/pages/viewpage.action?spaceKey=J7TDA4xSW&amp;title=PSDKRA+Static+Analysis+Policy</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/console_io/src/app_cli_rtos.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/ethfw_common/src/ethfw_trace.c</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1240036</v>
+        <v>1279934</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>130</v>
+        <v>272</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>'args.__ap' is used uninitialized in this function.</t>
+          <t>'ap.__ap' is used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>appCliPrintf</t>
+          <t>EthFwTrace_trace</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -2254,19 +2249,20 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Waiver id: PSDKRA_SA_DR_012</t>
+          <t>Waiver id: PSDKRA_SA_DR_012
+reference: https://confluence.itg.ti.com/pages/viewpage.action?spaceKey=J7TDA4xSW&amp;title=PSDKRA+Static+Analysis+Policy</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/ipc_cfg/ipc_trace.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/ethfw_common/src/ethfw_trace.c</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1240469</v>
+        <v>1282473</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2275,7 +2271,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Ipc_Trace_printf</t>
+          <t>EthFwTrace_print</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -2298,7 +2294,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Ignore</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -2317,79 +2313,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MUST</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Waiver id: PSDKRA_SA_DR_012</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/app_remoteswitchcfg_client/mcu_2_1/main.c</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>1240569</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>476</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>'args.__ap' is used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>appLogPrintf</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Not a Problem</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>EthFw</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O9"/>
   <hyperlinks>
     <hyperlink ref="N2" r:id="rId1"/>
     <hyperlink ref="N3" r:id="rId2"/>
@@ -2399,7 +2324,6 @@
     <hyperlink ref="N7" r:id="rId6"/>
     <hyperlink ref="N8" r:id="rId7"/>
     <hyperlink ref="N9" r:id="rId8"/>
-    <hyperlink ref="N10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/docs/misrac/ethfw_SA_Report.xlsx
+++ b/docs/misrac/ethfw_SA_Report.xlsx
@@ -13,13 +13,15 @@
     <sheet name="SA Summary by Severity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="SA Summary by Modules" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Raw Issue Details" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Taxonomy Checkers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Klocwork Project Modules" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Template Revision History" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SA_GEP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Taxonomy Checkers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Klocwork Project Modules" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Template Revision History" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$O$9</definedName>
-    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">'Taxonomy Checkers'!$A$1:$F$294</definedName>
+    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$U$9</definedName>
+    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">'SA_GEP'!$A$1:$E$339</definedName>
+    <definedName hidden="1" localSheetId="7" name="_xlnm._FilterDatabase">'Taxonomy Checkers'!$A$1:$F$294</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,7 +49,7 @@
       <color rgb="00ffffff"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +96,11 @@
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -113,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -142,6 +149,9 @@
     <xf applyAlignment="1" borderId="1" fillId="5" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf applyAlignment="1" borderId="1" fillId="6" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf applyAlignment="1" borderId="0" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -152,6 +162,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf applyAlignment="1" borderId="1" fillId="9" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="1" fillId="10" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -519,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="10"/>
@@ -539,7 +552,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Copyright (C) 2023 Texas Instruments Incorporated</t>
+          <t>Copyright (C) 2024 Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
@@ -653,7 +666,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Provides raw issue details from Klocwork.</t>
+          <t>Provides raw issue details from Klocwork. If you provided MISRA taxonomy as input parameter, it will also consist of Waiver details.</t>
         </is>
       </c>
     </row>
@@ -663,12 +676,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Taxonomy Checkers</t>
+          <t>SA_GEP</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Provides the list of checkers from the taxonomy/taxonomies in Klocwork.</t>
+          <t>Provides Static Analysis Guideline Enforcement Plan.</t>
         </is>
       </c>
     </row>
@@ -678,12 +691,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Klocwork Project Modules</t>
+          <t>Taxonomy Checkers</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Provides the list of modules defined the Klocwork project along with the file paths included in them.</t>
+          <t>Provides the list of checkers from the taxonomy/taxonomies in Klocwork.</t>
         </is>
       </c>
     </row>
@@ -693,10 +706,25 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>Klocwork Project Modules</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Provides the list of modules defined the Klocwork project along with the file paths included in them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>Template Revision History</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Provides Template Revision History.</t>
         </is>
@@ -707,6 +735,133 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" max="1" min="1" width="27"/>
+    <col customWidth="1" max="2" min="2" width="10"/>
+    <col customWidth="1" max="3" min="3" width="16"/>
+    <col customWidth="1" max="4" min="4" width="20"/>
+    <col customWidth="1" max="5" min="5" width="80"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Document Status</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Dhruv Dixit and Gayathri Ajith</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>26th-July-2022</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Combined as single reporting sheet for Static analysis reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Dhruv Dixit</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>3rd-Jan-2023</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Modified with changes within summary sheets, also added CIP marking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Dhruv Dixit, Gayathri Ajith and Shrikrushna Bhagwat</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>15th-March-2024</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>1. Added 'CERT C Summary by Severity' &amp; 'CERT C Summary by Modules' sheets. 
+2. Added 'CERT_GEP', 'HIS_GEP', 'SA_GEP' sheets.
+3. Updated 'MISRA_GEP' with latest Checker Codes.
+4. Added Deviation columns in MISRA, HIS, SA summary sheets.
+5. Added a new column 'levels' &amp; renamed 'MISRA Rule' column to 'Rule' in 'Raw Issue Details' sheet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
@@ -773,7 +928,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW_KW_BUILD_Nov_22_2023_04_26_PM</t>
+          <t>ETHFW_KW_BUILD_Mar_22_2024_01_44_PM</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -788,7 +943,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023-11-22 11:31:15.759823-06:00 CDT</t>
+          <t>2024-03-22 09:56:35.416608-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -885,37 +1040,37 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW_KW_BUILD_Nov_22_2023_04_26_PM</t>
+          <t>ETHFW_KW_BUILD_Mar_22_2024_01_44_PM</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Wed Nov 22 22:37:40 IST 2023</t>
+          <t>Fri Mar 22 20:02:38 IST 2024</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>32785</v>
+        <v>35278</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>98448</v>
+        <v>101567</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2475</v>
+        <v>2519</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>150495</v>
+        <v>151422</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>876</v>
+        <v>914</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -939,7 +1094,693 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" max="1" min="1" width="22"/>
+    <col customWidth="1" max="2" min="2" width="8"/>
+    <col customWidth="1" max="3" min="3" width="19"/>
+    <col customWidth="1" max="4" min="4" width="8"/>
+    <col customWidth="1" max="5" min="5" width="19"/>
+    <col customWidth="1" max="6" min="6" width="8"/>
+    <col customWidth="1" max="7" min="7" width="8"/>
+    <col customWidth="1" max="8" min="8" width="8"/>
+    <col customWidth="1" max="9" min="9" width="8"/>
+    <col customWidth="1" max="10" min="10" width="8"/>
+    <col customWidth="1" max="11" min="11" width="8"/>
+    <col customWidth="1" max="12" min="12" width="8"/>
+    <col customWidth="1" max="13" min="13" width="8"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
+    <col customWidth="1" max="15" min="15" width="14"/>
+    <col customWidth="1" max="16" min="16" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>State: New</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>State: New AND need to be Analyzed or Fixed</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>State: Existing</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>State: Existing AND need to be Analyzed or Fixed</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Status: Analyze</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Status: Ignore</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Status: Not a Problem</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Status: Defer</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Status: Fix</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Status: Fix in Next Release</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Status: Fix in Later Release</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Status: Filter</t>
+        </is>
+      </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
+          <t>Deviation Type: Permitted</t>
+        </is>
+      </c>
+      <c r="O1" s="10" t="inlineStr">
+        <is>
+          <t>Deviation Type: Permitted - Adopted Code</t>
+        </is>
+      </c>
+      <c r="P1" s="10" t="inlineStr">
+        <is>
+          <t>Deviation Type: Permitted - Module Specific</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>MISRA Mandatory</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>MISRA Required</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>MISRA Advisory</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>HIS METRICS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>CERT C Rule</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>CERT C Recommendation</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Total Issues</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="16"/>
@@ -955,12 +1796,15 @@
     <col customWidth="1" max="11" min="11" width="8"/>
     <col customWidth="1" max="12" min="12" width="8"/>
     <col customWidth="1" max="13" min="13" width="8"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
+    <col customWidth="1" max="15" min="15" width="14"/>
+    <col customWidth="1" max="16" min="16" width="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Module name</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -1023,11 +1867,26 @@
           <t>Status: Filter</t>
         </is>
       </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
+          <t>Deviation Type: Permitted</t>
+        </is>
+      </c>
+      <c r="O1" s="10" t="inlineStr">
+        <is>
+          <t>Deviation Type: Permitted - Adopted Code</t>
+        </is>
+      </c>
+      <c r="P1" s="10" t="inlineStr">
+        <is>
+          <t>Deviation Type: Permitted - Module Specific</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>MISRA Mandatory</t>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>No Module</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -1066,492 +1925,18 @@
       <c r="M2" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="N2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>MISRA Required</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>MISRA Advisory</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>HIS METRICS</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Total Issues</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col customWidth="1" max="1" min="1" width="16"/>
-    <col customWidth="1" max="2" min="2" width="8"/>
-    <col customWidth="1" max="3" min="3" width="19"/>
-    <col customWidth="1" max="4" min="4" width="8"/>
-    <col customWidth="1" max="5" min="5" width="19"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="8"/>
-    <col customWidth="1" max="8" min="8" width="8"/>
-    <col customWidth="1" max="9" min="9" width="8"/>
-    <col customWidth="1" max="10" min="10" width="8"/>
-    <col customWidth="1" max="11" min="11" width="8"/>
-    <col customWidth="1" max="12" min="12" width="8"/>
-    <col customWidth="1" max="13" min="13" width="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Module name</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>State: New</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>State: New AND need to be Analyzed or Fixed</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>State: Existing</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>State: Existing AND need to be Analyzed or Fixed</t>
-        </is>
-      </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>Status: Analyze</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>Status: Ignore</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>Status: Not a Problem</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>Status: Defer</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Status: Fix</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>Status: Fix in Next Release</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>Status: Fix in Later Release</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>Status: Filter</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
@@ -1592,47 +1977,65 @@
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="n">
+      <c r="B4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="11" t="n">
+      <c r="E4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="11" t="n">
+      <c r="I4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1647,7 +2050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="18"/>
@@ -1670,6 +2073,7 @@
     <col customWidth="1" max="18" min="18" width="12"/>
     <col customWidth="1" max="19" min="19" width="14"/>
     <col customWidth="1" max="20" min="20" width="23"/>
+    <col customWidth="1" max="21" min="21" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1713,12 +2117,12 @@
           <t>owner</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>severityCode</t>
         </is>
@@ -1743,9 +2147,39 @@
           <t>url</t>
         </is>
       </c>
-      <c r="O1" s="13" t="inlineStr">
+      <c r="O1" s="14" t="inlineStr">
+        <is>
+          <t>Waiver ID</t>
+        </is>
+      </c>
+      <c r="P1" s="14" t="inlineStr">
+        <is>
+          <t>Waiver Classification</t>
+        </is>
+      </c>
+      <c r="Q1" s="14" t="inlineStr">
+        <is>
+          <t>Deviation Type</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>module</t>
+        </is>
+      </c>
+      <c r="T1" s="6" t="inlineStr">
+        <is>
+          <t>Waiver ID/ Comment Validation</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>levels</t>
         </is>
       </c>
     </row>
@@ -1810,11 +2244,17 @@
           <t>KW Issue Link</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
       </c>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1832,7 +2272,7 @@
         <v>1087079</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1529</v>
+        <v>1672</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1877,11 +2317,17 @@
           <t>KW Issue Link</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
       </c>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1948,11 +2394,17 @@
           <t>KW Issue Link</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
       </c>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -2020,11 +2472,17 @@
           <t>KW Issue Link</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
       </c>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2091,11 +2549,17 @@
           <t>KW Issue Link</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
       </c>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2163,11 +2627,17 @@
           <t>KW Issue Link</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
       </c>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2235,11 +2705,17 @@
           <t>KW Issue Link</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
       </c>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2307,14 +2783,20 @@
           <t>KW Issue Link</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>EthFw</t>
         </is>
       </c>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:U9"/>
   <hyperlinks>
     <hyperlink ref="N2" r:id="rId1"/>
     <hyperlink ref="N3" r:id="rId2"/>
@@ -2335,12 +2817,6483 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E339"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" max="1" min="1" width="30"/>
+    <col customWidth="1" max="2" min="2" width="55"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="24"/>
+    <col customWidth="1" max="5" min="5" width="38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>KW Checker Code</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Default severity</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Waiver ID</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Waiver Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>ABV.ANY_SIZE_ARRAY</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow - Array Index Out of Bounds</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow - Array Index Out of Bounds</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ABV.GENERAL.MULTIDIMENSION</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow - Array Index Out of Bounds</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ABV.ITERATOR</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow - Array Index may be out of Bounds</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ABV.MEMBER</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow - Array Index Out of Bounds</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ABV.STACK</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow - Local Array Index Out of Bounds</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ABV.TAINTED</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow from Unvalidated Input</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ABV.UNICODE.BOUND_MAP</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Buffer overflow in mapping character function</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ABV.UNICODE.FAILED_MAP</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Mapping function failed</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ABV.UNICODE.NNTS_MAP</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Buffer overflow in mapping character function</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ABV.UNICODE.SELF_MAP</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Mapping function failed</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ABV.UNKNOWN_SIZE</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow - Array Index Out of Bounds</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ASSIGCOND.CALL</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Assignment in condition (call)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ASSIGCOND.GEN</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Assignment in condition</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.CAST.C</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>C style type cast to BSTR</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.CAST.CPP</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>C++ style type cast to BSTR</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.FUNC.ALLOC</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect call to BSTR allocating function</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.FUNC.FREE</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect call to BSTR freeing function</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.FUNC.LEN</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Trying to get length of non-BSTR string using BSTR-related functions</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.FUNC.REALLOC</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect call to BSTR reallocating function</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.IA.ASSIGN</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>BSTR variable is assigned a non-BSTR value</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.IA.INIT</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>BSTR variable is initialized with a non-BSTR value</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.OPS.ARITHM</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Illegal arithmetic operations with BSTR values</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.OPS.COMP</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Illegal comparison of BSTR values</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>BSTR.OPS.EQS</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Illegal equality comparison of BSTR values</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>BYTEORDER.HTON.SEND</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Missed conversion from host to network byte order</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>BYTEORDER.HTON.WRITE</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Missed conversion from host to network byte order</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BYTEORDER.NTOH.READ</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Missed conversion from network to host byte order</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>BYTEORDER.NTOH.RECV</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Missed conversion from network to host byte order</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>CERT.ARR.PTR.ARITH</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Pointer is used in arithmetic expression</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>CERT.CONC.ATOMIC_TWICE_EXPR</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Do not refer to an atomic variable twice in an expression</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>CERT.EXIT.HANDLER_TERMINATE</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>All exit handlers must return normally</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>CERT.EXPR.PARENS</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>The precedence of operators within expressions should be made explicit.</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>CERT.FILE_PTR.DEREF</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>A pointer to a FILE object shall not be dereferenced</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>CERT.FILE_PTR.DEREF.CAST</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Object is casted to a FILE pointer, and it shall not be dereferenced</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>CERT.FILE_PTR.DEREF.INDIRECT</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>A pointer to a FILE object shall not be indirectly dereferenced by a system function</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>CERT.FILE_PTR.DEREF.RETURN</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>A pointer to a FILE object (returned by function) shall not be dereferenced</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>CERT.FIO.NO_FLUSH</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Flush or positioning function call missing</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>CERT.FSETPOS.VALUE</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Only use values for fsetpos() that are returned from fgetpos()</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>CERT.MEMCMP.FLOAT_MEMBER</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Do not compare when member is floating point</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>CERT.MEMCMP.PADDED_DATA</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Do not compare padding data</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>CERT.OOP.CTOR.VIRTUAL_FUNC</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Do not invoke virtual functions from constructors or destructors</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>CERT.PUTENV.AUTO_VARIABLE</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Do not call putenv() with a pointer to an automatic variable as the argument</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>CERT.STDLIB.SIGNAL</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Do not return from a computational exception signal handler</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>CERT.VA_ARG.TYPE</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Do not call va_arg with an argument of the incorrect type</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>CERT.VA_START.TYPE</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Pass an object of the correct type to va_start</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>CL.ASSIGN.NON_CONST_ARG</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Assignment operator declares non-constant reference argument</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>CL.ASSIGN.RETURN_CONST</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Assignment operator returns constant reference</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>CL.ASSIGN.VOID</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Assignment operator returns void</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>CL.FFM.ASSIGN</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Use of free memory (double free) - no operator=</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>CL.FFM.COPY</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Use of free memory (double free) - no copy constructor</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>CL.FMM</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Freeing Mismatched Memory - in destructor</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>CL.MLK</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Memory Leak - in destructor</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>CL.MLK.ASSIGN</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Memory Leak - in assignment operator</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>CL.MLK.VIRTUAL</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Memory Leak - possible in destructor</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>CL.SELF-ASSIGN</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Use of free memory (double free) - in operator=</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>CL.SHALLOW.ASSIGN</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Use of free memory (double free) - shallow copy in operator=</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>CL.SHALLOW.COPY</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Use of free memory (double free) - shallow copy in copy constructor</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>CONC.DBL_LOCK</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Double Lock</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>CONC.DBL_UNLOCK</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Double Unlock</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>CONC.DL</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Deadlock</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>CONC.NO_LOCK</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Missing lock for variable</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>CONC.NO_UNLOCK</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Missing unlock for variable</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>CONC.SLEEP</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Function may block in critical section</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.ALIGNMENT</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect pointer scaling is used</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.BAD.PTR.ARITH</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Bad pointer arithmetic</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.BITOP.SIZE</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Operands of different size in bitwise operation</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.BOOLOP.INC</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>A boolean is incremented or decremented</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.CAST.VIRTUAL_INHERITANCE</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>C-style cast of pointer to object with virtual methods to pointer to its derived class</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.CMPCHR.EOF</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>A 'char' expression compared with EOF constant</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.CONSTCOND.DO</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>'do' controlling expression is constant</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.CONSTCOND.IF</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>'if' controlling expression is constant</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.CONSTCOND.SWITCH</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>'switch' selector expression is constant</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.CONSTCOND.TERNARY</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Controlling condition in conditional expression is constant</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.CONSTCOND.WHILE</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>'while' controlling expression is constant</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.COPY.NOASSIGN</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Class defines copy constructor, but no assignment operator</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.DTOR.NONVIRT.DELETE</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Delete expression for an object of a class with virtual methods and no virtual destructor</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.DTOR.NONVIRT.NOTEMPTY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Class has virtual functions inherited from a base class, but its destructor is not virtual and not empty</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.DTOR.VOIDPTR</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Delete expression with an object of type pointer to void</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.EMPTY.LABEL</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Empty label statement</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr"/>
+      <c r="E81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.EMPTY.TYPEDEF</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Missing typedef name</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr"/>
+      <c r="E82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.FUNCADDR</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Function address is used instead of a call to this function</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.HIDDEN.PARAM</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Parameter hidden by local variable</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.IMPLICITINT</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Anachronistic 'implicit int'</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.INCL.ABSOLUTE</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Absolute path is used in include directive</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.INCL.NO_INTERFACE</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Source file does not include its interface header</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.INLINE.NONFUNC</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>'inline' used with non-function</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.MEM.NONPOD</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Memory manipulation routine applied to a non-POD object</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.MEMBER.INIT.ORDER</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Members of the initialization list are not listed in the order in which they are declared in the class</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.MEMSET.SIZEOF.PTR</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Memset-like function is called for 'sizeof' applied to pointer</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.MOVE.CONST</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Const value used as argument for std::move</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.NOEFFECT.OUTOFRANGE</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Value outside of range</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr"/>
+      <c r="E93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.NOEFFECT.SELF_ASSIGN</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>A variable is assigned to self</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.NOEFFECT.UCMP.GE</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Comparison of unsigned value against 0 is always true</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr"/>
+      <c r="E95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.NOEFFECT.UCMP.GE.MACRO</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Comparison of unsigned value against 0 within a macro is always true</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr"/>
+      <c r="E96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.NOEFFECT.UCMP.LT</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Comparison of unsigned value against 0 is always false</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr"/>
+      <c r="E97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.NOEFFECT.UCMP.LT.MACRO</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Comparison of unsigned value against 0 within a macro is always false</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr"/>
+      <c r="E98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.NULLCHECK.FUNCNAME</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Function address was directly compared against 0</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.OVERRIDE.CONST</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Function overriding fails due to mismatch of 'const' qualifiers</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr"/>
+      <c r="E100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.PACKED.TYPEDEF</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>'packed' attribute ignored in typedef</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr"/>
+      <c r="E101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.PASSBYVALUE.ARG</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Function argument passed by value is too large</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr"/>
+      <c r="E102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.PASSBYVALUE.EXC</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Exception object passed by value is too large</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr"/>
+      <c r="E103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.RET.MAIN</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Bad return type of main</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr"/>
+      <c r="E104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>CWARN.SIGNEDBIT</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Signed one bit field</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr"/>
+      <c r="E105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>CXX.BITOP.BOOL_OPERAND</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Potential logic error: Boolean expressions should not be used directly as bitwise operator arguments. Consider using logical operators instead.</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr"/>
+      <c r="E106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>CXX.BITOP.NON_CONST_OPERAND</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Bitwise operators should be applied to constants only</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>CXX.CAST.OBJ_PTR_TO_OBJ_PTR</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Cast between a pointer to object type and a pointer to a different object type</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr"/>
+      <c r="E108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>CXX.CAST.SIGNED_CHAR_TO_INTEGER</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Cast char to unsigned char before converting to larger integer sizes</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr"/>
+      <c r="E109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>CXX.DIFF.WIDTH.STR_AND_FUNC</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Implicit cast between narrow and wide character string while calling function</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr"/>
+      <c r="E110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>CXX.ERRNO.INCORRECTLY_CHECKED</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Errno condition check not required after calling library function</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr"/>
+      <c r="E111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>CXX.ERRNO.NOT_CHECKED</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Errno condition check is missing after calling library function</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>CXX.ERRNO.NOT_SET</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Errno is not reset to zero before calling library function</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr"/>
+      <c r="E113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>CXX.ID_VIS.GLOBAL_VARIABLE.EXTERN</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Visibility of extern global variable is too wide</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr"/>
+      <c r="E114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>CXX.ID_VIS.GLOBAL_VARIABLE.STATIC</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Visibility of static global variable is too wide</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr"/>
+      <c r="E115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>CXX.INT_TO_FLOAT.CONV</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Use of implicit conversion in an arithmetic operation</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr"/>
+      <c r="E116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>CXX.LOGICAL_OP.INT_OPERAND</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Potential logic error: Integral expressions should not be used directly as logical operator operands. Boolean expressions should be used instead.</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr"/>
+      <c r="E117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>CXX.LOGICAL_OP.NON_BOOL_CONSTANT</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Logical operators should not be applied directly to constants</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr"/>
+      <c r="E118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>CXX.OVERWRITE_CONST_CHAR</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Attempt to overwrite a constant string</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr"/>
+      <c r="E119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>CXX.POSSIBLE_COPY_PASTE.FSTRING.APPEND_SAME_STRING</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Possible copy-paste error: Appending the same FString twice</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr"/>
+      <c r="E120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>CXX.POSSIBLE_COPY_PASTE.LOGICAL_OP.CMP_SAME_OBJECT</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Possible copy-paste error: An object should not be logically compared to itself</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr"/>
+      <c r="E121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>CXX.POSSIBLE_COPY_PASTE.TERNARY_OP</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Possible copy-paste in the 'then' and 'else' branches of a ternary operator</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr"/>
+      <c r="E122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>CXX.SQL.INJECT</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>SQL Injection</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr"/>
+      <c r="E123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>CXX.STDLIB.ILLEGAL_REUSE</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>The pointer returned by the Standard Library functions asctime and similar shall not be used following a subsequent call to the same function</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr"/>
+      <c r="E124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>CXX.STDLIB.ILLEGAL_WRITE</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>The pointers returned by the Standard Library functions localeconv, getenv, setlocale or, strerror shall only be used as if they have pointer to const-qualified type</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr"/>
+      <c r="E125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>DBZ.CONST</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Division by a zero constant occurs</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr"/>
+      <c r="E126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>DBZ.CONST.CALL</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>The value '0' is passed to function that can use this value as divisor</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr"/>
+      <c r="E127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>DBZ.GENERAL</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Division by zero might occur</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr"/>
+      <c r="E128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>DBZ.ITERATOR</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Division by zero might occur in a loop iterator</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr"/>
+      <c r="E129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>DBZ.ITERATOR.CALL</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Division by zero might occur in a function call</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr"/>
+      <c r="E130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>EFFECT</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Statement has no effect</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr"/>
+      <c r="E131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>FMM.MIGHT</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Freeing Mismatched Memory - possible</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr"/>
+      <c r="E132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>FMM.MUST</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Freeing Mismatched Memory</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr"/>
+      <c r="E133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>FNH.MIGHT</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Freeing Non-Heap Memory - possible</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr"/>
+      <c r="E134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>FNH.MUST</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Freeing Non-Heap Memory</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr"/>
+      <c r="E135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>FREE.INCONSISTENT</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Inconsistent Freeing of Memory</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr"/>
+      <c r="E136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>FUM.GEN.MIGHT</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Freeing Unallocated Memory - possible</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr"/>
+      <c r="E137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>FUM.GEN.MUST</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Freeing Unallocated Memory</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr"/>
+      <c r="E138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>FUNCRET.GEN</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Non-void function does not return value</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr"/>
+      <c r="E139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>FUNCRET.IMPLICIT</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Non-void function implicitly returning int does not return value</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr"/>
+      <c r="E140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>HCC</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Use of hardcoded credentials</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr"/>
+      <c r="E141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>HCC.PWD</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Use of a hardcoded password</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr"/>
+      <c r="E142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>HCC.USER</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Use of a hardcoded user name</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr"/>
+      <c r="E143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>INCONSISTENT.LABEL</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Inconsistent Case Labels</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr"/>
+      <c r="E144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECT.ALLOC_SIZE</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect Allocation Size</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr"/>
+      <c r="E145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>INFINITE_LOOP.GLOBAL</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Infinite loop</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr"/>
+      <c r="E146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>INFINITE_LOOP.LOCAL</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Infinite loop</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr"/>
+      <c r="E147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>INFINITE_LOOP.MACRO</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Infinite loop</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr"/>
+      <c r="E148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>INVARIANT_CONDITION.GEN</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Invariant expression in a condition</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr"/>
+      <c r="E149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>INVARIANT_CONDITION.UNREACH</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>Invariant expression in a condition</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr"/>
+      <c r="E150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>ITER.CONTAINER.MODIFIED</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Use of invalid iterator</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr"/>
+      <c r="E151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>ITER.END.DEREF.MIGHT</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Dereference of 'end' iterator</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>ITER.END.DEREF.MUST</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Dereference of 'end' iterator</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr"/>
+      <c r="E153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>ITER.INAPPROPRIATE</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Use of iterator with inappropriate container object</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr"/>
+      <c r="E154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>ITER.INAPPROPRIATE.MULTIPLE</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Use of iterator with inappropriate container object</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr"/>
+      <c r="E155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>LA_UNUSED</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>Label unused</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr"/>
+      <c r="E156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>LOCRET.ARG</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Function returns address of local variable</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr"/>
+      <c r="E157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>LOCRET.GLOB</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Function returns address of local variable</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr"/>
+      <c r="E158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>LOCRET.RET</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Function returns address of local variable</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr"/>
+      <c r="E159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>LS.CALL</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>Suspicious use of non-localized string in GUI function</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr"/>
+      <c r="E160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>LS.CALL.STRING</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Suspicious use of non-localized string in GUI function</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr"/>
+      <c r="E161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>LV_UNUSED.GEN</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Local variable unused</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr"/>
+      <c r="E162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>MLK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Memory Leak - possible</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr"/>
+      <c r="E163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>MLK.MUST</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Memory Leak</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr"/>
+      <c r="E164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>MLK.RET.MIGHT</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Memory Leak - possible</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr"/>
+      <c r="E165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>MLK.RET.MUST</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Memory Leak</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr"/>
+      <c r="E166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>NNTS.MIGHT</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow - Non-null Terminated String</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr"/>
+      <c r="E167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>NNTS.MUST</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow - Non-null Terminated String</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr"/>
+      <c r="E168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>NNTS.TAINTED</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Unvalidated User Input Causing Buffer Overflow - Non-Null Terminated String</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr"/>
+      <c r="E169" s="3" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>NPD.CHECK.CALL.MIGHT</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>Pointer may be passed to function that can dereference it after it was positively checked for NULL</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr"/>
+      <c r="E170" s="3" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>NPD.CHECK.CALL.MUST</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>Pointer will be passed to function that may dereference it after it was positively checked for NULL</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr"/>
+      <c r="E171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>NPD.CHECK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Pointer may be dereferenced after it was positively checked for NULL</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr"/>
+      <c r="E172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>NPD.CHECK.MUST</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Pointer will be dereferenced after it was positively checked for NULL</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr"/>
+      <c r="E173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>NPD.CONST.CALL</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>NULL is passed to function that can dereference it</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr"/>
+      <c r="E174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>NPD.CONST.DEREF</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>NULL is dereferenced</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr"/>
+      <c r="E175" s="3" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>NPD.FUNC.CALL.MIGHT</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Result of function that may return NULL may be passed to another function that may dereference it</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr"/>
+      <c r="E176" s="3" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>NPD.FUNC.CALL.MUST</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Result of function that may return NULL will be passed to another function that may dereference it</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr"/>
+      <c r="E177" s="3" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>NPD.FUNC.MIGHT</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Result of function that can return NULL may be dereferenced</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr"/>
+      <c r="E178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>NPD.FUNC.MUST</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>Result of function that may return NULL will be dereferenced</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr"/>
+      <c r="E179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>NPD.GEN.CALL.MIGHT</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Null pointer may be passed to function that may dereference it</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr"/>
+      <c r="E180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>NPD.GEN.CALL.MUST</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Null pointer will be passed to function that may dereference it</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr"/>
+      <c r="E181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>NPD.GEN.MIGHT</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>Null pointer may be dereferenced</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr"/>
+      <c r="E182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>NPD.GEN.MUST</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Null pointer will be dereferenced</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr"/>
+      <c r="E183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>NUM.OVERFLOW</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>Possible Overflow</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr"/>
+      <c r="E184" s="3" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>NUM.OVERFLOW.DF</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>Possible numeric overflow or wraparound</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr"/>
+      <c r="E185" s="3" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.BITFIELDS</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Usage of bitfields within a structure</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr"/>
+      <c r="E186" s="3" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.BSWAP.MACRO</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>A custom byte swap macro is used without checking endian</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr"/>
+      <c r="E187" s="3" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.BYTEORDER.SIZE</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>An incompatible type is used with a network macro such as 'ntohl'</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr"/>
+      <c r="E188" s="3" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.CAST.FLTPNT</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>Cast of a floating point expression to a non floating point type</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr"/>
+      <c r="E189" s="3" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.CAST.PTR</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>Cast between types that are not both pointers or not pointers</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr"/>
+      <c r="E190" s="3" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.CAST.PTR.FLTPNT</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>Cast of a pointer to a floating point expression to a non floating point type pointer</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr"/>
+      <c r="E191" s="3" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.CAST.PTR.SIZE</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Attempt to cast an expression to a type of a potentially incompatible size</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr"/>
+      <c r="E192" s="3" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.CAST.SIZE</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Expression is cast to a type of potentially different size</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr"/>
+      <c r="E193" s="3" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.CMPSPEC.EFFECTS.ASSIGNMENT</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Assignment in a function parameter</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr"/>
+      <c r="E194" s="3" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.CMPSPEC.TYPE.BOOL</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Assignment to a 'bool' type is larger than 1 byte</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr"/>
+      <c r="E195" s="3" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.CMPSPEC.TYPE.LONGLONG</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Use of 'long long'</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr"/>
+      <c r="E196" s="3" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.MACRO.NUMTYPE</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Macro describing a builtin numeric type is used</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr"/>
+      <c r="E197" s="3" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.OPTS</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>Compiler dependant option is used</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr"/>
+      <c r="E198" s="3" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.PRAGMA.ALIGN</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>#pragma align usage</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr"/>
+      <c r="E199" s="3" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.PRAGMA.PACK</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>#pragma pack usage</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr"/>
+      <c r="E200" s="3" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.SIGNED.CHAR</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>'char' used without explicitly specifying signedness</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr"/>
+      <c r="E201" s="3" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.STORAGE.STRUCT</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>Byte position of elements in a structure could depend on alignment and packing attributes.</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr"/>
+      <c r="E202" s="3" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.STRUCT.BOOL</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Struct/class has a bool member</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr"/>
+      <c r="E203" s="3" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.UNIONS</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Union is used within an enclosing struct/class/other union</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr"/>
+      <c r="E204" s="3" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.UNSIGNEDCHAR.OVERFLOW.FALSE</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Relational expression may be always false depending on 'char' type signedness</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr"/>
+      <c r="E205" s="3" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.UNSIGNEDCHAR.OVERFLOW.TRUE</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>Relational expression may be always true depending on 'char' type signedness</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr"/>
+      <c r="E206" s="3" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.UNSIGNEDCHAR.RELOP</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>Relational operations used between explicitly signed/unsigned char and char without signedness specification</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr"/>
+      <c r="E207" s="3" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>PORTING.VAR.EFFECTS</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>Variable used twice in one expression where one usage is subject to side-effects</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr"/>
+      <c r="E208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>PRECISION.LOSS</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>Loss of Precision</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr"/>
+      <c r="E209" s="3" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>PRECISION.LOSS.CALL</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>Loss of Precision during function call</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr"/>
+      <c r="E210" s="3" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>RABV.CHECK</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>Suspicious use of index before boundary check</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr"/>
+      <c r="E211" s="3" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>RCA</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Risky cryptographic algorithm used</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr"/>
+      <c r="E212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>RCA.HASH.SALT.EMPTY</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Use of a one-way hash with an empty salt</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr"/>
+      <c r="E213" s="3" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>RETVOID.GEN</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>Non-void function returns void value</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr"/>
+      <c r="E214" s="3" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>RETVOID.IMPLICIT</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Implicitly int function returns void value</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr"/>
+      <c r="E215" s="3" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>RH.LEAK</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>Resource leak</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr"/>
+      <c r="E216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>RN.INDEX</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>Suspicious use of index before negative check</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr"/>
+      <c r="E217" s="3" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>RNPD.CALL</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Suspicious dereference of pointer in function call before NULL check</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr"/>
+      <c r="E218" s="3" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>RNPD.DEREF</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>Suspicious dereference of pointer before NULL check</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr"/>
+      <c r="E219" s="3" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>SEMICOL</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>Suspiciously placed semicolon</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr"/>
+      <c r="E220" s="3" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>SPECTRE.VARIANT1</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>Potential exploit of speculative execution</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr"/>
+      <c r="E221" s="3" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.ASSIGN</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>Assignment does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr"/>
+      <c r="E222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.ASSIGN.ARG</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Assignment does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr"/>
+      <c r="E223" s="3" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.ASSIGN.CONST</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>Assignment does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr"/>
+      <c r="E224" s="3" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.ASSIGN.INIT</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>Assignment does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr"/>
+      <c r="E225" s="3" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.ASSIGN.RETURN</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>Assignment does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr"/>
+      <c r="E226" s="3" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.ASSIGN.ZERO</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>Assignment does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr"/>
+      <c r="E227" s="3" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.EXTRACT</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>Assignment does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr"/>
+      <c r="E228" s="3" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.JOIN.CMP</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>Joining with binary operator does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr"/>
+      <c r="E229" s="3" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.JOIN.CONST</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>Joining with binary operator does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr"/>
+      <c r="E230" s="3" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.JOIN.EQ</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>Joining with binary operator does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr"/>
+      <c r="E231" s="3" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.JOIN.OTHER</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>Joining with binary operator does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr"/>
+      <c r="E232" s="3" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>STRONG.TYPE.JOIN.ZERO</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>Joining with binary operator does not respect strong typing</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr"/>
+      <c r="E233" s="3" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.RECOMMENDED.ALLOCA</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>Banned recommended API: stack allocation functions</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr"/>
+      <c r="E234" s="3" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.RECOMMENDED.NUMERIC</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>Banned recommended API: unsafe numeric conversion functions</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr"/>
+      <c r="E235" s="3" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.RECOMMENDED.OEM</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>Banned recommended API: OEM character page conversion functions</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr"/>
+      <c r="E236" s="3" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.RECOMMENDED.PATH</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>Banned recommended API: unsafe path name manipulation functions</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr"/>
+      <c r="E237" s="3" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.RECOMMENDED.SCANF</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>Banned recommended API: unsafe scanf-type functions</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr"/>
+      <c r="E238" s="3" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.RECOMMENDED.SPRINTF</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>Banned recommended API: unsafe sprintf-type functions</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr"/>
+      <c r="E239" s="3" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.RECOMMENDED.STRLEN</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>Banned recommended API: unsafe string length functions</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr"/>
+      <c r="E240" s="3" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.RECOMMENDED.TOKEN</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Banned recommended API: unsafe string tokenizing functions</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr"/>
+      <c r="E241" s="3" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.RECOMMENDED.WINDOW</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>Banned recommended API: unsafe window functions</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr"/>
+      <c r="E242" s="3" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.REQUIRED.CONCAT</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>Banned required API: unsafe string concatenation functions</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr"/>
+      <c r="E243" s="3" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.REQUIRED.COPY</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>Banned required API: unsafe buffer copy functions</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr"/>
+      <c r="E244" s="3" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.REQUIRED.GETS</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>Banned required API: unsafe stream reading functions</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr"/>
+      <c r="E245" s="3" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.REQUIRED.ISBAD</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>Banned required API: IsBad-type functions</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr"/>
+      <c r="E246" s="3" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>SV.BANNED.REQUIRED.SPRINTF</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>Banned required API: unsafe sprintf-type functions</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr"/>
+      <c r="E247" s="3" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>SV.BFC.USING_STRUCT</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>Use of INADDR_ANY in sin_addr.s_addr field of struct sockaddr_in Structure Used for Call to bind Function</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr"/>
+      <c r="E248" s="3" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>SV.BRM.HKEY_LOCAL_MACHINE</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>HKEY_LOCAL_MACHINE Used as 'hkey' Parameter for Registry Manipulation Function</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr"/>
+      <c r="E249" s="3" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>SV.CODE_INJECTION.SHELL_EXEC</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>Command Injection into Shell Execution</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr"/>
+      <c r="E250" s="3" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>SV.DLLPRELOAD.NONABSOLUTE.DLL</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>Potential DLL-preload hijack vector</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr"/>
+      <c r="E251" s="3" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>SV.DLLPRELOAD.NONABSOLUTE.EXE</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>Potential process injection vector</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr"/>
+      <c r="E252" s="3" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>SV.DLLPRELOAD.SEARCHPATH</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>Do not use SearchPath to find DLLs</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr"/>
+      <c r="E253" s="3" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>SV.FIU.PROCESS_VARIANTS</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>Use of Dangerous Process Creation</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr"/>
+      <c r="E254" s="3" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.BAD_SCAN_FORMAT</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>Input format specifier error</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr"/>
+      <c r="E255" s="3" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.PRINT_FORMAT_MISMATCH.BAD</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>Incompatible type of a print function parameter</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr"/>
+      <c r="E256" s="3" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.PRINT_FORMAT_MISMATCH.UNDESIRED</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>Unexpected type of a print function parameter</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr"/>
+      <c r="E257" s="3" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.PRINT_IMPROP_LENGTH</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>Improper use of length modifier in a print function call</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr"/>
+      <c r="E258" s="3" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.PRINT_PARAMS_WRONGNUM.FEW</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>Too few arguments in a print function call</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr"/>
+      <c r="E259" s="3" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.PRINT_PARAMS_WRONGNUM.MANY</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>Too many arguments in a print function call</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr"/>
+      <c r="E260" s="3" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.SCAN_FORMAT_MISMATCH.BAD</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>Incompatible type of a scan function parameter</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr"/>
+      <c r="E261" s="3" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.SCAN_FORMAT_MISMATCH.UNDESIRED</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>Unexpected type of a scan function parameter</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr"/>
+      <c r="E262" s="3" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.SCAN_IMPROP_LENGTH</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>Improper use of length modifier in a scan function call</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr"/>
+      <c r="E263" s="3" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.SCAN_PARAMS_WRONGNUM.FEW</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>Too few arguments in a scan function call</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr"/>
+      <c r="E264" s="3" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.SCAN_PARAMS_WRONGNUM.MANY</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>Too many arguments in a scan function call</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr"/>
+      <c r="E265" s="3" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.UNKWN_FORMAT</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>Unknown format specifier in a print function call</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr"/>
+      <c r="E266" s="3" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMT_STR.UNKWN_FORMAT.SCAN</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Unknown format specifier in a scan function call</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr"/>
+      <c r="E267" s="3" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>SV.FMTSTR.GENERIC</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>Format String Vulnerability</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr"/>
+      <c r="E268" s="3" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>SV.INCORRECT_RESOURCE_HANDLING.URH</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>Insecure Resource Handling</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr"/>
+      <c r="E269" s="3" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>SV.INCORRECT_RESOURCE_HANDLING.WRONG_STATUS</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>Insecure Resource Handling</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr"/>
+      <c r="E270" s="3" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>SV.LPP.CONST</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>Use of Insecure Macro for Dangerous Functions</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr"/>
+      <c r="E271" s="3" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>SV.LPP.VAR</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>Use of Insecure Parameter for Dangerous Functions</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr"/>
+      <c r="E272" s="3" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>SV.PCC.CONST</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>Insecure (Constant) Temporary File Name in Call to CreateFile</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr"/>
+      <c r="E273" s="3" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>SV.PCC.INVALID_TEMP_PATH</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>Insecure Temporary File Name in Call to CreateFile</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr"/>
+      <c r="E274" s="3" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>SV.PCC.MISSING_TEMP_CALLS.MUST</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>Missing Secure Temporary File Names in Call to CreateFile</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr"/>
+      <c r="E275" s="3" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>SV.PCC.MISSING_TEMP_FILENAME</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>Missing Temporary File Name in Call to CreateFile</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr"/>
+      <c r="E276" s="3" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>SV.PCC.MODIFIED_BEFORE_CREATE</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>Modification of Temporary File Name before Call to CreateFile</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr"/>
+      <c r="E277" s="3" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>SV.PIPE.CONST</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>Potential pipe hijacking</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr"/>
+      <c r="E278" s="3" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>SV.PIPE.VAR</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>Potential pipe hijacking</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr"/>
+      <c r="E279" s="3" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>SV.RVT.RETVAL_NOTTESTED</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>Ignored Return Value</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr"/>
+      <c r="E280" s="3" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>SV.SIP.CONST</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>Use of Insecure Macro for Dangerous Functions</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr"/>
+      <c r="E281" s="3" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>SV.SIP.VAR</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>Use of Insecure Parameter for Dangerous Functions</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr"/>
+      <c r="E282" s="3" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>SV.STR_PAR.UNDESIRED_STRING_PARAMETER</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>Undesired String for File Path</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr"/>
+      <c r="E283" s="3" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>SV.STRBO.BOUND_COPY.OVERFLOW</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow in Bound String Copy</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr"/>
+      <c r="E284" s="3" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>SV.STRBO.BOUND_COPY.UNTERM</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>Possible Buffer Overflow in Following String Operations</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr"/>
+      <c r="E285" s="3" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>SV.STRBO.BOUND_SPRINTF</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow in Bound sprintf</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr"/>
+      <c r="E286" s="3" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>SV.STRBO.UNBOUND_COPY</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow in Unbound String Copy</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr"/>
+      <c r="E287" s="3" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>SV.STRBO.UNBOUND_SPRINTF</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>Buffer Overflow in Unbound sprintf</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr"/>
+      <c r="E288" s="3" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.ALLOC_SIZE</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Integer in Memory Allocation</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr"/>
+      <c r="E289" s="3" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.BINOP</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Integer in Binary Operation</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr"/>
+      <c r="E290" s="3" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.CALL.BINOP</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Integer in Binary Operation</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr"/>
+      <c r="E291" s="3" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.CALL.DEREF</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>Dereference Of An Unvalidated Pointer</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr"/>
+      <c r="E292" s="3" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.CALL.GLOBAL</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Integer in an Assignment Operation</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr"/>
+      <c r="E293" s="3" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.CALL.INDEX_ACCESS</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Integer as Array Index by Function Call</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr"/>
+      <c r="E294" s="3" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.CALL.LOOP_BOUND</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Integer in Loop Condition through a Function Call</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr"/>
+      <c r="E295" s="3" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.DEREF</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>Dereference Of An Unvalidated Pointer</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr"/>
+      <c r="E296" s="3" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.FMTSTR</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Data in a Format String</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr"/>
+      <c r="E297" s="3" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.GLOBAL</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Integer in an Assignment Operation</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr"/>
+      <c r="E298" s="3" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.INDEX_ACCESS</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Integer as Array Index</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr"/>
+      <c r="E299" s="3" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.INJECTION</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>Command Injection</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr"/>
+      <c r="E300" s="3" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.LOOP_BOUND</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Integer in Loop Condition</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr"/>
+      <c r="E301" s="3" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.PATH_TRAVERSAL</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>Use of Unvalidated Data in a Path Traversal</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr"/>
+      <c r="E302" s="3" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.SECURITY_DECISION</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>Security Decision</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr"/>
+      <c r="E303" s="3" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>SV.TAINTED.XSS.REFLECTED</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>Cross-site Scripting Vulnerability</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr"/>
+      <c r="E304" s="3" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>SV.TOCTOU.FILE_ACCESS</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>Time of Creation/Time of Use Race condition in File Access</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr"/>
+      <c r="E305" s="3" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>SV.UNBOUND_STRING_INPUT.CIN</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>Usage of cin for unbounded string input</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr"/>
+      <c r="E306" s="3" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>SV.UNBOUND_STRING_INPUT.FUNC</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>Usage of unbounded string input</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr"/>
+      <c r="E307" s="3" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>SV.USAGERULES.PERMISSIONS</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>Use of Privilege Elevation</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr"/>
+      <c r="E308" s="3" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>SV.USAGERULES.PROCESS_VARIANTS</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>Use of Dangerous Process Creation Function</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr"/>
+      <c r="E309" s="3" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>SV.USAGERULES.SPOOFING</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>Use of Function Susceptible to Spoofing</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr"/>
+      <c r="E310" s="3" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>SV.WEAK_CRYPTO.WEAK_HASH</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>Weak Hash Function</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr"/>
+      <c r="E311" s="3" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>UFM.DEREF.MIGHT</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>Use of free memory (access) - possible</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr"/>
+      <c r="E312" s="3" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>UFM.DEREF.MUST</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>Use of Freed Memory by Pointer</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr"/>
+      <c r="E313" s="3" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>UFM.FFM.MIGHT</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>Use of free memory (double free) - possible</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr"/>
+      <c r="E314" s="3" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>UFM.FFM.MUST</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>Freeing Freed Memory</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr"/>
+      <c r="E315" s="3" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>UFM.RETURN.MIGHT</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>Use of freed memory (return) - possible</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr"/>
+      <c r="E316" s="3" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>UFM.RETURN.MUST</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>Use of Freed Memory on Return</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr"/>
+      <c r="E317" s="3" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>UFM.USE.MIGHT</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>Use of free memory - possible</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr"/>
+      <c r="E318" s="3" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>UFM.USE.MUST</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>Use of Freed Memory</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr"/>
+      <c r="E319" s="3" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.CTOR.MIGHT</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>Uninitialized Variable in Constructor - possible</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr"/>
+      <c r="E320" s="3" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.CTOR.MUST</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>Uninitialized Variable in Constructor</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr"/>
+      <c r="E321" s="3" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.HEAP.MIGHT</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>Uninitialized Heap Use - possible</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr"/>
+      <c r="E322" s="3" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.HEAP.MUST</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>Uninitialized Heap Use</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr"/>
+      <c r="E323" s="3" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.STACK.ARRAY.MIGHT</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>Uninitialized Array - possible</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr"/>
+      <c r="E324" s="3" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.STACK.ARRAY.MUST</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>Uninitialized Array</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr"/>
+      <c r="E325" s="3" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.STACK.ARRAY.PARTIAL.MUST</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>Partially Uninitialized Array</t>
+        </is>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr"/>
+      <c r="E326" s="3" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.STACK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>Uninitialized Variable - possible</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr"/>
+      <c r="E327" s="3" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.STACK.MUST</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>Uninitialized Variable</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr"/>
+      <c r="E328" s="3" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>UNREACH.ENUM</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>Code is unreachable due to the possible value(s) of an enum</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr"/>
+      <c r="E329" s="3" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>UNREACH.GEN</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>Unreachable code</t>
+        </is>
+      </c>
+      <c r="C330" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr"/>
+      <c r="E330" s="3" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>UNREACH.RETURN</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>Unreachable Void Return</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="inlineStr"/>
+      <c r="E331" s="3" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>UNREACH.SIZEOF</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>Architecture-related unreachable code</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr"/>
+      <c r="E332" s="3" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>UNUSED.FUNC.GEN</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>Function defined but not used</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr"/>
+      <c r="E333" s="3" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>UNUSED.FUNC.STL_EMPTY</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>Ignored return value of an STL object empty() method</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr"/>
+      <c r="E334" s="3" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>UNUSED.FUNC.WARN</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>Potential unused function</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr"/>
+      <c r="E335" s="3" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>VA.LIST.INDETERMINATE</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>Attempt to call va_arg() on a va_list that has an indeterminate value</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr"/>
+      <c r="E336" s="3" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>VA_UNUSED.GEN</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>Value is Never Used after Assignment</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr"/>
+      <c r="E337" s="3" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>VA_UNUSED.INIT</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>Value is Never Used after Initialization</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr"/>
+      <c r="E338" s="3" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>VOIDRET</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>Void function returns value</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr"/>
+      <c r="E339" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E339"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="41"/>
-    <col customWidth="1" max="2" min="2" width="8"/>
-    <col customWidth="1" max="3" min="3" width="75"/>
+    <col customWidth="1" max="2" min="2" width="45"/>
+    <col customWidth="1" max="3" min="3" width="12"/>
     <col customWidth="1" max="4" min="4" width="8"/>
     <col customWidth="1" max="5" min="5" width="13"/>
     <col customWidth="1" max="6" min="6" width="20"/>
@@ -10002,7 +16955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10054,102 +17007,4 @@
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col customWidth="1" max="1" min="1" width="27"/>
-    <col customWidth="1" max="2" min="2" width="10"/>
-    <col customWidth="1" max="3" min="3" width="13"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
-    <col customWidth="1" max="5" min="5" width="60"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Document Status</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Dhruv Dixit and Gayathri Ajith</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>26th-July-2022</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Combined as single reporting sheet for Static analysis reporting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Dhruv Dixit</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>3rd-Jan-2023</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Modified with changes within summary sheets, also added CIP marking.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-</worksheet>
 </file>
--- a/docs/misrac/ethfw_SA_Report.xlsx
+++ b/docs/misrac/ethfw_SA_Report.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Template Revision History" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$U$304</definedName>
+    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$U$315</definedName>
     <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">'SA_GEP'!$A$1:$E$339</definedName>
     <definedName hidden="1" localSheetId="7" name="_xlnm._FilterDatabase">'Taxonomy Checkers'!$A$1:$F$339</definedName>
   </definedNames>
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Copyright (C) 2024 Texas Instruments Incorporated</t>
+          <t>Copyright (C) 2025 Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW_KW_BUILD_Nov_24_2024_10_10_AM</t>
+          <t>ETHFW_KW_BUILD_May_04_2025_09_10_AM</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24 06:14:22.807079-06:00 CDT</t>
+          <t>2025-05-04 07:41:27.783534-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1048,37 +1048,37 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW_KW_BUILD_Nov_24_2024_10_10_AM</t>
+          <t>ETHFW_KW_BUILD_May_04_2025_09_10_AM</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2107</v>
+        <v>2144</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Sun Nov 24 17:02:56 IST 2024</t>
+          <t>Sun May 04 16:06:57 IST 2025</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>429334</v>
+        <v>437540</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>372290</v>
+        <v>376582</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>7968</v>
+        <v>8039</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>657875</v>
+        <v>659089</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2768</v>
+        <v>2807</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>13756</v>
+        <v>13974</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>23</v>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>24</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -1732,25 +1732,25 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I12" s="13" t="n">
         <v>23</v>
@@ -1898,19 +1898,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C2" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="E2" s="12" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -1956,19 +1956,19 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="E3" s="12" t="n">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0</v>
@@ -2002,25 +2002,25 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I4" s="13" t="n">
         <v>23</v>
@@ -2058,7 +2058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U304"/>
+  <dimension ref="A1:U315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="18"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L137" s="3" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr">
@@ -12447,7 +12447,7 @@
       <c r="B141" s="3" t="inlineStr"/>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/safertos_j721e_r5f_009-004-199-024-219-005/source_code_and_projects/SafeRTOS/kernel/task.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/safertos_j721e_r5f_009-005-199-024-219-005/source_code_and_projects/SafeRTOS/kernel/task.c</t>
         </is>
       </c>
       <c r="D141" s="3" t="n">
@@ -12520,7 +12520,7 @@
       <c r="B142" s="3" t="inlineStr"/>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/safertos_j721e_r5f_009-004-199-024-219-005/source_code_and_projects/SafeRTOS/kernel/timers.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/safertos_j721e_r5f_009-005-199-024-219-005/source_code_and_projects/SafeRTOS/kernel/timers.c</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -12600,7 +12600,7 @@
         <v>1242158</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -12673,11 +12673,11 @@
         <v>1247342</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Pointer '*forAllDomainSM' may be dereferenced at line 598 after having been checked for NULL.</t>
+          <t>Pointer '*forAllDomainSM' may be dereferenced at line 604 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -12969,7 +12969,7 @@
         <v>1300666</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>1300667</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>1300668</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>1300669</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>1300670</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>1300671</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>1300672</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>1300673</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1300674</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>1300675</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>1300676</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>1300677</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>1300678</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>1300679</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>1300680</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>1300681</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>1300682</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>1300683</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>1300684</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>1300685</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>1300686</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>1302217</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>1307747</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>760</v>
+        <v>901</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -15299,29 +15299,29 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr"/>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_combase/tilld/lldenetext.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_memutils.c</t>
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>1311736</v>
+        <v>1313423</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>271</v>
+        <v>143</v>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Array 'gateCmdList' of size 16 may use index value(s) 16</t>
+          <t>Pointer 'dst' returned from call to function 'nconf_memalloc_def' at line 141 may be NULL and may be dereferenced at line 143.</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>LLDEnetTasSetConfig</t>
+          <t>nconf_strdup_def</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr">
@@ -15372,29 +15372,29 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>SV.TAINTED.CALL.INDEX_ACCESS</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr"/>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_combase/tilld/lldenetext.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_msgdec.c</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>1311737</v>
+        <v>1313480</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>272</v>
+        <v>341</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Array 'gateCmdList' of size 16 may use index value(s) 16</t>
+          <t>Unvalidated integer value 'xmllen' is received from 'nconf_msgdec_parse_chunked_frame' at line 328 and can be used to access an array through call to 'nconf_xmlutils_parse_xml' at line 341.</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>LLDEnetTasSetConfig</t>
+          <t>nconf_msgdec_parse_netconf_frame</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
@@ -15404,11 +15404,11 @@
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="J180" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
@@ -15445,29 +15445,29 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>SV.TAINTED.CALL.INDEX_ACCESS</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr"/>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_memutils.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_msgdec.c</t>
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>1313423</v>
+        <v>1313481</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>143</v>
+        <v>445</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'dst' returned from call to function 'nconf_memalloc_def' at line 141 may be NULL and may be dereferenced at line 143.</t>
+          <t>Unvalidated integer value 'chunksize' is received from 'strtol' at line 437 and can be used to access an array through call to 'memmove' at line 445.</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>nconf_strdup_def</t>
+          <t>nconf_msgdec_parse_chunked_frame</t>
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr">
@@ -15477,11 +15477,11 @@
       </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="J181" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
@@ -15518,29 +15518,29 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>SV.TAINTED.CALL.INDEX_ACCESS</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr"/>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_msgdec.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_msghdlr.c</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>1313480</v>
+        <v>1313826</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>341</v>
+        <v>1478</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Unvalidated integer value 'xmllen' is received from 'nconf_msgdec_parse_chunked_frame' at line 328 and can be used to access an array through call to 'nconf_xmlutils_parse_xml' at line 341.</t>
+          <t>Pointer 'sndbuf' returned from call to function 'nconf_memalloc_def' at line 1476 may be NULL and may be dereferenced at line 1478.</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>nconf_msgdec_parse_netconf_frame</t>
+          <t>nconf_msghdlr_send_get_schema_resp</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
@@ -15550,11 +15550,11 @@
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J182" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
@@ -15591,29 +15591,29 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>SV.TAINTED.CALL.INDEX_ACCESS</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr"/>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_msgdec.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/platform/ti-frtos/nconf_transmngr.c</t>
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>1313481</v>
+        <v>1314024</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>445</v>
+        <v>268</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Unvalidated integer value 'chunksize' is received from 'strtol' at line 437 and can be used to access an array through call to 'memmove' at line 445.</t>
+          <t>Pointer 'pRecvMsg' returned from call to function 'nconf_tlscon_recv_msg' at line 266 may be NULL and may be dereferenced at line 268.</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>nconf_msgdec_parse_chunked_frame</t>
+          <t>nconf_transport_process_tls_client_msg</t>
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr">
@@ -15623,11 +15623,11 @@
       </c>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J183" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
@@ -15670,23 +15670,23 @@
       <c r="B184" s="3" t="inlineStr"/>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_msghdlr.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_ucclient.c</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>1313826</v>
+        <v>1314341</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>1478</v>
+        <v>293</v>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'sndbuf' returned from call to function 'nconf_memalloc_def' at line 1476 may be NULL and may be dereferenced at line 1478.</t>
+          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 291 may be NULL and may be dereferenced at line 293.</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>nconf_msghdlr_send_get_schema_resp</t>
+          <t>nconf_ucclient_get_schema_hdl</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
@@ -15743,23 +15743,23 @@
       <c r="B185" s="3" t="inlineStr"/>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/platform/ti-frtos/nconf_transmngr.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_ucclient.c</t>
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>1314024</v>
+        <v>1314342</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>268</v>
+        <v>1075</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pRecvMsg' returned from call to function 'nconf_tlscon_recv_msg' at line 266 may be NULL and may be dereferenced at line 268.</t>
+          <t>Pointer 'retbuf' returned from call to function 'nconf_memalloc_def' at line 1073 may be NULL and may be dereferenced at line 1075.</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>nconf_transport_process_tls_client_msg</t>
+          <t>nconf_ucclient_get_vstr</t>
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr">
@@ -15820,19 +15820,19 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>1314341</v>
+        <v>1314343</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>293</v>
+        <v>1260</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 291 may be NULL and may be dereferenced at line 293.</t>
+          <t>Pointer 'cfginfo-&gt;path' returned from call to function 'nconf_strdup_def' at line 1253 may be NULL and may be dereferenced at line 1260.</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_schema_hdl</t>
+          <t>nconf_ucclient_update_config_cache</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
@@ -15893,19 +15893,19 @@
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>1314342</v>
+        <v>1314344</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>1075</v>
+        <v>1434</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'retbuf' returned from call to function 'nconf_memalloc_def' at line 1073 may be NULL and may be dereferenced at line 1075.</t>
+          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 1431 may be NULL and may be dereferenced at line 1434.</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_vstr</t>
+          <t>nconf_ucclient_get_schema_namespace</t>
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr">
@@ -15966,19 +15966,19 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>1314343</v>
+        <v>1314345</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>1260</v>
+        <v>1460</v>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'cfginfo-&gt;path' returned from call to function 'nconf_strdup_def' at line 1253 may be NULL and may be dereferenced at line 1260.</t>
+          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 1458 may be NULL and may be dereferenced at line 1460.</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_update_config_cache</t>
+          <t>nconf_ucclient_schema_search</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr">
@@ -16039,19 +16039,19 @@
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>1314344</v>
+        <v>1314346</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>1434</v>
+        <v>1739</v>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 1431 may be NULL and may be dereferenced at line 1434.</t>
+          <t>Pointer 'kvpair' returned from call to function 'nconf_memalloc_def' at line 1737 may be NULL and may be dereferenced at line 1739.</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_schema_namespace</t>
+          <t>nconf_ucclient_is_nodekey_sent</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr">
@@ -16102,7 +16102,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr"/>
@@ -16112,19 +16112,19 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>1314345</v>
+        <v>1314429</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>1460</v>
+        <v>326</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 1458 may be NULL and may be dereferenced at line 1460.</t>
+          <t>Array 'aps' of size 16 may use index value(s) 16..254</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_schema_search</t>
+          <t>nconf_ucclient_get_nodepath_vknum</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr">
@@ -16175,7 +16175,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr"/>
@@ -16185,19 +16185,19 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>1314346</v>
+        <v>1314430</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>1739</v>
+        <v>363</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'kvpair' returned from call to function 'nconf_memalloc_def' at line 1737 may be NULL and may be dereferenced at line 1739.</t>
+          <t>Array 'aps' of size 16 may use index value(s) 16..254</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_is_nodekey_sent</t>
+          <t>nconf_ucclient_get_nodepath_vkstr</t>
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr">
@@ -16258,10 +16258,10 @@
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>1314429</v>
+        <v>1314431</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>326</v>
+        <v>386</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_nodepath_vknum</t>
+          <t>nconf_ucclient_get_nodepath_vktype</t>
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr">
@@ -16321,29 +16321,29 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr"/>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_ucclient.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_xmlutils.cpp</t>
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>1314430</v>
+        <v>1314633</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>363</v>
+        <v>590</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Array 'aps' of size 16 may use index value(s) 16..254</t>
+          <t>Pointer 'retpath' returned from call to function 'nconf_memalloc_def' at line 587 may be NULL and may be dereferenced at line 590.</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_nodepath_vkstr</t>
+          <t>nconf_xmlutils_get_node_path</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr">
@@ -16394,29 +16394,29 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr"/>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_ucclient.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_xmlutils.cpp</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>1314431</v>
+        <v>1314634</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>386</v>
+        <v>638</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Array 'aps' of size 16 may use index value(s) 16..254</t>
+          <t>Pointer 'retpath' returned from call to function 'nconf_memalloc_def' at line 635 may be NULL and may be dereferenced at line 638.</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_nodepath_vktype</t>
+          <t>nconf_xmlutils_get_module_node_path</t>
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr">
@@ -16477,19 +16477,19 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>1314633</v>
+        <v>1314635</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>590</v>
+        <v>1128</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'retpath' returned from call to function 'nconf_memalloc_def' at line 587 may be NULL and may be dereferenced at line 590.</t>
+          <t>Pointer 'buf' returned from call to function 'nconf_memalloc_def' at line 1124 may be NULL and may be dereferenced at line 1128.</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>nconf_xmlutils_get_node_path</t>
+          <t>nconf_xmlutils_get_xpath_buf</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
@@ -16550,19 +16550,19 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>1314634</v>
+        <v>1314636</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>638</v>
+        <v>1307</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'retpath' returned from call to function 'nconf_memalloc_def' at line 635 may be NULL and may be dereferenced at line 638.</t>
+          <t>Pointer 'outbuf' returned from call to function 'nconf_memalloc_def' at line 1305 may be NULL and may be dereferenced at line 1307.</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>nconf_xmlutils_get_module_node_path</t>
+          <t>nconf_xmlutils_replaced_amp</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
@@ -16613,29 +16613,29 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr"/>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_xmlutils.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>1314635</v>
+        <v>1315139</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>1128</v>
+        <v>246</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'buf' returned from call to function 'nconf_memalloc_def' at line 1124 may be NULL and may be dereferenced at line 1128.</t>
+          <t>Pointer 'src' will be dereferenced at line 246 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>nconf_xmlutils_get_xpath_buf</t>
+          <t>strequal</t>
         </is>
       </c>
       <c r="H197" s="3" t="inlineStr">
@@ -16686,29 +16686,29 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr"/>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_xmlutils.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>1314636</v>
+        <v>1315140</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>1307</v>
+        <v>246</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'outbuf' returned from call to function 'nconf_memalloc_def' at line 1305 may be NULL and may be dereferenced at line 1307.</t>
+          <t>Pointer 'dst' will be dereferenced at line 246 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>nconf_xmlutils_replaced_amp</t>
+          <t>strequal</t>
         </is>
       </c>
       <c r="H198" s="3" t="inlineStr">
@@ -16769,19 +16769,19 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>1315139</v>
+        <v>1315141</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>246</v>
+        <v>7242</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'src' will be dereferenced at line 246 after having been checked for NULL.</t>
+          <t>Pointer 'root_page' will be dereferenced at line 7242 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>strequal</t>
+          <t>_destroy</t>
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr">
@@ -16842,19 +16842,19 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>1315140</v>
+        <v>1315142</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>246</v>
+        <v>7322</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'dst' will be dereferenced at line 246 after having been checked for NULL.</t>
+          <t>Pointer 'other_page' will be dereferenced at line 7322 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>strequal</t>
+          <t>_move</t>
         </is>
       </c>
       <c r="H200" s="3" t="inlineStr">
@@ -16915,19 +16915,19 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>1315141</v>
+        <v>1315143</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>7242</v>
+        <v>7328</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'root_page' will be dereferenced at line 7242 after having been checked for NULL.</t>
+          <t>Pointer 'doc_page' will be dereferenced at line 7328 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>_destroy</t>
+          <t>_move</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
@@ -16988,14 +16988,14 @@
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>1315142</v>
+        <v>1315144</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>7322</v>
+        <v>7333</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'other_page' will be dereferenced at line 7322 after having been checked for NULL.</t>
+          <t>Pointer 'doc_page' will be dereferenced at line 7333 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -17051,7 +17051,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr"/>
@@ -17061,19 +17061,19 @@
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>1315143</v>
+        <v>1316905</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>7328</v>
+        <v>328</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'doc_page' will be dereferenced at line 7328 after having been checked for NULL.</t>
+          <t>Pointer 'item' returned from call to function 'get_item' at line 326 may be NULL and will be dereferenced at line 328.</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>_move</t>
+          <t>find</t>
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr">
@@ -17124,7 +17124,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr"/>
@@ -17134,19 +17134,19 @@
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>1315144</v>
+        <v>1316906</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>7333</v>
+        <v>340</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'doc_page' will be dereferenced at line 7333 after having been checked for NULL.</t>
+          <t>Pointer 'item' returned from call to function 'get_item' at line 337 may be NULL and will be dereferenced at line 340.</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>_move</t>
+          <t>insert</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
@@ -17207,19 +17207,19 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>1316905</v>
+        <v>1316907</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>328</v>
+        <v>2406</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'item' returned from call to function 'get_item' at line 326 may be NULL and will be dereferenced at line 328.</t>
+          <t>Pointer 'dest.operator(char*)()' returned from call to function 'operator(char*)' at line 2406 may be NULL and will be dereferenced at line 2406.</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>find</t>
+          <t>strcpy_insitu</t>
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr">
@@ -17280,19 +17280,19 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>1316906</v>
+        <v>1316908</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>340</v>
+        <v>2407</v>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'item' returned from call to function 'get_item' at line 337 may be NULL and will be dereferenced at line 340.</t>
+          <t>Pointer 'dest.operator(char*)()' returned from call to function 'operator(char*)' at line 2407 may be NULL and will be dereferenced at line 2407.</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>insert</t>
+          <t>strcpy_insitu</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">
@@ -17353,19 +17353,19 @@
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>1316907</v>
+        <v>1316909</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>2406</v>
+        <v>4158</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'dest.operator(char*)()' returned from call to function 'operator(char*)' at line 2406 may be NULL and will be dereferenced at line 2406.</t>
+          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 4155 may be NULL and will be dereferenced at line 4158.</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>strcpy_insitu</t>
+          <t>node_output_start</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
@@ -17426,19 +17426,19 @@
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>1316908</v>
+        <v>1316910</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>2407</v>
+        <v>4220</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'dest.operator(char*)()' returned from call to function 'operator(char*)' at line 2407 may be NULL and will be dereferenced at line 2407.</t>
+          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 4217 may be NULL and will be dereferenced at line 4220.</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>strcpy_insitu</t>
+          <t>node_output_end</t>
         </is>
       </c>
       <c r="H208" s="3" t="inlineStr">
@@ -17499,19 +17499,19 @@
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>1316909</v>
+        <v>1316911</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>4158</v>
+        <v>4235</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 4155 may be NULL and will be dereferenced at line 4158.</t>
+          <t>Pointer '...?"":&amp;&amp;(node-&gt;value).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4235 may be NULL and will be dereferenced at line 4235.</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>node_output_start</t>
+          <t>node_output_simple</t>
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr">
@@ -17572,19 +17572,19 @@
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>1316910</v>
+        <v>1316912</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>4220</v>
+        <v>4239</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 4217 may be NULL and will be dereferenced at line 4220.</t>
+          <t>Pointer '...?"":&amp;&amp;(node-&gt;value).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4239 may be NULL and will be dereferenced at line 4239.</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>node_output_end</t>
+          <t>node_output_simple</t>
         </is>
       </c>
       <c r="H210" s="3" t="inlineStr">
@@ -17645,14 +17645,14 @@
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>1316911</v>
+        <v>1316913</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>4235</v>
+        <v>4244</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Pointer '...?"":&amp;&amp;(node-&gt;value).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4235 may be NULL and will be dereferenced at line 4235.</t>
+          <t>Pointer '...?default_name:&amp;&amp;(node-&gt;name).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4244 may be NULL and will be dereferenced at line 4244.</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -17718,14 +17718,14 @@
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>1316912</v>
+        <v>1316914</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>4239</v>
+        <v>4249</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Pointer '...?"":&amp;&amp;(node-&gt;value).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4239 may be NULL and will be dereferenced at line 4239.</t>
+          <t>Pointer '&amp;(node-&gt;value).operator(char*)()' returned from call to function 'operator(char*)' at line 4249 may be NULL and will be dereferenced at line 4249.</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -17791,14 +17791,14 @@
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>1316913</v>
+        <v>1316915</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>4244</v>
+        <v>4257</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Pointer '...?default_name:&amp;&amp;(node-&gt;name).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4244 may be NULL and will be dereferenced at line 4244.</t>
+          <t>Pointer '...?default_name:&amp;&amp;(node-&gt;name).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4257 may be NULL and will be dereferenced at line 4257.</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -17864,14 +17864,14 @@
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>1316914</v>
+        <v>1316916</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>4249</v>
+        <v>4269</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Pointer '&amp;(node-&gt;value).operator(char*)()' returned from call to function 'operator(char*)' at line 4249 may be NULL and will be dereferenced at line 4249.</t>
+          <t>Pointer '&amp;(node-&gt;value).operator(char*)()' returned from call to function 'operator(char*)' at line 4269 may be NULL and will be dereferenced at line 4269.</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -17937,19 +17937,19 @@
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>1316915</v>
+        <v>1316917</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>4257</v>
+        <v>4357</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Pointer '...?default_name:&amp;&amp;(node-&gt;name).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4257 may be NULL and will be dereferenced at line 4257.</t>
+          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4354 may be NULL and will be dereferenced at line 4357.</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>node_output_simple</t>
+          <t>node_output</t>
         </is>
       </c>
       <c r="H215" s="3" t="inlineStr">
@@ -18010,19 +18010,19 @@
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>1316916</v>
+        <v>1316918</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>4269</v>
+        <v>8495</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Pointer '&amp;(node-&gt;value).operator(char*)()' returned from call to function 'operator(char*)' at line 4269 may be NULL and will be dereferenced at line 4269.</t>
+          <t>Pointer 'exponent_string' returned from call to function 'strchr' at line 8492 may be NULL and will be dereferenced at line 8495.</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>node_output_simple</t>
+          <t>convert_number_to_mantissa_exponent</t>
         </is>
       </c>
       <c r="H216" s="3" t="inlineStr">
@@ -18083,19 +18083,19 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>1316917</v>
+        <v>1316919</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>4357</v>
+        <v>10090</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4354 may be NULL and will be dereferenced at line 4357.</t>
+          <t>Pointer '&amp;(n-&gt;name).operator(char*)()' returned from call to function 'operator(char*)' at line 10090 may be NULL and will be dereferenced at line 10090.</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>node_output</t>
+          <t>step_push</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
@@ -18156,19 +18156,19 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>1316918</v>
+        <v>1316920</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>8495</v>
+        <v>10126</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'exponent_string' returned from call to function 'strchr' at line 8492 may be NULL and will be dereferenced at line 8495.</t>
+          <t>Pointer '&amp;(n-&gt;name).operator(char*)()' returned from call to function 'operator(char*)' at line 10126 may be NULL and will be dereferenced at line 10126.</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>convert_number_to_mantissa_exponent</t>
+          <t>step_push</t>
         </is>
       </c>
       <c r="H218" s="3" t="inlineStr">
@@ -18229,19 +18229,19 @@
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>1316919</v>
+        <v>1316921</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>10090</v>
+        <v>12780</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Pointer '&amp;(n-&gt;name).operator(char*)()' returned from call to function 'operator(char*)' at line 10090 may be NULL and will be dereferenced at line 10090.</t>
+          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12780 may be NULL and will be dereferenced at line 12780.</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>step_push</t>
+          <t>_find</t>
         </is>
       </c>
       <c r="H219" s="3" t="inlineStr">
@@ -18302,19 +18302,19 @@
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>1316920</v>
+        <v>1316922</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>10126</v>
+        <v>12832</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Pointer '&amp;(n-&gt;name).operator(char*)()' returned from call to function 'operator(char*)' at line 10126 may be NULL and will be dereferenced at line 10126.</t>
+          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12832 may be NULL and will be dereferenced at line 12832.</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>step_push</t>
+          <t>add</t>
         </is>
       </c>
       <c r="H220" s="3" t="inlineStr">
@@ -18365,7 +18365,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr"/>
@@ -18375,19 +18375,19 @@
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>1316921</v>
+        <v>1317952</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>12780</v>
+        <v>3441</v>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12780 may be NULL and will be dereferenced at line 12780.</t>
+          <t>Pointer 'cursor' returned from call to function 'parse_question' at line 3437 may be NULL and may be dereferenced at line 3441.</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>_find</t>
+          <t>parse_tree</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr">
@@ -18438,7 +18438,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr"/>
@@ -18448,19 +18448,19 @@
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>1316922</v>
+        <v>1317953</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>12832</v>
+        <v>4298</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12832 may be NULL and will be dereferenced at line 12832.</t>
+          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4350 may be NULL and may be dereferenced at line 4298.</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>node_output</t>
         </is>
       </c>
       <c r="H222" s="3" t="inlineStr">
@@ -18521,19 +18521,19 @@
         </is>
       </c>
       <c r="D223" s="3" t="n">
-        <v>1317952</v>
+        <v>1317954</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>3441</v>
+        <v>4298</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'cursor' returned from call to function 'parse_question' at line 3437 may be NULL and may be dereferenced at line 3441.</t>
+          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4333 may be NULL and may be dereferenced at line 4298.</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>parse_tree</t>
+          <t>node_output</t>
         </is>
       </c>
       <c r="H223" s="3" t="inlineStr">
@@ -18594,14 +18594,14 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>1317953</v>
+        <v>1317955</v>
       </c>
       <c r="E224" s="3" t="n">
         <v>4298</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4350 may be NULL and may be dereferenced at line 4298.</t>
+          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4322 may be NULL and may be dereferenced at line 4298.</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -18667,19 +18667,19 @@
         </is>
       </c>
       <c r="D225" s="3" t="n">
-        <v>1317954</v>
+        <v>1317956</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>4298</v>
+        <v>10050</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4333 may be NULL and may be dereferenced at line 4298.</t>
+          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 10045 may be NULL and may be dereferenced at line 10050.</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>node_output</t>
+          <t>step_push</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
@@ -18740,19 +18740,19 @@
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>1317955</v>
+        <v>1317957</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>4298</v>
+        <v>10059</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4322 may be NULL and may be dereferenced at line 4298.</t>
+          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 10045 may be NULL and may be dereferenced at line 10059.</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>node_output</t>
+          <t>step_push</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
@@ -18813,14 +18813,14 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>1317956</v>
+        <v>1317958</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>10050</v>
+        <v>10067</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 10045 may be NULL and may be dereferenced at line 10050.</t>
+          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 10045 may be NULL and may be dereferenced at line 10067.</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -18876,7 +18876,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr"/>
@@ -18886,19 +18886,19 @@
         </is>
       </c>
       <c r="D228" s="3" t="n">
-        <v>1317957</v>
+        <v>1317963</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>10059</v>
+        <v>4031</v>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 10045 may be NULL and may be dereferenced at line 10059.</t>
+          <t>Array 'writer.buffer' of size 204 may use index value(s) 4..204</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>step_push</t>
+          <t>text_output_cdata</t>
         </is>
       </c>
       <c r="H228" s="3" t="inlineStr">
@@ -18949,7 +18949,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr"/>
@@ -18959,19 +18959,19 @@
         </is>
       </c>
       <c r="D229" s="3" t="n">
-        <v>1317958</v>
+        <v>1317964</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>10067</v>
+        <v>4089</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 10045 may be NULL and may be dereferenced at line 10067.</t>
+          <t>Array 'writer.buffer' of size 204 may use index value(s) 0..204</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>step_push</t>
+          <t>node_output_comment</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
@@ -19022,7 +19022,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>NPD.CHECK.CALL.MIGHT</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr"/>
@@ -19032,19 +19032,19 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>1317963</v>
+        <v>1317965</v>
       </c>
       <c r="E230" s="3" t="n">
-        <v>4031</v>
+        <v>4765</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Array 'writer.buffer' of size 204 may use index value(s) 4..204</t>
+          <t>Pointer 'contents' checked for NULL at line 4752 may be passed to function and may be dereferenced there by passing argument 4 to function 'convert_buffer' at line 4765.</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>text_output_cdata</t>
+          <t>load_buffer_impl</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
@@ -19095,7 +19095,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>ABV.ITERATOR</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr"/>
@@ -19105,19 +19105,19 @@
         </is>
       </c>
       <c r="D231" s="3" t="n">
-        <v>1317964</v>
+        <v>1317978</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>4089</v>
+        <v>7242</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Array 'writer.buffer' of size 204 may use index value(s) 0..204</t>
+          <t>Buffer overflow, pointer 'root_page' is used at line 7242 when its value may exceed array 'this-&gt;_memory' bounds. Pointer 'root_page' is checked against array bounds (reinterpret_cast&lt;char* &gt; (root_page) &lt;_memory+sizeof(_memory)) at line 7240.</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>node_output_comment</t>
+          <t>_destroy</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
@@ -19168,7 +19168,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.CALL.MIGHT</t>
+          <t>RH.LEAK</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr"/>
@@ -19178,19 +19178,19 @@
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>1317965</v>
+        <v>1317979</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>4765</v>
+        <v>7410</v>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'contents' checked for NULL at line 4752 may be passed to function and may be dereferenced there by passing argument 4 to function 'convert_buffer' at line 4765.</t>
+          <t>Resource acquired to 'impl::open_file(path_, "rb" )' at line 7408 may be lost here.</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>load_buffer_impl</t>
+          <t>load_file</t>
         </is>
       </c>
       <c r="H232" s="3" t="inlineStr">
@@ -19200,11 +19200,11 @@
       </c>
       <c r="I232" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="J232" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>ABV.ITERATOR</t>
+          <t>RH.LEAK</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr"/>
@@ -19251,19 +19251,19 @@
         </is>
       </c>
       <c r="D233" s="3" t="n">
-        <v>1317978</v>
+        <v>1317980</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>7242</v>
+        <v>7420</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Buffer overflow, pointer 'root_page' is used at line 7242 when its value may exceed array 'this-&gt;_memory' bounds. Pointer 'root_page' is checked against array bounds (reinterpret_cast&lt;char* &gt; (root_page) &lt;_memory+sizeof(_memory)) at line 7240.</t>
+          <t>Resource acquired to 'impl::open_file_wide(path_, L"rb" )' at line 7418 may be lost here.</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>_destroy</t>
+          <t>load_file</t>
         </is>
       </c>
       <c r="H233" s="3" t="inlineStr">
@@ -19273,11 +19273,11 @@
       </c>
       <c r="I233" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="J233" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
@@ -19324,19 +19324,19 @@
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>1317979</v>
+        <v>1317981</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>7410</v>
+        <v>7493</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file(path_, "rb" )' at line 7408 may be lost here.</t>
+          <t>Resource acquired to 'impl::open_file(path_,  (flags&amp;format_save_file_text)?"w" :"wb" )' at line 7491 may be lost here.</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>load_file</t>
+          <t>save_file</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
@@ -19397,19 +19397,19 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>1317980</v>
+        <v>1317982</v>
       </c>
       <c r="E235" s="3" t="n">
-        <v>7420</v>
+        <v>7493</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file_wide(path_, L"rb" )' at line 7418 may be lost here.</t>
+          <t>Resource acquired to 'impl::open_file(path_,  (flags&amp;format_save_file_text)?"w" :"wb" )' at line 7491 may be lost here.</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>load_file</t>
+          <t>save_file</t>
         </is>
       </c>
       <c r="H235" s="3" t="inlineStr">
@@ -19470,14 +19470,14 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>1317981</v>
+        <v>1317983</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>7493</v>
+        <v>7501</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file(path_,  (flags&amp;format_save_file_text)?"w" :"wb" )' at line 7491 may be lost here.</t>
+          <t>Resource acquired to 'impl::open_file_wide(path_,  (flags&amp;format_save_file_text)?L"w" :L"wb" )' at line 7499 may be lost here.</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -19543,14 +19543,14 @@
         </is>
       </c>
       <c r="D237" s="3" t="n">
-        <v>1317982</v>
+        <v>1317984</v>
       </c>
       <c r="E237" s="3" t="n">
-        <v>7493</v>
+        <v>7501</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file(path_,  (flags&amp;format_save_file_text)?"w" :"wb" )' at line 7491 may be lost here.</t>
+          <t>Resource acquired to 'impl::open_file_wide(path_,  (flags&amp;format_save_file_text)?L"w" :L"wb" )' at line 7499 may be lost here.</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -19606,7 +19606,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>RH.LEAK</t>
+          <t>SV.TAINTED.LOOP_BOUND</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr"/>
@@ -19616,19 +19616,19 @@
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>1317983</v>
+        <v>1317993</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>7501</v>
+        <v>8546</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file_wide(path_,  (flags&amp;format_save_file_text)?L"w" :L"wb" )' at line 7499 may be lost here.</t>
+          <t>Unvalidated integer value 'exponent' is received from 'convert_number_to_mantissa_exponent' at line 8526 and can be used in a loop condition at line 8546.</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>save_file</t>
+          <t>convert_number_to_string</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
@@ -19679,29 +19679,29 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>RH.LEAK</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr"/>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/hal/uc_hwal.c</t>
         </is>
       </c>
       <c r="D239" s="3" t="n">
-        <v>1317984</v>
+        <v>1319695</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>7501</v>
+        <v>825</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file_wide(path_,  (flags&amp;format_save_file_text)?L"w" :L"wb" )' at line 7499 may be lost here.</t>
+          <t>Pointer 'clst' returned from call to function 'ub_esarray_init' at line 817 may be NULL and may be dereferenced at line 825.</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>save_file</t>
+          <t>tas_hw_action</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
@@ -19711,11 +19711,11 @@
       </c>
       <c r="I239" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J239" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
@@ -19752,29 +19752,29 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>SV.TAINTED.LOOP_BOUND</t>
+          <t>NNTS.MIGHT</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr"/>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/hal/uc_hwal.c</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>1317993</v>
+        <v>1319699</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>8546</v>
+        <v>854</v>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Unvalidated integer value 'exponent' is received from 'convert_number_to_mantissa_exponent' at line 8526 and can be used in a loop condition at line 8546.</t>
+          <t>Buffer overflow of 'nevent.ifname' due to non null terminated string 'nevent.ifname'</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>convert_number_to_string</t>
+          <t>preempt_hw_action</t>
         </is>
       </c>
       <c r="H240" s="3" t="inlineStr">
@@ -19784,11 +19784,11 @@
       </c>
       <c r="I240" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J240" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
@@ -19825,29 +19825,29 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr"/>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_lldp/tlv_data.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>1318982</v>
+        <v>1319877</v>
       </c>
       <c r="E241" s="3" t="n">
-        <v>626</v>
+        <v>288</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Array 'unknown_tlv-&gt;tlv_info' of size 64 may use index value(s) 64..255</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 286 may be NULL and may be dereferenced at line 288.</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>collect_other_tlv_infos</t>
+          <t>find_semname_in_putnoticelist</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
@@ -19904,23 +19904,23 @@
       <c r="B242" s="3" t="inlineStr"/>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/hal/uc_hwal.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>1319695</v>
+        <v>1319878</v>
       </c>
       <c r="E242" s="3" t="n">
-        <v>769</v>
+        <v>411</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'clst' returned from call to function 'ub_esarray_init' at line 761 may be NULL and may be dereferenced at line 769.</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 409 may be NULL and may be dereferenced at line 411.</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>tas_hw_action</t>
+          <t>incremant_actcounter</t>
         </is>
       </c>
       <c r="H242" s="3" t="inlineStr">
@@ -19971,29 +19971,29 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>NNTS.MIGHT</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr"/>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/hal/uc_hwal.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>1319699</v>
+        <v>1319879</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>798</v>
+        <v>440</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Buffer overflow of 'nevent.ifname' due to non null terminated string 'nevent.ifname'</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 436 may be NULL and may be dereferenced at line 440.</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>preempt_hw_action</t>
+          <t>proc_refactcounter</t>
         </is>
       </c>
       <c r="H243" s="3" t="inlineStr">
@@ -20054,19 +20054,19 @@
         </is>
       </c>
       <c r="D244" s="3" t="n">
-        <v>1319877</v>
+        <v>1319880</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>280</v>
+        <v>470</v>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 278 may be NULL and may be dereferenced at line 280.</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 468 may be NULL and may be dereferenced at line 470.</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>find_semname_in_putnoticelist</t>
+          <t>nu_clear_refcounter</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
@@ -20127,19 +20127,19 @@
         </is>
       </c>
       <c r="D245" s="3" t="n">
-        <v>1319878</v>
+        <v>1319881</v>
       </c>
       <c r="E245" s="3" t="n">
-        <v>396</v>
+        <v>486</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 394 may be NULL and may be dereferenced at line 396.</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 484 may be NULL and may be dereferenced at line 486.</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>incremant_actcounter</t>
+          <t>nu_increment_refcounter</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
@@ -20190,29 +20190,29 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr"/>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_access.c</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>1319879</v>
+        <v>1321342</v>
       </c>
       <c r="E246" s="3" t="n">
-        <v>425</v>
+        <v>1209</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 421 may be NULL and may be dereferenced at line 425.</t>
+          <t>Array 'pstr' of size 64 may use index value(s) 64..UINT_MAX-1</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>proc_refactcounter</t>
+          <t>one_combine</t>
         </is>
       </c>
       <c r="H246" s="3" t="inlineStr">
@@ -20263,29 +20263,29 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr"/>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_access.c</t>
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>1319880</v>
+        <v>1321343</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>454</v>
+        <v>1225</v>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 452 may be NULL and may be dereferenced at line 454.</t>
+          <t>Array 'pstr' of size 64 may use index value(s) 64..UINT_MAX-1</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>nu_clear_refcounter</t>
+          <t>one_combine</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
@@ -20336,29 +20336,29 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr"/>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>1319881</v>
+        <v>1321804</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>469</v>
+        <v>200</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 467 may be NULL and may be dereferenced at line 469.</t>
+          <t>Array 'apsd' of size 21 may use index value(s) 21..259</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>nu_increment_refcounter</t>
+          <t>proc_get_keyv</t>
         </is>
       </c>
       <c r="H248" s="3" t="inlineStr">
@@ -20415,23 +20415,23 @@
       <c r="B249" s="3" t="inlineStr"/>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_access.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
         </is>
       </c>
       <c r="D249" s="3" t="n">
-        <v>1321342</v>
+        <v>1321805</v>
       </c>
       <c r="E249" s="3" t="n">
-        <v>1228</v>
+        <v>249</v>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Array 'pstr' of size 64 may use index value(s) 64..UINT_MAX-1</t>
+          <t>Array 'kpi' of size 16 may use index value(s) 16..254</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>one_combine</t>
+          <t>proc_get_keyv</t>
         </is>
       </c>
       <c r="H249" s="3" t="inlineStr">
@@ -20488,23 +20488,23 @@
       <c r="B250" s="3" t="inlineStr"/>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_access.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>1321343</v>
+        <v>1321806</v>
       </c>
       <c r="E250" s="3" t="n">
-        <v>1244</v>
+        <v>365</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Array 'pstr' of size 64 may use index value(s) 64..UINT_MAX-1</t>
+          <t>Array 'kpi' of size 16 may use index value(s) 16..254</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>one_combine</t>
+          <t>proc_set_onenode</t>
         </is>
       </c>
       <c r="H250" s="3" t="inlineStr">
@@ -20565,19 +20565,19 @@
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>1321804</v>
+        <v>1321807</v>
       </c>
       <c r="E251" s="3" t="n">
-        <v>195</v>
+        <v>548</v>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Array 'apsd' of size 21 may use index value(s) 21..259</t>
+          <t>Array 'apsd' of size 21 may use index value(s) 21..257</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>proc_get_keyv</t>
+          <t>get_value_type</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr">
@@ -20638,19 +20638,19 @@
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>1321805</v>
+        <v>1321808</v>
       </c>
       <c r="E252" s="3" t="n">
-        <v>235</v>
+        <v>1051</v>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Array 'kpi' of size 16 may use index value(s) 16..254</t>
+          <t>Array 'linebuf' of size 513 may use index value(s) -1</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>proc_get_keyv</t>
+          <t>yang_db_runtime_readfile</t>
         </is>
       </c>
       <c r="H252" s="3" t="inlineStr">
@@ -20701,29 +20701,33 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="inlineStr"/>
+          <t>NPD.FUNC.MUST</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>Waiver id: PSDKRA_SA_DR_003</t>
+        </is>
+      </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>1321806</v>
+        <v>1343713</v>
       </c>
       <c r="E253" s="3" t="n">
-        <v>300</v>
+        <v>2972</v>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Array 'kpi' of size 16 may use index value(s) 16..254</t>
+          <t>Pointer 'hClient' returned from call to function 'CpswProxyServer_getClient' at line 2958 may be NULL and will be dereferenced at line 2972.</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>proc_set_onenode</t>
+          <t>CpswProxyServer_clientRequestHandler</t>
         </is>
       </c>
       <c r="H253" s="3" t="inlineStr">
@@ -20746,7 +20750,7 @@
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
@@ -20765,7 +20769,7 @@
       <c r="R253" s="3" t="inlineStr"/>
       <c r="S253" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T253" s="3" t="inlineStr"/>
@@ -20774,29 +20778,33 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="inlineStr"/>
+          <t>NPD.FUNC.MUST</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>Waiver id: PSDKRA_SA_DR_003</t>
+        </is>
+      </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>1321807</v>
+        <v>1343714</v>
       </c>
       <c r="E254" s="3" t="n">
-        <v>444</v>
+        <v>3614</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Array 'apsd' of size 21 may use index value(s) 21..257</t>
+          <t>Pointer 'hClient' returned from call to function 'CpswProxyServer_getClient' at line 3611 may be NULL and will be dereferenced at line 3614.</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>get_value_type</t>
+          <t>CpswProxyServer_clientRequestHandler</t>
         </is>
       </c>
       <c r="H254" s="3" t="inlineStr">
@@ -20819,7 +20827,7 @@
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
@@ -20838,7 +20846,7 @@
       <c r="R254" s="3" t="inlineStr"/>
       <c r="S254" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T254" s="3" t="inlineStr"/>
@@ -20850,26 +20858,30 @@
           <t>ABV.GENERAL</t>
         </is>
       </c>
-      <c r="B255" s="3" t="inlineStr"/>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>waiver id: PSDKRA_SA_DR_001</t>
+        </is>
+      </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D255" s="3" t="n">
-        <v>1321808</v>
+        <v>1343722</v>
       </c>
       <c r="E255" s="3" t="n">
-        <v>806</v>
+        <v>2705</v>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Array 'linebuf' of size 513 may use index value(s) -1</t>
+          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>yang_db_runtime_readfile</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr">
@@ -20892,7 +20904,7 @@
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
@@ -20911,7 +20923,7 @@
       <c r="R255" s="3" t="inlineStr"/>
       <c r="S255" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T255" s="3" t="inlineStr"/>
@@ -20923,26 +20935,30 @@
           <t>ABV.GENERAL</t>
         </is>
       </c>
-      <c r="B256" s="3" t="inlineStr"/>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>waiver id: PSDKRA_SA_DR_001</t>
+        </is>
+      </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
-        <v>1321809</v>
+        <v>1343723</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>1057</v>
+        <v>2706</v>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Array 'raps' of size 3 may use index value(s) 3..15</t>
+          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>vkey_on_node</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H256" s="3" t="inlineStr">
@@ -20965,7 +20981,7 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
@@ -20984,7 +21000,7 @@
       <c r="R256" s="3" t="inlineStr"/>
       <c r="S256" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T256" s="3" t="inlineStr"/>
@@ -20993,12 +21009,12 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Waiver id: PSDKRA_SA_DR_003</t>
+          <t>waiver id: PSDKRA_SA_DR_001</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
@@ -21007,19 +21023,19 @@
         </is>
       </c>
       <c r="D257" s="3" t="n">
-        <v>1343713</v>
+        <v>1343724</v>
       </c>
       <c r="E257" s="3" t="n">
-        <v>2917</v>
+        <v>2707</v>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'hClient' returned from call to function 'CpswProxyServer_getClient' at line 2903 may be NULL and will be dereferenced at line 2917.</t>
+          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_clientRequestHandler</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
@@ -21070,12 +21086,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Waiver id: PSDKRA_SA_DR_003</t>
+          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -21084,19 +21100,19 @@
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>1343714</v>
+        <v>1343725</v>
       </c>
       <c r="E258" s="3" t="n">
-        <v>3559</v>
+        <v>2708</v>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'hClient' returned from call to function 'CpswProxyServer_getClient' at line 3556 may be NULL and will be dereferenced at line 3559.</t>
+          <t>Array 'g_CpswProxyServerAutosarRpmsgBuf' of size 2 may use index value(s) 0..5</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_clientRequestHandler</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
@@ -21147,12 +21163,12 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>waiver id: PSDKRA_SA_DR_001</t>
+          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
@@ -21161,14 +21177,14 @@
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>1343722</v>
+        <v>1343726</v>
       </c>
       <c r="E259" s="3" t="n">
-        <v>2712</v>
+        <v>2708</v>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
+          <t>Array 'hServer-&gt;ethDrvObj' of size 2 may use index value(s) 0..5</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -21224,12 +21240,12 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>waiver id: PSDKRA_SA_DR_001</t>
+          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -21238,14 +21254,14 @@
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>1343723</v>
+        <v>1343727</v>
       </c>
       <c r="E260" s="3" t="n">
-        <v>2713</v>
+        <v>2708</v>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
+          <t>Array 'gCpswProxyServer_autosarEthDriverTaskStackBuf' of size 2 may use index value(s) 0..5</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -21301,12 +21317,12 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>waiver id: PSDKRA_SA_DR_001</t>
+          <t>waiver id: PSDKRA_SA_DR_005</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
@@ -21315,19 +21331,19 @@
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>1343724</v>
+        <v>1343728</v>
       </c>
       <c r="E261" s="3" t="n">
-        <v>2714</v>
+        <v>2972</v>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
+          <t>Pointer 'hClient' will be dereferenced at line 2972 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>CpswProxyServer_clientRequestHandler</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
@@ -21378,12 +21394,12 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
+          <t>waiver id: PSDKRA_SA_DR_005</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -21392,19 +21408,19 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>1343725</v>
+        <v>1343729</v>
       </c>
       <c r="E262" s="3" t="n">
-        <v>2715</v>
+        <v>3614</v>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Array 'g_CpswProxyServerAutosarRpmsgBuf' of size 2 may use index value(s) 0..5</t>
+          <t>Pointer 'hClient' will be dereferenced at line 3614 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>CpswProxyServer_clientRequestHandler</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
@@ -21455,33 +21471,29 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
-        </is>
-      </c>
+          <t>UNINIT.STACK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr"/>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/lwipif/src/lwip2enet.c</t>
         </is>
       </c>
       <c r="D263" s="3" t="n">
-        <v>1343726</v>
+        <v>1343777</v>
       </c>
       <c r="E263" s="3" t="n">
-        <v>2715</v>
+        <v>1361</v>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Array 'hServer-&gt;ethDrvObj' of size 2 may use index value(s) 0..5</t>
+          <t>'errPkt' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>Lwip2Enet_prepRxPktQ</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
@@ -21504,7 +21516,7 @@
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
@@ -21523,7 +21535,7 @@
       <c r="R263" s="3" t="inlineStr"/>
       <c r="S263" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T263" s="3" t="inlineStr"/>
@@ -21535,30 +21547,26 @@
           <t>ABV.STACK</t>
         </is>
       </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
-        </is>
-      </c>
+      <c r="B264" s="3" t="inlineStr"/>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/src/per/cpsw_intervlan.c</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
-        <v>1343727</v>
+        <v>1344826</v>
       </c>
       <c r="E264" s="3" t="n">
-        <v>2715</v>
+        <v>172</v>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Array 'gCpswProxyServer_autosarEthDriverTaskStackBuf' of size 2 may use index value(s) 0..5</t>
+          <t>Array 'inArgs-&gt;egressCfg' of size 8 may use index value(s) 0..MAX</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>Cpsw_ioctlInterVlan</t>
         </is>
       </c>
       <c r="H264" s="3" t="inlineStr">
@@ -21581,7 +21589,7 @@
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
@@ -21600,7 +21608,7 @@
       <c r="R264" s="3" t="inlineStr"/>
       <c r="S264" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T264" s="3" t="inlineStr"/>
@@ -21609,33 +21617,33 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>waiver id: PSDKRA_SA_DR_005</t>
+          <t>waiver id: PSDKRA_SA_DR_008</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_api.c</t>
         </is>
       </c>
       <c r="D265" s="3" t="n">
-        <v>1343728</v>
+        <v>1344879</v>
       </c>
       <c r="E265" s="3" t="n">
-        <v>2917</v>
+        <v>1382</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'hClient' will be dereferenced at line 2917 after having been checked for NULL.</t>
+          <t>Array 'gMcmObj' of size 8 may use index value(s) 0..8</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_clientRequestHandler</t>
+          <t>EthFw_initMcm</t>
         </is>
       </c>
       <c r="H265" s="3" t="inlineStr">
@@ -21686,33 +21694,33 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>INFINITE_LOOP.LOCAL</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>waiver id: PSDKRA_SA_DR_005</t>
+          <t>waiver id: PSDKRA_SA_DR_006</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/app_remoteswitchcfg_server/main.c</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>1343729</v>
+        <v>1344937</v>
       </c>
       <c r="E266" s="3" t="n">
-        <v>3559</v>
+        <v>1944</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'hClient' will be dereferenced at line 3559 after having been checked for NULL.</t>
+          <t>Infinite loop</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_clientRequestHandler</t>
+          <t>EthApp_traceBufFlush</t>
         </is>
       </c>
       <c r="H266" s="3" t="inlineStr">
@@ -21722,11 +21730,11 @@
       </c>
       <c r="I266" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="J266" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
@@ -21763,29 +21771,29 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr"/>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/lwipif/src/lwip2enet.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns.c</t>
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>1343773</v>
+        <v>1344946</v>
       </c>
       <c r="E267" s="3" t="n">
-        <v>311</v>
+        <v>2580</v>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Array 'rxInfo' of size 2 may use index value(s) 2</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>Lwip2Enet_open</t>
+          <t>mdns_resp_del_service</t>
         </is>
       </c>
       <c r="H267" s="3" t="inlineStr">
@@ -21836,29 +21844,29 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>UNINIT.STACK.MIGHT</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr"/>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/lwipif/src/lwip2enet.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>1343777</v>
+        <v>1344947</v>
       </c>
       <c r="E268" s="3" t="n">
-        <v>1361</v>
+        <v>373</v>
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>'errPkt' might be used uninitialized in this function.</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>Lwip2Enet_prepRxPktQ</t>
+          <t>mdns_build_reverse_v4_domain</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
@@ -21909,29 +21917,29 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr"/>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/src/per/cpsw_intervlan.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D269" s="3" t="n">
-        <v>1344826</v>
+        <v>1344948</v>
       </c>
       <c r="E269" s="3" t="n">
-        <v>172</v>
+        <v>430</v>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Array 'inArgs-&gt;egressCfg' of size 8 may use index value(s) 0..MAX</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>Cpsw_ioctlInterVlan</t>
+          <t>mdns_add_dotlocal</t>
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr">
@@ -21982,33 +21990,29 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>waiver id: PSDKRA_SA_DR_008</t>
-        </is>
-      </c>
+          <t>FUNCRET.GEN</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr"/>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_api.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
-        <v>1344879</v>
+        <v>1344949</v>
       </c>
       <c r="E270" s="3" t="n">
-        <v>1372</v>
+        <v>448</v>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Array 'gMcmObj' of size 8 may use index value(s) 0..8</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>EthFw_initMcm</t>
+          <t>mdns_build_host_domain</t>
         </is>
       </c>
       <c r="H270" s="3" t="inlineStr">
@@ -22031,7 +22035,7 @@
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
@@ -22050,7 +22054,7 @@
       <c r="R270" s="3" t="inlineStr"/>
       <c r="S270" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T270" s="3" t="inlineStr"/>
@@ -22059,29 +22063,29 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr"/>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/ipc/src/ipc_api.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>1344913</v>
+        <v>1344950</v>
       </c>
       <c r="E271" s="3" t="n">
-        <v>754</v>
+        <v>468</v>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Array 'gRPMessageWaiterElemPool' of size 256 may use index value(s) 256</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>RPMessage_getFreeTaskWaiter</t>
+          <t>mdns_build_dnssd_domain</t>
         </is>
       </c>
       <c r="H271" s="3" t="inlineStr">
@@ -22132,29 +22136,29 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr"/>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/ipc/src/ipc_api.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
-        <v>1344914</v>
+        <v>1344951</v>
       </c>
       <c r="E272" s="3" t="n">
-        <v>770</v>
+        <v>494</v>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Array 'gRPMessageWaiterElemPool' of size 256 may use index value(s) 256</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>RPMessage_lookupTaskWaiter</t>
+          <t>mdns_build_service_domain</t>
         </is>
       </c>
       <c r="H272" s="3" t="inlineStr">
@@ -22205,33 +22209,29 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>INFINITE_LOOP.LOCAL</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
-        <is>
-          <t>waiver id: PSDKRA_SA_DR_006</t>
-        </is>
-      </c>
+          <t>FUNCRET.GEN</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr"/>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/app_remoteswitchcfg_server/main.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D273" s="3" t="n">
-        <v>1344937</v>
+        <v>1344952</v>
       </c>
       <c r="E273" s="3" t="n">
-        <v>1774</v>
+        <v>520</v>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Infinite loop</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>EthApp_traceBufFlush</t>
+          <t>mdns_build_request_domain</t>
         </is>
       </c>
       <c r="H273" s="3" t="inlineStr">
@@ -22241,11 +22241,11 @@
       </c>
       <c r="I273" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J273" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K273" s="3" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="L273" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
@@ -22273,7 +22273,7 @@
       <c r="R273" s="3" t="inlineStr"/>
       <c r="S273" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T273" s="3" t="inlineStr"/>
@@ -22288,14 +22288,14 @@
       <c r="B274" s="3" t="inlineStr"/>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/memp.c</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
-        <v>1344946</v>
+        <v>1344953</v>
       </c>
       <c r="E274" s="3" t="n">
-        <v>2580</v>
+        <v>356</v>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>mdns_resp_del_service</t>
+          <t>memp_malloc</t>
         </is>
       </c>
       <c r="H274" s="3" t="inlineStr">
@@ -22361,14 +22361,14 @@
       <c r="B275" s="3" t="inlineStr"/>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/pbuf.c</t>
         </is>
       </c>
       <c r="D275" s="3" t="n">
-        <v>1344947</v>
+        <v>1344959</v>
       </c>
       <c r="E275" s="3" t="n">
-        <v>373</v>
+        <v>616</v>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>mdns_build_reverse_v4_domain</t>
+          <t>pbuf_remove_header</t>
         </is>
       </c>
       <c r="H275" s="3" t="inlineStr">
@@ -22434,14 +22434,14 @@
       <c r="B276" s="3" t="inlineStr"/>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/pbuf.c</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>1344948</v>
+        <v>1344960</v>
       </c>
       <c r="E276" s="3" t="n">
-        <v>430</v>
+        <v>1043</v>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>mdns_add_dotlocal</t>
+          <t>pbuf_copy_partial_pbuf</t>
         </is>
       </c>
       <c r="H276" s="3" t="inlineStr">
@@ -22501,29 +22501,29 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr"/>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D277" s="3" t="n">
-        <v>1344949</v>
+        <v>1344966</v>
       </c>
       <c r="E277" s="3" t="n">
-        <v>448</v>
+        <v>234</v>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Pointer 's' will be dereferenced at line 234 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>mdns_build_host_domain</t>
+          <t>strlength</t>
         </is>
       </c>
       <c r="H277" s="3" t="inlineStr">
@@ -22574,29 +22574,29 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr"/>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
-        <v>1344950</v>
+        <v>1344967</v>
       </c>
       <c r="E278" s="3" t="n">
-        <v>468</v>
+        <v>246</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Pointer 'src' will be dereferenced at line 246 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>mdns_build_dnssd_domain</t>
+          <t>strequal</t>
         </is>
       </c>
       <c r="H278" s="3" t="inlineStr">
@@ -22647,29 +22647,29 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr"/>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D279" s="3" t="n">
-        <v>1344951</v>
+        <v>1344968</v>
       </c>
       <c r="E279" s="3" t="n">
-        <v>494</v>
+        <v>246</v>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Pointer 'dst' will be dereferenced at line 246 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>mdns_build_service_domain</t>
+          <t>strequal</t>
         </is>
       </c>
       <c r="H279" s="3" t="inlineStr">
@@ -22720,29 +22720,29 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr"/>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
-        <v>1344952</v>
+        <v>1344969</v>
       </c>
       <c r="E280" s="3" t="n">
-        <v>520</v>
+        <v>269</v>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Pointer 'end' will be dereferenced at line 269 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>mdns_build_request_domain</t>
+          <t>strlength_wide</t>
         </is>
       </c>
       <c r="H280" s="3" t="inlineStr">
@@ -22793,29 +22793,29 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr"/>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/memp.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D281" s="3" t="n">
-        <v>1344953</v>
+        <v>1344970</v>
       </c>
       <c r="E281" s="3" t="n">
-        <v>356</v>
+        <v>7953</v>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Pointer 'cur' will be dereferenced at line 7953 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>memp_malloc</t>
+          <t>release</t>
         </is>
       </c>
       <c r="H281" s="3" t="inlineStr">
@@ -22866,29 +22866,29 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr"/>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/pbuf.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
-        <v>1344959</v>
+        <v>1344971</v>
       </c>
       <c r="E282" s="3" t="n">
-        <v>616</v>
+        <v>11398</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Pointer 'this-&gt;_alloc-&gt;_error' will be dereferenced at line 11398 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>pbuf_remove_header</t>
+          <t>error_oom</t>
         </is>
       </c>
       <c r="H282" s="3" t="inlineStr">
@@ -22939,29 +22939,29 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr"/>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/pbuf.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D283" s="3" t="n">
-        <v>1344960</v>
+        <v>1344972</v>
       </c>
       <c r="E283" s="3" t="n">
-        <v>1043</v>
+        <v>12780</v>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12780 may be NULL and will be dereferenced at line 12780.</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>pbuf_copy_partial_pbuf</t>
+          <t>_find</t>
         </is>
       </c>
       <c r="H283" s="3" t="inlineStr">
@@ -23012,7 +23012,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr"/>
@@ -23022,19 +23022,19 @@
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>1344966</v>
+        <v>1344973</v>
       </c>
       <c r="E284" s="3" t="n">
-        <v>234</v>
+        <v>12832</v>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>Pointer 's' will be dereferenced at line 234 after having been checked for NULL.</t>
+          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12832 may be NULL and will be dereferenced at line 12832.</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>strlength</t>
+          <t>add</t>
         </is>
       </c>
       <c r="H284" s="3" t="inlineStr">
@@ -23085,29 +23085,29 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr"/>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/snmp/snmp_core.c</t>
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>1344967</v>
+        <v>1344976</v>
       </c>
       <c r="E285" s="3" t="n">
-        <v>246</v>
+        <v>847</v>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'src' will be dereferenced at line 246 after having been checked for NULL.</t>
+          <t>Array 'node_oid-&gt;id' of size 50 may use index value(s) 0..50</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>strequal</t>
+          <t>snmp_get_next_node_instance_from_oid</t>
         </is>
       </c>
       <c r="H285" s="3" t="inlineStr">
@@ -23158,29 +23158,29 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr"/>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/snmp/snmp_core.c</t>
         </is>
       </c>
       <c r="D286" s="3" t="n">
-        <v>1344968</v>
+        <v>1344977</v>
       </c>
       <c r="E286" s="3" t="n">
-        <v>246</v>
+        <v>903</v>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'dst' will be dereferenced at line 246 after having been checked for NULL.</t>
+          <t>Array 'node_instance-&gt;instance_oid.id' of size 50 may use index value(s) 0..50</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>strequal</t>
+          <t>snmp_get_next_node_instance_from_oid</t>
         </is>
       </c>
       <c r="H286" s="3" t="inlineStr">
@@ -23231,29 +23231,29 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr"/>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>1344969</v>
+        <v>1346141</v>
       </c>
       <c r="E287" s="3" t="n">
-        <v>269</v>
+        <v>540</v>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'end' will be dereferenced at line 269 after having been checked for NULL.</t>
+          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 537 may be NULL and will be dereferenced at line 540.</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>strlength_wide</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H287" s="3" t="inlineStr">
@@ -23304,29 +23304,29 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr"/>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>1344970</v>
+        <v>1346142</v>
       </c>
       <c r="E288" s="3" t="n">
-        <v>7953</v>
+        <v>518</v>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'cur' will be dereferenced at line 7953 after having been checked for NULL.</t>
+          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 515 may be NULL and will be dereferenced at line 518.</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H288" s="3" t="inlineStr">
@@ -23377,29 +23377,29 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr"/>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>1344971</v>
+        <v>1346143</v>
       </c>
       <c r="E289" s="3" t="n">
-        <v>11398</v>
+        <v>565</v>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'this-&gt;_alloc-&gt;_error' will be dereferenced at line 11398 after having been checked for NULL.</t>
+          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 562 may be NULL and will be dereferenced at line 565.</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>error_oom</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H289" s="3" t="inlineStr">
@@ -23456,23 +23456,23 @@
       <c r="B290" s="3" t="inlineStr"/>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
-        <v>1344972</v>
+        <v>1346144</v>
       </c>
       <c r="E290" s="3" t="n">
-        <v>12780</v>
+        <v>589</v>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12780 may be NULL and will be dereferenced at line 12780.</t>
+          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 586 may be NULL and will be dereferenced at line 589.</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>_find</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H290" s="3" t="inlineStr">
@@ -23523,29 +23523,29 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr"/>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>1344973</v>
+        <v>1346153</v>
       </c>
       <c r="E291" s="3" t="n">
-        <v>12832</v>
+        <v>247</v>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12832 may be NULL and will be dereferenced at line 12832.</t>
+          <t>'remapType' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>EnetCli_priorityMap</t>
         </is>
       </c>
       <c r="H291" s="3" t="inlineStr">
@@ -23596,29 +23596,29 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr"/>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/snmp/snmp_core.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>1344976</v>
+        <v>1347582</v>
       </c>
       <c r="E292" s="3" t="n">
-        <v>847</v>
+        <v>1465</v>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>Array 'node_oid-&gt;id' of size 50 may use index value(s) 0..50</t>
+          <t>'dpPll' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>snmp_get_next_node_instance_from_oid</t>
+          <t>ml100MhzPhyPmaCmnVcoCfg</t>
         </is>
       </c>
       <c r="H292" s="3" t="inlineStr">
@@ -23669,29 +23669,29 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr"/>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/snmp/snmp_core.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
         </is>
       </c>
       <c r="D293" s="3" t="n">
-        <v>1344977</v>
+        <v>1347583</v>
       </c>
       <c r="E293" s="3" t="n">
-        <v>903</v>
+        <v>1468</v>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>Array 'node_instance-&gt;instance_oid.id' of size 50 may use index value(s) 0..50</t>
+          <t>'dpPll' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>snmp_get_next_node_instance_from_oid</t>
+          <t>ml100MhzPhyPmaCmnVcoCfg</t>
         </is>
       </c>
       <c r="H293" s="3" t="inlineStr">
@@ -23742,29 +23742,29 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr"/>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>1346141</v>
+        <v>1347584</v>
       </c>
       <c r="E294" s="3" t="n">
-        <v>494</v>
+        <v>1471</v>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 491 may be NULL and will be dereferenced at line 494.</t>
+          <t>'dpPll' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>EnetCli_classifier</t>
+          <t>ml100MhzPhyPmaCmnVcoCfg</t>
         </is>
       </c>
       <c r="H294" s="3" t="inlineStr">
@@ -23815,29 +23815,29 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr"/>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
         </is>
       </c>
       <c r="D295" s="3" t="n">
-        <v>1346142</v>
+        <v>1347585</v>
       </c>
       <c r="E295" s="3" t="n">
-        <v>478</v>
+        <v>1474</v>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 475 may be NULL and will be dereferenced at line 478.</t>
+          <t>'dpPll' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>EnetCli_classifier</t>
+          <t>ml100MhzPhyPmaCmnVcoCfg</t>
         </is>
       </c>
       <c r="H295" s="3" t="inlineStr">
@@ -23888,7 +23888,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr"/>
@@ -23898,14 +23898,14 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>1346143</v>
+        <v>1347871</v>
       </c>
       <c r="E296" s="3" t="n">
-        <v>528</v>
+        <v>470</v>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 525 may be NULL and will be dereferenced at line 528.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -23961,7 +23961,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr"/>
@@ -23971,14 +23971,14 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>1346144</v>
+        <v>1347872</v>
       </c>
       <c r="E297" s="3" t="n">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 509 may be NULL and will be dereferenced at line 512.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -24044,19 +24044,19 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>1346153</v>
+        <v>1347873</v>
       </c>
       <c r="E298" s="3" t="n">
-        <v>241</v>
+        <v>514</v>
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>'remapType' might be used uninitialized in this function.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>EnetCli_priorityMap</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H298" s="3" t="inlineStr">
@@ -24113,23 +24113,23 @@
       <c r="B299" s="3" t="inlineStr"/>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>1347582</v>
+        <v>1347874</v>
       </c>
       <c r="E299" s="3" t="n">
-        <v>1465</v>
+        <v>583</v>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>'dpPll' might be used uninitialized in this function.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>ml100MhzPhyPmaCmnVcoCfg</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H299" s="3" t="inlineStr">
@@ -24186,23 +24186,23 @@
       <c r="B300" s="3" t="inlineStr"/>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>1347583</v>
+        <v>1347875</v>
       </c>
       <c r="E300" s="3" t="n">
-        <v>1468</v>
+        <v>559</v>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>'dpPll' might be used uninitialized in this function.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>ml100MhzPhyPmaCmnVcoCfg</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H300" s="3" t="inlineStr">
@@ -24259,23 +24259,23 @@
       <c r="B301" s="3" t="inlineStr"/>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>1347584</v>
+        <v>1347876</v>
       </c>
       <c r="E301" s="3" t="n">
-        <v>1471</v>
+        <v>536</v>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>'dpPll' might be used uninitialized in this function.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>ml100MhzPhyPmaCmnVcoCfg</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H301" s="3" t="inlineStr">
@@ -24332,23 +24332,23 @@
       <c r="B302" s="3" t="inlineStr"/>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>1347585</v>
+        <v>1347877</v>
       </c>
       <c r="E302" s="3" t="n">
-        <v>1474</v>
+        <v>605</v>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>'dpPll' might be used uninitialized in this function.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>ml100MhzPhyPmaCmnVcoCfg</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H302" s="3" t="inlineStr">
@@ -24399,29 +24399,29 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>LOCRET.ARG</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr"/>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_api.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>1347590</v>
+        <v>1347878</v>
       </c>
       <c r="E303" s="3" t="n">
-        <v>952</v>
+        <v>629</v>
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>Address of a local variable is returned through formal argument 'config-&gt;portMirCfg'.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>EthFw_initConfigParams</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H303" s="3" t="inlineStr">
@@ -24463,7 +24463,7 @@
       <c r="R303" s="3" t="inlineStr"/>
       <c r="S303" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T303" s="3" t="inlineStr"/>
@@ -24472,29 +24472,29 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>UNINIT.STACK.MUST</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr"/>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/csirx/src/csirx_event.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>1347733</v>
+        <v>1347879</v>
       </c>
       <c r="E304" s="3" t="n">
-        <v>457</v>
+        <v>653</v>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>'config.type' is used uninitialized in this function.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>CsirxDrv_eventDisable</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H304" s="3" t="inlineStr">
@@ -24512,7 +24512,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr">
@@ -24542,8 +24542,837 @@
       <c r="T304" s="3" t="inlineStr"/>
       <c r="U304" s="3" t="inlineStr"/>
     </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>ABV.MEMBER</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>Waiver id: PSDKRA_SA_DR_001 (Usecase 1)</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/client/src/cpsw_proxy.c</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="n">
+        <v>1349271</v>
+      </c>
+      <c r="E305" s="3" t="n">
+        <v>1456</v>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>Array '&amp;(req.hdr)' of size 20 may use index value(s) 20..23</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>CpswProxy_freeHwPushInst</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I305" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J305" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K305" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L305" s="3" t="inlineStr">
+        <is>
+          <t>Not a Problem</t>
+        </is>
+      </c>
+      <c r="M305" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N305" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O305" s="3" t="inlineStr"/>
+      <c r="P305" s="3" t="inlineStr"/>
+      <c r="Q305" s="3" t="inlineStr"/>
+      <c r="R305" s="3" t="inlineStr"/>
+      <c r="S305" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="T305" s="3" t="inlineStr"/>
+      <c r="U305" s="3" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.STACK.MUST</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>Waiver ID: PSDKRA_SA_DR_012</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/perf_stats/src/app_perf_stats_rtos.c</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>1350498</v>
+      </c>
+      <c r="E306" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>'rtos_load_stat.totalTime' is used uninitialized in this function.</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>appPerfStatsTaskLoadUpdate</t>
+        </is>
+      </c>
+      <c r="H306" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I306" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J306" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K306" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L306" s="3" t="inlineStr">
+        <is>
+          <t>Not a Problem</t>
+        </is>
+      </c>
+      <c r="M306" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N306" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O306" s="3" t="inlineStr"/>
+      <c r="P306" s="3" t="inlineStr"/>
+      <c r="Q306" s="3" t="inlineStr"/>
+      <c r="R306" s="3" t="inlineStr"/>
+      <c r="S306" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="T306" s="3" t="inlineStr"/>
+      <c r="U306" s="3" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>UNINIT.STACK.MUST</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>Waiver ID: PSDKRA_SA_DR_012</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/perf_stats/src/app_perf_stats_rtos.c</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>1350499</v>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="F307" s="3" t="inlineStr">
+        <is>
+          <t>'rtos_load_stat.threadTime' is used uninitialized in this function.</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>appPerfStatsTaskLoadUpdate</t>
+        </is>
+      </c>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I307" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J307" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K307" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L307" s="3" t="inlineStr">
+        <is>
+          <t>Not a Problem</t>
+        </is>
+      </c>
+      <c r="M307" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N307" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O307" s="3" t="inlineStr"/>
+      <c r="P307" s="3" t="inlineStr"/>
+      <c r="Q307" s="3" t="inlineStr"/>
+      <c r="R307" s="3" t="inlineStr"/>
+      <c r="S307" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="T307" s="3" t="inlineStr"/>
+      <c r="U307" s="3" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>Waiver ID: PSDKRA_SA_DR_001
+Out of bounds will never happen</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_tsn.c</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>1350598</v>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>619</v>
+      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>Array 'netdevs' of size 16 may use index value(s) INT_MIN..254</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>EthFwTsn_gptpTask</t>
+        </is>
+      </c>
+      <c r="H308" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I308" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J308" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K308" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L308" s="3" t="inlineStr">
+        <is>
+          <t>Not a Problem</t>
+        </is>
+      </c>
+      <c r="M308" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N308" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O308" s="3" t="inlineStr"/>
+      <c r="P308" s="3" t="inlineStr"/>
+      <c r="Q308" s="3" t="inlineStr"/>
+      <c r="R308" s="3" t="inlineStr"/>
+      <c r="S308" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="T308" s="3" t="inlineStr"/>
+      <c r="U308" s="3" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>Waiver ID: PSDKRA_SA_DR_001
+Out of bounds will never happen</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_tsn.c</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>1350599</v>
+      </c>
+      <c r="E309" s="3" t="n">
+        <v>619</v>
+      </c>
+      <c r="F309" s="3" t="inlineStr">
+        <is>
+          <t>Array 'netdevs' of size 16 may use index value(s) INT_MIN..INT_MAX-1</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>EthFwTsn_gptpTask</t>
+        </is>
+      </c>
+      <c r="H309" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I309" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J309" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K309" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L309" s="3" t="inlineStr">
+        <is>
+          <t>Not a Problem</t>
+        </is>
+      </c>
+      <c r="M309" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N309" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O309" s="3" t="inlineStr"/>
+      <c r="P309" s="3" t="inlineStr"/>
+      <c r="Q309" s="3" t="inlineStr"/>
+      <c r="R309" s="3" t="inlineStr"/>
+      <c r="S309" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="T309" s="3" t="inlineStr"/>
+      <c r="U309" s="3" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>NPD.GEN.CALL.MUST</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr"/>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_gptp/gptpconf/gptpgcfg.c</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="n">
+        <v>1350992</v>
+      </c>
+      <c r="E310" s="3" t="n">
+        <v>462</v>
+      </c>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>Null pointer '...?&amp;(gycd-&gt;nonyangsem):( (void* )0)' that comes from line 462 will be passed to function and can be dereferenced there by passing argument 7 to function 'uc_nc_notice_register' at line 462.</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>gptp_nonyang_init_notice</t>
+        </is>
+      </c>
+      <c r="H310" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I310" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J310" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K310" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L310" s="3" t="inlineStr">
+        <is>
+          <t>Analyze</t>
+        </is>
+      </c>
+      <c r="M310" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N310" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O310" s="3" t="inlineStr"/>
+      <c r="P310" s="3" t="inlineStr"/>
+      <c r="Q310" s="3" t="inlineStr"/>
+      <c r="R310" s="3" t="inlineStr"/>
+      <c r="S310" s="3" t="inlineStr">
+        <is>
+          <t>No Module</t>
+        </is>
+      </c>
+      <c r="T310" s="3" t="inlineStr"/>
+      <c r="U310" s="3" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr"/>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="n">
+        <v>1352585</v>
+      </c>
+      <c r="E311" s="3" t="n">
+        <v>1559</v>
+      </c>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>Array 'aps' of size 18 may use index value(s) 18</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>yang_db_runtime_state_keyvkstr</t>
+        </is>
+      </c>
+      <c r="H311" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I311" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J311" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K311" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L311" s="3" t="inlineStr">
+        <is>
+          <t>Analyze</t>
+        </is>
+      </c>
+      <c r="M311" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N311" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O311" s="3" t="inlineStr"/>
+      <c r="P311" s="3" t="inlineStr"/>
+      <c r="Q311" s="3" t="inlineStr"/>
+      <c r="R311" s="3" t="inlineStr"/>
+      <c r="S311" s="3" t="inlineStr">
+        <is>
+          <t>No Module</t>
+        </is>
+      </c>
+      <c r="T311" s="3" t="inlineStr"/>
+      <c r="U311" s="3" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>LOCRET.ARG</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr"/>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/tsnconf/excelfore-config-uni_access.c</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="n">
+        <v>1353264</v>
+      </c>
+      <c r="E312" s="3" t="n">
+        <v>441</v>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>Address of a local variable is returned through formal argument 'ydbia-&gt;dbpara.value'.</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>ydbi_get_mac_in_pool</t>
+        </is>
+      </c>
+      <c r="H312" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I312" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J312" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K312" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L312" s="3" t="inlineStr">
+        <is>
+          <t>Analyze</t>
+        </is>
+      </c>
+      <c r="M312" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N312" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O312" s="3" t="inlineStr"/>
+      <c r="P312" s="3" t="inlineStr"/>
+      <c r="Q312" s="3" t="inlineStr"/>
+      <c r="R312" s="3" t="inlineStr"/>
+      <c r="S312" s="3" t="inlineStr">
+        <is>
+          <t>No Module</t>
+        </is>
+      </c>
+      <c r="T312" s="3" t="inlineStr"/>
+      <c r="U312" s="3" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>LOCRET.ARG</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr"/>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/tsnconf/excelfore-config-uni_access.c</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="n">
+        <v>1353265</v>
+      </c>
+      <c r="E313" s="3" t="n">
+        <v>509</v>
+      </c>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>Address of a local variable is returned through formal argument 'ydbia-&gt;dbpara.value'.</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>ydbi_rel_mac_in_pool</t>
+        </is>
+      </c>
+      <c r="H313" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I313" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J313" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K313" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L313" s="3" t="inlineStr">
+        <is>
+          <t>Analyze</t>
+        </is>
+      </c>
+      <c r="M313" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N313" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O313" s="3" t="inlineStr"/>
+      <c r="P313" s="3" t="inlineStr"/>
+      <c r="Q313" s="3" t="inlineStr"/>
+      <c r="R313" s="3" t="inlineStr"/>
+      <c r="S313" s="3" t="inlineStr">
+        <is>
+          <t>No Module</t>
+        </is>
+      </c>
+      <c r="T313" s="3" t="inlineStr"/>
+      <c r="U313" s="3" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>INFINITE_LOOP.LOCAL</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>PSDKRA_SA_DR_006 (INFINITE_LOOP.LOCAL)</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/client/src/ts_coupler_client.c</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="n">
+        <v>1356124</v>
+      </c>
+      <c r="E314" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>Infinite loop</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>TsCouplerClient_task</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>a0502541</t>
+        </is>
+      </c>
+      <c r="I314" s="3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="J314" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K314" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L314" s="3" t="inlineStr">
+        <is>
+          <t>Not a Problem</t>
+        </is>
+      </c>
+      <c r="M314" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N314" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O314" s="3" t="inlineStr"/>
+      <c r="P314" s="3" t="inlineStr"/>
+      <c r="Q314" s="3" t="inlineStr"/>
+      <c r="R314" s="3" t="inlineStr"/>
+      <c r="S314" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="T314" s="3" t="inlineStr"/>
+      <c r="U314" s="3" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr"/>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/lwipif/src/lwip2enet.c</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="n">
+        <v>1364364</v>
+      </c>
+      <c r="E315" s="3" t="n">
+        <v>311</v>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>Array 'rxInfo' of size 2 may use index value(s) 2</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>Lwip2Enet_open</t>
+        </is>
+      </c>
+      <c r="H315" s="3" t="inlineStr">
+        <is>
+          <t>unowned</t>
+        </is>
+      </c>
+      <c r="I315" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J315" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K315" s="3" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="L315" s="3" t="inlineStr">
+        <is>
+          <t>Analyze</t>
+        </is>
+      </c>
+      <c r="M315" s="3" t="inlineStr">
+        <is>
+          <t>C and C++</t>
+        </is>
+      </c>
+      <c r="N315" s="3" t="inlineStr">
+        <is>
+          <t>KW Issue Link</t>
+        </is>
+      </c>
+      <c r="O315" s="3" t="inlineStr"/>
+      <c r="P315" s="3" t="inlineStr"/>
+      <c r="Q315" s="3" t="inlineStr"/>
+      <c r="R315" s="3" t="inlineStr"/>
+      <c r="S315" s="3" t="inlineStr">
+        <is>
+          <t>No Module</t>
+        </is>
+      </c>
+      <c r="T315" s="3" t="inlineStr"/>
+      <c r="U315" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U304"/>
+  <autoFilter ref="A1:U315"/>
   <hyperlinks>
     <hyperlink ref="N2" r:id="rId1"/>
     <hyperlink ref="N3" r:id="rId2"/>
@@ -24848,6 +25677,17 @@
     <hyperlink ref="N302" r:id="rId301"/>
     <hyperlink ref="N303" r:id="rId302"/>
     <hyperlink ref="N304" r:id="rId303"/>
+    <hyperlink ref="N305" r:id="rId304"/>
+    <hyperlink ref="N306" r:id="rId305"/>
+    <hyperlink ref="N307" r:id="rId306"/>
+    <hyperlink ref="N308" r:id="rId307"/>
+    <hyperlink ref="N309" r:id="rId308"/>
+    <hyperlink ref="N310" r:id="rId309"/>
+    <hyperlink ref="N311" r:id="rId310"/>
+    <hyperlink ref="N312" r:id="rId311"/>
+    <hyperlink ref="N313" r:id="rId312"/>
+    <hyperlink ref="N314" r:id="rId313"/>
+    <hyperlink ref="N315" r:id="rId314"/>
   </hyperlinks>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/docs/misrac/ethfw_SA_Report.xlsx
+++ b/docs/misrac/ethfw_SA_Report.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Template Revision History" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$U$315</definedName>
+    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Raw Issue Details'!$A$1:$U$272</definedName>
     <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">'SA_GEP'!$A$1:$E$339</definedName>
     <definedName hidden="1" localSheetId="7" name="_xlnm._FilterDatabase">'Taxonomy Checkers'!$A$1:$F$339</definedName>
   </definedNames>
@@ -936,7 +936,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW_KW_BUILD_May_04_2025_09_10_AM</t>
+          <t>ETHFW_KW_BUILD_Aug_10_2025_09_10_AM</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2025-05-04 07:41:27.783534-05:00 CDT</t>
+          <t>2025-08-10 10:18:02.055705-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1048,37 +1048,37 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW_KW_BUILD_May_04_2025_09_10_AM</t>
+          <t>ETHFW_KW_BUILD_Aug_10_2025_09_10_AM</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Sun May 04 16:06:57 IST 2025</t>
+          <t>Sun Aug 10 16:12:54 IST 2025</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>437540</v>
+        <v>439095</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>376582</v>
+        <v>377152</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>8039</v>
+        <v>7371</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>659089</v>
+        <v>656746</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2807</v>
+        <v>3017</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>13974</v>
+        <v>13292</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>663</v>
+        <v>874</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>23</v>
@@ -1426,13 +1426,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -1732,25 +1732,25 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I12" s="13" t="n">
         <v>23</v>
@@ -1898,19 +1898,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="E2" s="12" t="n">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -1950,13 +1950,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0</v>
@@ -2002,25 +2002,25 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I4" s="13" t="n">
         <v>23</v>
@@ -2058,7 +2058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U315"/>
+  <dimension ref="A1:U272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="18"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L137" s="3" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr">
@@ -15382,19 +15382,19 @@
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>1313480</v>
+        <v>1313481</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>341</v>
+        <v>445</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Unvalidated integer value 'xmllen' is received from 'nconf_msgdec_parse_chunked_frame' at line 328 and can be used to access an array through call to 'nconf_xmlutils_parse_xml' at line 341.</t>
+          <t>Unvalidated integer value 'chunksize' is received from 'strtol' at line 437 and can be used to access an array through call to 'memmove' at line 445.</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>nconf_msgdec_parse_netconf_frame</t>
+          <t>nconf_msgdec_parse_chunked_frame</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
@@ -15445,29 +15445,29 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>SV.TAINTED.CALL.INDEX_ACCESS</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr"/>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_msgdec.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_msghdlr.c</t>
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>1313481</v>
+        <v>1313826</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>445</v>
+        <v>1478</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Unvalidated integer value 'chunksize' is received from 'strtol' at line 437 and can be used to access an array through call to 'memmove' at line 445.</t>
+          <t>Pointer 'sndbuf' returned from call to function 'nconf_memalloc_def' at line 1476 may be NULL and may be dereferenced at line 1478.</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>nconf_msgdec_parse_chunked_frame</t>
+          <t>nconf_msghdlr_send_get_schema_resp</t>
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr">
@@ -15477,11 +15477,11 @@
       </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J181" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
@@ -15524,23 +15524,23 @@
       <c r="B182" s="3" t="inlineStr"/>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_msghdlr.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/platform/ti-frtos/nconf_transmngr.c</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>1313826</v>
+        <v>1314024</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>1478</v>
+        <v>268</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'sndbuf' returned from call to function 'nconf_memalloc_def' at line 1476 may be NULL and may be dereferenced at line 1478.</t>
+          <t>Pointer 'pRecvMsg' returned from call to function 'nconf_tlscon_recv_msg' at line 266 may be NULL and may be dereferenced at line 268.</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>nconf_msghdlr_send_get_schema_resp</t>
+          <t>nconf_transport_process_tls_client_msg</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
@@ -15597,23 +15597,23 @@
       <c r="B183" s="3" t="inlineStr"/>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/platform/ti-frtos/nconf_transmngr.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_ucclient.c</t>
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>1314024</v>
+        <v>1314341</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pRecvMsg' returned from call to function 'nconf_tlscon_recv_msg' at line 266 may be NULL and may be dereferenced at line 268.</t>
+          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 291 may be NULL and may be dereferenced at line 293.</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>nconf_transport_process_tls_client_msg</t>
+          <t>nconf_ucclient_get_schema_hdl</t>
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr">
@@ -15674,19 +15674,19 @@
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>1314341</v>
+        <v>1314342</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>293</v>
+        <v>1075</v>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 291 may be NULL and may be dereferenced at line 293.</t>
+          <t>Pointer 'retbuf' returned from call to function 'nconf_memalloc_def' at line 1073 may be NULL and may be dereferenced at line 1075.</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_schema_hdl</t>
+          <t>nconf_ucclient_get_vstr</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
@@ -15747,19 +15747,19 @@
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>1314342</v>
+        <v>1314343</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>1075</v>
+        <v>1260</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'retbuf' returned from call to function 'nconf_memalloc_def' at line 1073 may be NULL and may be dereferenced at line 1075.</t>
+          <t>Pointer 'cfginfo-&gt;path' returned from call to function 'nconf_strdup_def' at line 1253 may be NULL and may be dereferenced at line 1260.</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_vstr</t>
+          <t>nconf_ucclient_update_config_cache</t>
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr">
@@ -15820,19 +15820,19 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>1314343</v>
+        <v>1314344</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>1260</v>
+        <v>1434</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'cfginfo-&gt;path' returned from call to function 'nconf_strdup_def' at line 1253 may be NULL and may be dereferenced at line 1260.</t>
+          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 1431 may be NULL and may be dereferenced at line 1434.</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_update_config_cache</t>
+          <t>nconf_ucclient_get_schema_namespace</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
@@ -15893,19 +15893,19 @@
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>1314344</v>
+        <v>1314345</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>1434</v>
+        <v>1460</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 1431 may be NULL and may be dereferenced at line 1434.</t>
+          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 1458 may be NULL and may be dereferenced at line 1460.</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_schema_namespace</t>
+          <t>nconf_ucclient_schema_search</t>
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr">
@@ -15966,19 +15966,19 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>1314345</v>
+        <v>1314346</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>1460</v>
+        <v>1739</v>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'tmpbuf' returned from call to function 'nconf_memalloc_def' at line 1458 may be NULL and may be dereferenced at line 1460.</t>
+          <t>Pointer 'kvpair' returned from call to function 'nconf_memalloc_def' at line 1737 may be NULL and may be dereferenced at line 1739.</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_schema_search</t>
+          <t>nconf_ucclient_is_nodekey_sent</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr">
@@ -16029,7 +16029,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr"/>
@@ -16039,19 +16039,19 @@
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>1314346</v>
+        <v>1314429</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>1739</v>
+        <v>326</v>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'kvpair' returned from call to function 'nconf_memalloc_def' at line 1737 may be NULL and may be dereferenced at line 1739.</t>
+          <t>Array 'aps' of size 16 may use index value(s) 16..254</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_is_nodekey_sent</t>
+          <t>nconf_ucclient_get_nodepath_vknum</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr">
@@ -16112,10 +16112,10 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>1314429</v>
+        <v>1314430</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_nodepath_vknum</t>
+          <t>nconf_ucclient_get_nodepath_vkstr</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr">
@@ -16185,10 +16185,10 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>1314430</v>
+        <v>1314431</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_nodepath_vkstr</t>
+          <t>nconf_ucclient_get_nodepath_vktype</t>
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr">
@@ -16248,29 +16248,29 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr"/>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_ucclient.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_xmlutils.cpp</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>1314431</v>
+        <v>1314633</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>386</v>
+        <v>590</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Array 'aps' of size 16 may use index value(s) 16..254</t>
+          <t>Pointer 'retpath' returned from call to function 'nconf_memalloc_def' at line 587 may be NULL and may be dereferenced at line 590.</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>nconf_ucclient_get_nodepath_vktype</t>
+          <t>nconf_xmlutils_get_node_path</t>
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr">
@@ -16331,19 +16331,19 @@
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>1314633</v>
+        <v>1314634</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>590</v>
+        <v>638</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'retpath' returned from call to function 'nconf_memalloc_def' at line 587 may be NULL and may be dereferenced at line 590.</t>
+          <t>Pointer 'retpath' returned from call to function 'nconf_memalloc_def' at line 635 may be NULL and may be dereferenced at line 638.</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>nconf_xmlutils_get_node_path</t>
+          <t>nconf_xmlutils_get_module_node_path</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr">
@@ -16404,19 +16404,19 @@
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>1314634</v>
+        <v>1314635</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>638</v>
+        <v>1128</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'retpath' returned from call to function 'nconf_memalloc_def' at line 635 may be NULL and may be dereferenced at line 638.</t>
+          <t>Pointer 'buf' returned from call to function 'nconf_memalloc_def' at line 1124 may be NULL and may be dereferenced at line 1128.</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>nconf_xmlutils_get_module_node_path</t>
+          <t>nconf_xmlutils_get_xpath_buf</t>
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr">
@@ -16477,19 +16477,19 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>1314635</v>
+        <v>1314636</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>1128</v>
+        <v>1307</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'buf' returned from call to function 'nconf_memalloc_def' at line 1124 may be NULL and may be dereferenced at line 1128.</t>
+          <t>Pointer 'outbuf' returned from call to function 'nconf_memalloc_def' at line 1305 may be NULL and may be dereferenced at line 1307.</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>nconf_xmlutils_get_xpath_buf</t>
+          <t>nconf_xmlutils_replaced_amp</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
@@ -16540,29 +16540,29 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr"/>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_netconf/src/daemon/nconf_xmlutils.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>1314636</v>
+        <v>1315140</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>1307</v>
+        <v>246</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'outbuf' returned from call to function 'nconf_memalloc_def' at line 1305 may be NULL and may be dereferenced at line 1307.</t>
+          <t>Pointer 'dst' will be dereferenced at line 246 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>nconf_xmlutils_replaced_amp</t>
+          <t>strequal</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
@@ -16613,7 +16613,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr"/>
@@ -16623,19 +16623,19 @@
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>1315139</v>
+        <v>1316918</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>246</v>
+        <v>8495</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'src' will be dereferenced at line 246 after having been checked for NULL.</t>
+          <t>Pointer 'exponent_string' returned from call to function 'strchr' at line 8492 may be NULL and will be dereferenced at line 8495.</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>strequal</t>
+          <t>convert_number_to_mantissa_exponent</t>
         </is>
       </c>
       <c r="H197" s="3" t="inlineStr">
@@ -16686,7 +16686,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr"/>
@@ -16696,19 +16696,19 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>1315140</v>
+        <v>1316921</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>246</v>
+        <v>12780</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'dst' will be dereferenced at line 246 after having been checked for NULL.</t>
+          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12780 may be NULL and will be dereferenced at line 12780.</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>strequal</t>
+          <t>_find</t>
         </is>
       </c>
       <c r="H198" s="3" t="inlineStr">
@@ -16759,29 +16759,29 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr"/>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/hal/uc_hwal.c</t>
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>1315141</v>
+        <v>1319695</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>7242</v>
+        <v>824</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'root_page' will be dereferenced at line 7242 after having been checked for NULL.</t>
+          <t>Pointer 'clst' returned from call to function 'ub_esarray_init' at line 816 may be NULL and may be dereferenced at line 824.</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>_destroy</t>
+          <t>tas_hw_action</t>
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr">
@@ -16832,29 +16832,29 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NNTS.MIGHT</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr"/>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/hal/uc_hwal.c</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>1315142</v>
+        <v>1319699</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>7322</v>
+        <v>853</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'other_page' will be dereferenced at line 7322 after having been checked for NULL.</t>
+          <t>Buffer overflow of 'nevent.ifname' due to non null terminated string 'nevent.ifname'</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>_move</t>
+          <t>preempt_hw_action</t>
         </is>
       </c>
       <c r="H200" s="3" t="inlineStr">
@@ -16905,29 +16905,29 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr"/>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>1315143</v>
+        <v>1319877</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>7328</v>
+        <v>288</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'doc_page' will be dereferenced at line 7328 after having been checked for NULL.</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 286 may be NULL and may be dereferenced at line 288.</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>_move</t>
+          <t>find_semname_in_putnoticelist</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
@@ -16978,29 +16978,29 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr"/>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>1315144</v>
+        <v>1319878</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>7333</v>
+        <v>411</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'doc_page' will be dereferenced at line 7333 after having been checked for NULL.</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 409 may be NULL and may be dereferenced at line 411.</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>_move</t>
+          <t>incremant_actcounter</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
@@ -17051,29 +17051,29 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr"/>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>1316905</v>
+        <v>1319879</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>328</v>
+        <v>440</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'item' returned from call to function 'get_item' at line 326 may be NULL and will be dereferenced at line 328.</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 436 may be NULL and may be dereferenced at line 440.</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>find</t>
+          <t>proc_refactcounter</t>
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr">
@@ -17124,29 +17124,29 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr"/>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>1316906</v>
+        <v>1319880</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>340</v>
+        <v>470</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'item' returned from call to function 'get_item' at line 337 may be NULL and will be dereferenced at line 340.</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 468 may be NULL and may be dereferenced at line 470.</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>insert</t>
+          <t>nu_clear_refcounter</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
@@ -17197,29 +17197,29 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>NPD.FUNC.MIGHT</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr"/>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>1316907</v>
+        <v>1319881</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>2406</v>
+        <v>486</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'dest.operator(char*)()' returned from call to function 'operator(char*)' at line 2406 may be NULL and will be dereferenced at line 2406.</t>
+          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 484 may be NULL and may be dereferenced at line 486.</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>strcpy_insitu</t>
+          <t>nu_increment_refcounter</t>
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr">
@@ -17270,29 +17270,29 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr"/>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_access.c</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>1316908</v>
+        <v>1321342</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>2407</v>
+        <v>1209</v>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'dest.operator(char*)()' returned from call to function 'operator(char*)' at line 2407 may be NULL and will be dereferenced at line 2407.</t>
+          <t>Array 'pstr' of size 64 may use index value(s) 64..UINT_MAX-1</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>strcpy_insitu</t>
+          <t>one_combine</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">
@@ -17343,29 +17343,29 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr"/>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_access.c</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>1316909</v>
+        <v>1321343</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>4158</v>
+        <v>1225</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 4155 may be NULL and will be dereferenced at line 4158.</t>
+          <t>Array 'pstr' of size 64 may use index value(s) 64..UINT_MAX-1</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>node_output_start</t>
+          <t>one_combine</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
@@ -17416,29 +17416,29 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr"/>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>1316910</v>
+        <v>1321804</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>4220</v>
+        <v>200</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 4217 may be NULL and will be dereferenced at line 4220.</t>
+          <t>Array 'apsd' of size 21 may use index value(s) 21..259</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>node_output_end</t>
+          <t>proc_get_keyv</t>
         </is>
       </c>
       <c r="H208" s="3" t="inlineStr">
@@ -17489,29 +17489,29 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr"/>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>1316911</v>
+        <v>1321805</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>4235</v>
+        <v>249</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Pointer '...?"":&amp;&amp;(node-&gt;value).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4235 may be NULL and will be dereferenced at line 4235.</t>
+          <t>Array 'kpi' of size 16 may use index value(s) 16..254</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>node_output_simple</t>
+          <t>proc_get_keyv</t>
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr">
@@ -17562,29 +17562,29 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr"/>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>1316912</v>
+        <v>1321806</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>4239</v>
+        <v>365</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Pointer '...?"":&amp;&amp;(node-&gt;value).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4239 may be NULL and will be dereferenced at line 4239.</t>
+          <t>Array 'kpi' of size 16 may use index value(s) 16..254</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>node_output_simple</t>
+          <t>proc_set_onenode</t>
         </is>
       </c>
       <c r="H210" s="3" t="inlineStr">
@@ -17635,29 +17635,29 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr"/>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>1316913</v>
+        <v>1321807</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>4244</v>
+        <v>548</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Pointer '...?default_name:&amp;&amp;(node-&gt;name).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4244 may be NULL and will be dereferenced at line 4244.</t>
+          <t>Array 'apsd' of size 21 may use index value(s) 21..257</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>node_output_simple</t>
+          <t>get_value_type</t>
         </is>
       </c>
       <c r="H211" s="3" t="inlineStr">
@@ -17708,29 +17708,29 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr"/>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>1316914</v>
+        <v>1321808</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>4249</v>
+        <v>1051</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Pointer '&amp;(node-&gt;value).operator(char*)()' returned from call to function 'operator(char*)' at line 4249 may be NULL and will be dereferenced at line 4249.</t>
+          <t>Array 'linebuf' of size 513 may use index value(s) -1</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>node_output_simple</t>
+          <t>yang_db_runtime_readfile</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr">
@@ -17784,26 +17784,30 @@
           <t>NPD.FUNC.MUST</t>
         </is>
       </c>
-      <c r="B213" s="3" t="inlineStr"/>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Waiver id: PSDKRA_SA_DR_003</t>
+        </is>
+      </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>1316915</v>
+        <v>1343714</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>4257</v>
+        <v>3616</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Pointer '...?default_name:&amp;&amp;(node-&gt;name).operator(char*)()[0]' returned from call to function 'operator(char*)' at line 4257 may be NULL and will be dereferenced at line 4257.</t>
+          <t>Pointer 'hClient' returned from call to function 'CpswProxyServer_getClient' at line 3613 may be NULL and will be dereferenced at line 3616.</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>node_output_simple</t>
+          <t>CpswProxyServer_clientRequestHandler</t>
         </is>
       </c>
       <c r="H213" s="3" t="inlineStr">
@@ -17826,7 +17830,7 @@
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
@@ -17845,7 +17849,7 @@
       <c r="R213" s="3" t="inlineStr"/>
       <c r="S213" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T213" s="3" t="inlineStr"/>
@@ -17854,29 +17858,33 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="inlineStr"/>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>waiver id: PSDKRA_SA_DR_001</t>
+        </is>
+      </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>1316916</v>
+        <v>1343722</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>4269</v>
+        <v>2706</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Pointer '&amp;(node-&gt;value).operator(char*)()' returned from call to function 'operator(char*)' at line 4269 may be NULL and will be dereferenced at line 4269.</t>
+          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>node_output_simple</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H214" s="3" t="inlineStr">
@@ -17899,7 +17907,7 @@
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
@@ -17918,7 +17926,7 @@
       <c r="R214" s="3" t="inlineStr"/>
       <c r="S214" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T214" s="3" t="inlineStr"/>
@@ -17927,29 +17935,33 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr"/>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>waiver id: PSDKRA_SA_DR_001</t>
+        </is>
+      </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>1316917</v>
+        <v>1343723</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>4357</v>
+        <v>2707</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4354 may be NULL and will be dereferenced at line 4357.</t>
+          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>node_output</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H215" s="3" t="inlineStr">
@@ -17972,7 +17984,7 @@
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
@@ -17991,7 +18003,7 @@
       <c r="R215" s="3" t="inlineStr"/>
       <c r="S215" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T215" s="3" t="inlineStr"/>
@@ -18000,29 +18012,33 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr"/>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>waiver id: PSDKRA_SA_DR_001</t>
+        </is>
+      </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>1316918</v>
+        <v>1343724</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>8495</v>
+        <v>2708</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'exponent_string' returned from call to function 'strchr' at line 8492 may be NULL and will be dereferenced at line 8495.</t>
+          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>convert_number_to_mantissa_exponent</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H216" s="3" t="inlineStr">
@@ -18045,7 +18061,7 @@
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
@@ -18064,7 +18080,7 @@
       <c r="R216" s="3" t="inlineStr"/>
       <c r="S216" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T216" s="3" t="inlineStr"/>
@@ -18073,29 +18089,33 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr"/>
+          <t>ABV.STACK</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
+        </is>
+      </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>1316919</v>
+        <v>1343725</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>10090</v>
+        <v>2709</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Pointer '&amp;(n-&gt;name).operator(char*)()' returned from call to function 'operator(char*)' at line 10090 may be NULL and will be dereferenced at line 10090.</t>
+          <t>Array 'g_CpswProxyServerAutosarRpmsgBuf' of size 2 may use index value(s) 0..5</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>step_push</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
@@ -18118,7 +18138,7 @@
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
@@ -18137,7 +18157,7 @@
       <c r="R217" s="3" t="inlineStr"/>
       <c r="S217" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T217" s="3" t="inlineStr"/>
@@ -18146,29 +18166,33 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr"/>
+          <t>ABV.STACK</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
+        </is>
+      </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>1316920</v>
+        <v>1343726</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>10126</v>
+        <v>2709</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Pointer '&amp;(n-&gt;name).operator(char*)()' returned from call to function 'operator(char*)' at line 10126 may be NULL and will be dereferenced at line 10126.</t>
+          <t>Array 'hServer-&gt;ethDrvObj' of size 2 may use index value(s) 0..5</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>step_push</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H218" s="3" t="inlineStr">
@@ -18191,7 +18215,7 @@
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
@@ -18210,7 +18234,7 @@
       <c r="R218" s="3" t="inlineStr"/>
       <c r="S218" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T218" s="3" t="inlineStr"/>
@@ -18219,29 +18243,33 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="inlineStr"/>
+          <t>ABV.STACK</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
+        </is>
+      </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>1316921</v>
+        <v>1343727</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>12780</v>
+        <v>2709</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12780 may be NULL and will be dereferenced at line 12780.</t>
+          <t>Array 'gCpswProxyServer_autosarEthDriverTaskStackBuf' of size 2 may use index value(s) 0..5</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>_find</t>
+          <t>CpswProxyServer_init</t>
         </is>
       </c>
       <c r="H219" s="3" t="inlineStr">
@@ -18264,7 +18292,7 @@
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
@@ -18283,7 +18311,7 @@
       <c r="R219" s="3" t="inlineStr"/>
       <c r="S219" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T219" s="3" t="inlineStr"/>
@@ -18292,29 +18320,33 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr"/>
+          <t>NPD.CHECK.MUST</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>waiver id: PSDKRA_SA_DR_005</t>
+        </is>
+      </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>1316922</v>
+        <v>1343729</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>12832</v>
+        <v>3616</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12832 may be NULL and will be dereferenced at line 12832.</t>
+          <t>Pointer 'hClient' will be dereferenced at line 3616 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>CpswProxyServer_clientRequestHandler</t>
         </is>
       </c>
       <c r="H220" s="3" t="inlineStr">
@@ -18337,7 +18369,7 @@
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
@@ -18356,7 +18388,7 @@
       <c r="R220" s="3" t="inlineStr"/>
       <c r="S220" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T220" s="3" t="inlineStr"/>
@@ -18365,29 +18397,29 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr"/>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/lwipif/src/lwip2enet.c</t>
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>1317952</v>
+        <v>1343777</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>3441</v>
+        <v>1361</v>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'cursor' returned from call to function 'parse_question' at line 3437 may be NULL and may be dereferenced at line 3441.</t>
+          <t>'errPkt' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>parse_tree</t>
+          <t>Lwip2Enet_prepRxPktQ</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr">
@@ -18438,29 +18470,29 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr"/>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/src/per/cpsw_intervlan.c</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>1317953</v>
+        <v>1344826</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>4298</v>
+        <v>172</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4350 may be NULL and may be dereferenced at line 4298.</t>
+          <t>Array 'inArgs-&gt;egressCfg' of size 8 may use index value(s) 0..MAX</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>node_output</t>
+          <t>Cpsw_ioctlInterVlan</t>
         </is>
       </c>
       <c r="H222" s="3" t="inlineStr">
@@ -18511,29 +18543,33 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="inlineStr"/>
+          <t>ABV.STACK</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>waiver id: PSDKRA_SA_DR_008</t>
+        </is>
+      </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_api.c</t>
         </is>
       </c>
       <c r="D223" s="3" t="n">
-        <v>1317954</v>
+        <v>1344879</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>4298</v>
+        <v>1382</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4333 may be NULL and may be dereferenced at line 4298.</t>
+          <t>Array 'gMcmObj' of size 8 may use index value(s) 0..8</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>node_output</t>
+          <t>EthFw_initMcm</t>
         </is>
       </c>
       <c r="H223" s="3" t="inlineStr">
@@ -18551,12 +18587,12 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
@@ -18575,7 +18611,7 @@
       <c r="R223" s="3" t="inlineStr"/>
       <c r="S223" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T223" s="3" t="inlineStr"/>
@@ -18584,29 +18620,33 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr"/>
+          <t>INFINITE_LOOP.LOCAL</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>waiver id: PSDKRA_SA_DR_006</t>
+        </is>
+      </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/app_remoteswitchcfg_server/main.c</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>1317955</v>
+        <v>1344937</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>4298</v>
+        <v>1960</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'node' returned from call to function 'operator(pugi::xml_node_struct*)' at line 4322 may be NULL and may be dereferenced at line 4298.</t>
+          <t>Infinite loop</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>node_output</t>
+          <t>EthApp_traceBufFlush</t>
         </is>
       </c>
       <c r="H224" s="3" t="inlineStr">
@@ -18616,11 +18656,11 @@
       </c>
       <c r="I224" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="J224" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
@@ -18629,7 +18669,7 @@
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
@@ -18648,7 +18688,7 @@
       <c r="R224" s="3" t="inlineStr"/>
       <c r="S224" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T224" s="3" t="inlineStr"/>
@@ -18657,29 +18697,29 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr"/>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns.c</t>
         </is>
       </c>
       <c r="D225" s="3" t="n">
-        <v>1317956</v>
+        <v>1344946</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>10050</v>
+        <v>2580</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 10045 may be NULL and may be dereferenced at line 10050.</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>step_push</t>
+          <t>mdns_resp_del_service</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
@@ -18730,29 +18770,29 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr"/>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>1317957</v>
+        <v>1344947</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>10059</v>
+        <v>373</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 10045 may be NULL and may be dereferenced at line 10059.</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>step_push</t>
+          <t>mdns_build_reverse_v4_domain</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
@@ -18803,29 +18843,29 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr"/>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>1317958</v>
+        <v>1344948</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>10067</v>
+        <v>430</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'name' returned from call to function 'operator(char*)' at line 10045 may be NULL and may be dereferenced at line 10067.</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>step_push</t>
+          <t>mdns_add_dotlocal</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
@@ -18876,29 +18916,29 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr"/>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
-        <v>1317963</v>
+        <v>1344949</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>4031</v>
+        <v>448</v>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Array 'writer.buffer' of size 204 may use index value(s) 4..204</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>text_output_cdata</t>
+          <t>mdns_build_host_domain</t>
         </is>
       </c>
       <c r="H228" s="3" t="inlineStr">
@@ -18949,29 +18989,29 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr"/>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D229" s="3" t="n">
-        <v>1317964</v>
+        <v>1344950</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>4089</v>
+        <v>468</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Array 'writer.buffer' of size 204 may use index value(s) 0..204</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>node_output_comment</t>
+          <t>mdns_build_dnssd_domain</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
@@ -19022,29 +19062,29 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.CALL.MIGHT</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr"/>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>1317965</v>
+        <v>1344951</v>
       </c>
       <c r="E230" s="3" t="n">
-        <v>4765</v>
+        <v>494</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'contents' checked for NULL at line 4752 may be passed to function and may be dereferenced there by passing argument 4 to function 'convert_buffer' at line 4765.</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>load_buffer_impl</t>
+          <t>mdns_build_service_domain</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
@@ -19095,29 +19135,29 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>ABV.ITERATOR</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr"/>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
         </is>
       </c>
       <c r="D231" s="3" t="n">
-        <v>1317978</v>
+        <v>1344952</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>7242</v>
+        <v>520</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Buffer overflow, pointer 'root_page' is used at line 7242 when its value may exceed array 'this-&gt;_memory' bounds. Pointer 'root_page' is checked against array bounds (reinterpret_cast&lt;char* &gt; (root_page) &lt;_memory+sizeof(_memory)) at line 7240.</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>_destroy</t>
+          <t>mdns_build_request_domain</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
@@ -19168,29 +19208,29 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>RH.LEAK</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr"/>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/memp.c</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>1317979</v>
+        <v>1344953</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>7410</v>
+        <v>356</v>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file(path_, "rb" )' at line 7408 may be lost here.</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>load_file</t>
+          <t>memp_malloc</t>
         </is>
       </c>
       <c r="H232" s="3" t="inlineStr">
@@ -19200,11 +19240,11 @@
       </c>
       <c r="I232" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J232" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
@@ -19241,29 +19281,29 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>RH.LEAK</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr"/>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/pbuf.c</t>
         </is>
       </c>
       <c r="D233" s="3" t="n">
-        <v>1317980</v>
+        <v>1344959</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>7420</v>
+        <v>616</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file_wide(path_, L"rb" )' at line 7418 may be lost here.</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>load_file</t>
+          <t>pbuf_remove_header</t>
         </is>
       </c>
       <c r="H233" s="3" t="inlineStr">
@@ -19273,11 +19313,11 @@
       </c>
       <c r="I233" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J233" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
@@ -19314,29 +19354,29 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>RH.LEAK</t>
+          <t>FUNCRET.GEN</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr"/>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/pbuf.c</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>1317981</v>
+        <v>1344960</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>7493</v>
+        <v>1043</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file(path_,  (flags&amp;format_save_file_text)?"w" :"wb" )' at line 7491 may be lost here.</t>
+          <t>Non-void function does not return value</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>save_file</t>
+          <t>pbuf_copy_partial_pbuf</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
@@ -19346,11 +19386,11 @@
       </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J234" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
@@ -19387,7 +19427,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>RH.LEAK</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr"/>
@@ -19397,19 +19437,19 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>1317982</v>
+        <v>1344966</v>
       </c>
       <c r="E235" s="3" t="n">
-        <v>7493</v>
+        <v>234</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file(path_,  (flags&amp;format_save_file_text)?"w" :"wb" )' at line 7491 may be lost here.</t>
+          <t>Pointer 's' will be dereferenced at line 234 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>save_file</t>
+          <t>strlength</t>
         </is>
       </c>
       <c r="H235" s="3" t="inlineStr">
@@ -19419,11 +19459,11 @@
       </c>
       <c r="I235" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J235" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
@@ -19460,7 +19500,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>RH.LEAK</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr"/>
@@ -19470,19 +19510,19 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>1317983</v>
+        <v>1344967</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>7501</v>
+        <v>246</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file_wide(path_,  (flags&amp;format_save_file_text)?L"w" :L"wb" )' at line 7499 may be lost here.</t>
+          <t>Pointer 'src' will be dereferenced at line 246 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>save_file</t>
+          <t>strequal</t>
         </is>
       </c>
       <c r="H236" s="3" t="inlineStr">
@@ -19492,11 +19532,11 @@
       </c>
       <c r="I236" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J236" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
@@ -19533,7 +19573,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>RH.LEAK</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr"/>
@@ -19543,19 +19583,19 @@
         </is>
       </c>
       <c r="D237" s="3" t="n">
-        <v>1317984</v>
+        <v>1344969</v>
       </c>
       <c r="E237" s="3" t="n">
-        <v>7501</v>
+        <v>269</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>Resource acquired to 'impl::open_file_wide(path_,  (flags&amp;format_save_file_text)?L"w" :L"wb" )' at line 7499 may be lost here.</t>
+          <t>Pointer 'end' will be dereferenced at line 269 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>save_file</t>
+          <t>strlength_wide</t>
         </is>
       </c>
       <c r="H237" s="3" t="inlineStr">
@@ -19565,11 +19605,11 @@
       </c>
       <c r="I237" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J237" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
@@ -19606,7 +19646,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>SV.TAINTED.LOOP_BOUND</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr"/>
@@ -19616,19 +19656,19 @@
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>1317993</v>
+        <v>1344970</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>8546</v>
+        <v>7953</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Unvalidated integer value 'exponent' is received from 'convert_number_to_mantissa_exponent' at line 8526 and can be used in a loop condition at line 8546.</t>
+          <t>Pointer 'cur' will be dereferenced at line 7953 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>convert_number_to_string</t>
+          <t>release</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
@@ -19638,11 +19678,11 @@
       </c>
       <c r="I238" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J238" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
@@ -19679,29 +19719,29 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr"/>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/hal/uc_hwal.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D239" s="3" t="n">
-        <v>1319695</v>
+        <v>1344971</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>825</v>
+        <v>11398</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'clst' returned from call to function 'ub_esarray_init' at line 817 may be NULL and may be dereferenced at line 825.</t>
+          <t>Pointer 'this-&gt;_alloc-&gt;_error' will be dereferenced at line 11398 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>tas_hw_action</t>
+          <t>error_oom</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
@@ -19752,29 +19792,29 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>NNTS.MIGHT</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr"/>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/hal/uc_hwal.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/snmp/snmp_core.c</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>1319699</v>
+        <v>1344976</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Buffer overflow of 'nevent.ifname' due to non null terminated string 'nevent.ifname'</t>
+          <t>Array 'node_oid-&gt;id' of size 50 may use index value(s) 0..50</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>preempt_hw_action</t>
+          <t>snmp_get_next_node_instance_from_oid</t>
         </is>
       </c>
       <c r="H240" s="3" t="inlineStr">
@@ -19825,29 +19865,29 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>ABV.STACK</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr"/>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/snmp/snmp_core.c</t>
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>1319877</v>
+        <v>1344977</v>
       </c>
       <c r="E241" s="3" t="n">
-        <v>288</v>
+        <v>903</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 286 may be NULL and may be dereferenced at line 288.</t>
+          <t>Array 'node_instance-&gt;instance_oid.id' of size 50 may use index value(s) 0..50</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>find_semname_in_putnoticelist</t>
+          <t>snmp_get_next_node_instance_from_oid</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
@@ -19898,29 +19938,29 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr"/>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>1319878</v>
+        <v>1346141</v>
       </c>
       <c r="E242" s="3" t="n">
-        <v>411</v>
+        <v>540</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 409 may be NULL and may be dereferenced at line 411.</t>
+          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 537 may be NULL and will be dereferenced at line 540.</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>incremant_actcounter</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H242" s="3" t="inlineStr">
@@ -19938,7 +19978,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr">
@@ -19971,29 +20011,29 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr"/>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>1319879</v>
+        <v>1346142</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>440</v>
+        <v>518</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 436 may be NULL and may be dereferenced at line 440.</t>
+          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 515 may be NULL and will be dereferenced at line 518.</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>proc_refactcounter</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H243" s="3" t="inlineStr">
@@ -20011,7 +20051,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L243" s="3" t="inlineStr">
@@ -20044,29 +20084,29 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr"/>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
-        <v>1319880</v>
+        <v>1346143</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>470</v>
+        <v>565</v>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 468 may be NULL and may be dereferenced at line 470.</t>
+          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 562 may be NULL and will be dereferenced at line 565.</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>nu_clear_refcounter</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
@@ -20084,7 +20124,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr">
@@ -20117,29 +20157,29 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MIGHT</t>
+          <t>NPD.FUNC.MUST</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr"/>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/uc_notice.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D245" s="3" t="n">
-        <v>1319881</v>
+        <v>1346144</v>
       </c>
       <c r="E245" s="3" t="n">
-        <v>486</v>
+        <v>589</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'pnd' returned from call to function 'ub_esarray_get_ele' at line 484 may be NULL and may be dereferenced at line 486.</t>
+          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 586 may be NULL and will be dereferenced at line 589.</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>nu_increment_refcounter</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
@@ -20157,7 +20197,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="L245" s="3" t="inlineStr">
@@ -20190,29 +20230,29 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr"/>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_access.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>1321342</v>
+        <v>1346153</v>
       </c>
       <c r="E246" s="3" t="n">
-        <v>1209</v>
+        <v>247</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Array 'pstr' of size 64 may use index value(s) 64..UINT_MAX-1</t>
+          <t>'remapType' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>one_combine</t>
+          <t>EnetCli_priorityMap</t>
         </is>
       </c>
       <c r="H246" s="3" t="inlineStr">
@@ -20263,29 +20303,29 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr"/>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_access.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>1321343</v>
+        <v>1347582</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>1225</v>
+        <v>1465</v>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Array 'pstr' of size 64 may use index value(s) 64..UINT_MAX-1</t>
+          <t>'dpPll' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>one_combine</t>
+          <t>ml100MhzPhyPmaCmnVcoCfg</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
@@ -20336,29 +20376,29 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr"/>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>1321804</v>
+        <v>1347583</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>200</v>
+        <v>1468</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Array 'apsd' of size 21 may use index value(s) 21..259</t>
+          <t>'dpPll' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>proc_get_keyv</t>
+          <t>ml100MhzPhyPmaCmnVcoCfg</t>
         </is>
       </c>
       <c r="H248" s="3" t="inlineStr">
@@ -20409,29 +20449,29 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr"/>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
         </is>
       </c>
       <c r="D249" s="3" t="n">
-        <v>1321805</v>
+        <v>1347584</v>
       </c>
       <c r="E249" s="3" t="n">
-        <v>249</v>
+        <v>1471</v>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Array 'kpi' of size 16 may use index value(s) 16..254</t>
+          <t>'dpPll' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>proc_get_keyv</t>
+          <t>ml100MhzPhyPmaCmnVcoCfg</t>
         </is>
       </c>
       <c r="H249" s="3" t="inlineStr">
@@ -20482,29 +20522,29 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr"/>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>1321806</v>
+        <v>1347585</v>
       </c>
       <c r="E250" s="3" t="n">
-        <v>365</v>
+        <v>1474</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Array 'kpi' of size 16 may use index value(s) 16..254</t>
+          <t>'dpPll' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>proc_set_onenode</t>
+          <t>ml100MhzPhyPmaCmnVcoCfg</t>
         </is>
       </c>
       <c r="H250" s="3" t="inlineStr">
@@ -20555,29 +20595,29 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr"/>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>1321807</v>
+        <v>1347871</v>
       </c>
       <c r="E251" s="3" t="n">
-        <v>548</v>
+        <v>470</v>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Array 'apsd' of size 21 may use index value(s) 21..257</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>get_value_type</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr">
@@ -20628,29 +20668,29 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
+          <t>UNINIT.STACK.MIGHT</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr"/>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>1321808</v>
+        <v>1347872</v>
       </c>
       <c r="E252" s="3" t="n">
-        <v>1051</v>
+        <v>489</v>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Array 'linebuf' of size 513 may use index value(s) -1</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>yang_db_runtime_readfile</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H252" s="3" t="inlineStr">
@@ -20701,33 +20741,29 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="inlineStr">
-        <is>
-          <t>Waiver id: PSDKRA_SA_DR_003</t>
-        </is>
-      </c>
+          <t>UNINIT.STACK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr"/>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>1343713</v>
+        <v>1347873</v>
       </c>
       <c r="E253" s="3" t="n">
-        <v>2972</v>
+        <v>514</v>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'hClient' returned from call to function 'CpswProxyServer_getClient' at line 2958 may be NULL and will be dereferenced at line 2972.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_clientRequestHandler</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H253" s="3" t="inlineStr">
@@ -20750,7 +20786,7 @@
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
@@ -20769,7 +20805,7 @@
       <c r="R253" s="3" t="inlineStr"/>
       <c r="S253" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T253" s="3" t="inlineStr"/>
@@ -20778,33 +20814,29 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="inlineStr">
-        <is>
-          <t>Waiver id: PSDKRA_SA_DR_003</t>
-        </is>
-      </c>
+          <t>UNINIT.STACK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr"/>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>1343714</v>
+        <v>1347874</v>
       </c>
       <c r="E254" s="3" t="n">
-        <v>3614</v>
+        <v>583</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'hClient' returned from call to function 'CpswProxyServer_getClient' at line 3611 may be NULL and will be dereferenced at line 3614.</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_clientRequestHandler</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H254" s="3" t="inlineStr">
@@ -20827,7 +20859,7 @@
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
@@ -20846,7 +20878,7 @@
       <c r="R254" s="3" t="inlineStr"/>
       <c r="S254" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T254" s="3" t="inlineStr"/>
@@ -20855,33 +20887,29 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="inlineStr">
-        <is>
-          <t>waiver id: PSDKRA_SA_DR_001</t>
-        </is>
-      </c>
+          <t>UNINIT.STACK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr"/>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D255" s="3" t="n">
-        <v>1343722</v>
+        <v>1347875</v>
       </c>
       <c r="E255" s="3" t="n">
-        <v>2705</v>
+        <v>559</v>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr">
@@ -20904,7 +20932,7 @@
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
@@ -20923,7 +20951,7 @@
       <c r="R255" s="3" t="inlineStr"/>
       <c r="S255" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T255" s="3" t="inlineStr"/>
@@ -20932,33 +20960,29 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="inlineStr">
-        <is>
-          <t>waiver id: PSDKRA_SA_DR_001</t>
-        </is>
-      </c>
+          <t>UNINIT.STACK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr"/>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
-        <v>1343723</v>
+        <v>1347876</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>2706</v>
+        <v>536</v>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H256" s="3" t="inlineStr">
@@ -20981,7 +21005,7 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
@@ -21000,7 +21024,7 @@
       <c r="R256" s="3" t="inlineStr"/>
       <c r="S256" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T256" s="3" t="inlineStr"/>
@@ -21009,33 +21033,29 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>ABV.GENERAL</t>
-        </is>
-      </c>
-      <c r="B257" s="3" t="inlineStr">
-        <is>
-          <t>waiver id: PSDKRA_SA_DR_001</t>
-        </is>
-      </c>
+          <t>UNINIT.STACK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr"/>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D257" s="3" t="n">
-        <v>1343724</v>
+        <v>1347877</v>
       </c>
       <c r="E257" s="3" t="n">
-        <v>2707</v>
+        <v>605</v>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Array 'ethDrvObj' of size 2 may use index value(s) 2..5</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
@@ -21058,7 +21078,7 @@
       </c>
       <c r="L257" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
@@ -21077,7 +21097,7 @@
       <c r="R257" s="3" t="inlineStr"/>
       <c r="S257" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T257" s="3" t="inlineStr"/>
@@ -21086,33 +21106,29 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
-        </is>
-      </c>
+          <t>UNINIT.STACK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr"/>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>1343725</v>
+        <v>1347878</v>
       </c>
       <c r="E258" s="3" t="n">
-        <v>2708</v>
+        <v>629</v>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Array 'g_CpswProxyServerAutosarRpmsgBuf' of size 2 may use index value(s) 0..5</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
@@ -21135,7 +21151,7 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
@@ -21154,7 +21170,7 @@
       <c r="R258" s="3" t="inlineStr"/>
       <c r="S258" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T258" s="3" t="inlineStr"/>
@@ -21163,33 +21179,29 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
-        </is>
-      </c>
-      <c r="B259" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
-        </is>
-      </c>
+          <t>UNINIT.STACK.MIGHT</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr"/>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>1343726</v>
+        <v>1347879</v>
       </c>
       <c r="E259" s="3" t="n">
-        <v>2708</v>
+        <v>653</v>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Array 'hServer-&gt;ethDrvObj' of size 2 may use index value(s) 0..5</t>
+          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>EnetCli_classifier</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
@@ -21212,7 +21224,7 @@
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
@@ -21231,7 +21243,7 @@
       <c r="R259" s="3" t="inlineStr"/>
       <c r="S259" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T259" s="3" t="inlineStr"/>
@@ -21240,33 +21252,33 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
+          <t>ABV.MEMBER</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waiver id: PSDKRA_SA_DR_008 </t>
+          <t>Waiver id: PSDKRA_SA_DR_001 (Usecase 1)</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/client/src/cpsw_proxy.c</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>1343727</v>
+        <v>1349271</v>
       </c>
       <c r="E260" s="3" t="n">
-        <v>2708</v>
+        <v>1456</v>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Array 'gCpswProxyServer_autosarEthDriverTaskStackBuf' of size 2 may use index value(s) 0..5</t>
+          <t>Array '&amp;(req.hdr)' of size 20 may use index value(s) 20..23</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_init</t>
+          <t>CpswProxy_freeHwPushInst</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
@@ -21317,33 +21329,33 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>UNINIT.STACK.MUST</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>waiver id: PSDKRA_SA_DR_005</t>
+          <t>Waiver ID: PSDKRA_SA_DR_012</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/perf_stats/src/app_perf_stats_rtos.c</t>
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>1343728</v>
+        <v>1350498</v>
       </c>
       <c r="E261" s="3" t="n">
-        <v>2972</v>
+        <v>272</v>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'hClient' will be dereferenced at line 2972 after having been checked for NULL.</t>
+          <t>'rtos_load_stat.totalTime' is used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_clientRequestHandler</t>
+          <t>appPerfStatsTaskLoadUpdate</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
@@ -21394,33 +21406,33 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>NPD.CHECK.MUST</t>
+          <t>UNINIT.STACK.MUST</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>waiver id: PSDKRA_SA_DR_005</t>
+          <t>Waiver ID: PSDKRA_SA_DR_012</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/cpsw_proxy_server.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/perf_stats/src/app_perf_stats_rtos.c</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>1343729</v>
+        <v>1350499</v>
       </c>
       <c r="E262" s="3" t="n">
-        <v>3614</v>
+        <v>273</v>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Pointer 'hClient' will be dereferenced at line 3614 after having been checked for NULL.</t>
+          <t>'rtos_load_stat.threadTime' is used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>CpswProxyServer_clientRequestHandler</t>
+          <t>appPerfStatsTaskLoadUpdate</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
@@ -21471,29 +21483,34 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="inlineStr"/>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>Waiver ID: PSDKRA_SA_DR_001
+Out of bounds will never happen</t>
+        </is>
+      </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/lwipif/src/lwip2enet.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_tsn.c</t>
         </is>
       </c>
       <c r="D263" s="3" t="n">
-        <v>1343777</v>
+        <v>1350598</v>
       </c>
       <c r="E263" s="3" t="n">
-        <v>1361</v>
+        <v>619</v>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>'errPkt' might be used uninitialized in this function.</t>
+          <t>Array 'netdevs' of size 16 may use index value(s) INT_MIN..254</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>Lwip2Enet_prepRxPktQ</t>
+          <t>EthFwTsn_gptpTask</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
@@ -21516,7 +21533,7 @@
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
@@ -21535,7 +21552,7 @@
       <c r="R263" s="3" t="inlineStr"/>
       <c r="S263" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T263" s="3" t="inlineStr"/>
@@ -21544,29 +21561,34 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr"/>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>Waiver ID: PSDKRA_SA_DR_001
+Out of bounds will never happen</t>
+        </is>
+      </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/src/per/cpsw_intervlan.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_tsn.c</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
-        <v>1344826</v>
+        <v>1350599</v>
       </c>
       <c r="E264" s="3" t="n">
-        <v>172</v>
+        <v>619</v>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Array 'inArgs-&gt;egressCfg' of size 8 may use index value(s) 0..MAX</t>
+          <t>Array 'netdevs' of size 16 may use index value(s) INT_MIN..INT_MAX-1</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>Cpsw_ioctlInterVlan</t>
+          <t>EthFwTsn_gptpTask</t>
         </is>
       </c>
       <c r="H264" s="3" t="inlineStr">
@@ -21589,7 +21611,7 @@
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
@@ -21608,7 +21630,7 @@
       <c r="R264" s="3" t="inlineStr"/>
       <c r="S264" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T264" s="3" t="inlineStr"/>
@@ -21617,33 +21639,29 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>ABV.STACK</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>waiver id: PSDKRA_SA_DR_008</t>
-        </is>
-      </c>
+          <t>NPD.GEN.CALL.MUST</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr"/>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_api.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_gptp/gptpconf/gptpgcfg.c</t>
         </is>
       </c>
       <c r="D265" s="3" t="n">
-        <v>1344879</v>
+        <v>1350992</v>
       </c>
       <c r="E265" s="3" t="n">
-        <v>1382</v>
+        <v>462</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Array 'gMcmObj' of size 8 may use index value(s) 0..8</t>
+          <t>Null pointer '...?&amp;(gycd-&gt;nonyangsem):0' that comes from line 462 will be passed to function and can be dereferenced there by passing argument 7 to function 'uc_nc_notice_register' at line 462.</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>EthFw_initMcm</t>
+          <t>gptp_nonyang_init_notice</t>
         </is>
       </c>
       <c r="H265" s="3" t="inlineStr">
@@ -21666,7 +21684,7 @@
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
@@ -21685,7 +21703,7 @@
       <c r="R265" s="3" t="inlineStr"/>
       <c r="S265" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T265" s="3" t="inlineStr"/>
@@ -21694,33 +21712,29 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>INFINITE_LOOP.LOCAL</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="inlineStr">
-        <is>
-          <t>waiver id: PSDKRA_SA_DR_006</t>
-        </is>
-      </c>
+          <t>ABV.GENERAL</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr"/>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/apps/app_remoteswitchcfg_server/main.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>1344937</v>
+        <v>1352585</v>
       </c>
       <c r="E266" s="3" t="n">
-        <v>1944</v>
+        <v>1559</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Infinite loop</t>
+          <t>Array 'aps' of size 18 may use index value(s) 18</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>EthApp_traceBufFlush</t>
+          <t>yang_db_runtime_state_keyvkstr</t>
         </is>
       </c>
       <c r="H266" s="3" t="inlineStr">
@@ -21730,11 +21744,11 @@
       </c>
       <c r="I266" s="3" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J266" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
@@ -21743,7 +21757,7 @@
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>Not a Problem</t>
+          <t>Analyze</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
@@ -21762,7 +21776,7 @@
       <c r="R266" s="3" t="inlineStr"/>
       <c r="S266" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>No Module</t>
         </is>
       </c>
       <c r="T266" s="3" t="inlineStr"/>
@@ -21771,29 +21785,29 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>LOCRET.ARG</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr"/>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/tsnconf/excelfore-config-uni_access.c</t>
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>1344946</v>
+        <v>1353264</v>
       </c>
       <c r="E267" s="3" t="n">
-        <v>2580</v>
+        <v>441</v>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Address of a local variable is returned through formal argument 'ydbia-&gt;dbpara.value'.</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>mdns_resp_del_service</t>
+          <t>ydbi_get_mac_in_pool</t>
         </is>
       </c>
       <c r="H267" s="3" t="inlineStr">
@@ -21844,29 +21858,29 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>LOCRET.ARG</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr"/>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/tsnconf/excelfore-config-uni_access.c</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>1344947</v>
+        <v>1353265</v>
       </c>
       <c r="E268" s="3" t="n">
-        <v>373</v>
+        <v>509</v>
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Address of a local variable is returned through formal argument 'ydbia-&gt;dbpara.value'.</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>mdns_build_reverse_v4_domain</t>
+          <t>ydbi_rel_mac_in_pool</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
@@ -21917,43 +21931,47 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr"/>
+          <t>INFINITE_LOOP.LOCAL</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>PSDKRA_SA_DR_006 (INFINITE_LOOP.LOCAL)</t>
+        </is>
+      </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/client/src/ts_coupler_client.c</t>
         </is>
       </c>
       <c r="D269" s="3" t="n">
-        <v>1344948</v>
+        <v>1356124</v>
       </c>
       <c r="E269" s="3" t="n">
-        <v>430</v>
+        <v>241</v>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Infinite loop</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>mdns_add_dotlocal</t>
+          <t>TsCouplerClient_task</t>
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>unowned</t>
+          <t>a0502541</t>
         </is>
       </c>
       <c r="I269" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="J269" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K269" s="3" t="inlineStr">
         <is>
@@ -21962,7 +21980,7 @@
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Not a Problem</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
@@ -21981,7 +21999,7 @@
       <c r="R269" s="3" t="inlineStr"/>
       <c r="S269" s="3" t="inlineStr">
         <is>
-          <t>No Module</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="T269" s="3" t="inlineStr"/>
@@ -21990,29 +22008,29 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>ABV.GENERAL</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr"/>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/lwipif/src/lwip2enet.c</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
-        <v>1344949</v>
+        <v>1364364</v>
       </c>
       <c r="E270" s="3" t="n">
-        <v>448</v>
+        <v>311</v>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Array 'rxInfo' of size 2 may use index value(s) 2</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>mdns_build_host_domain</t>
+          <t>Lwip2Enet_open</t>
         </is>
       </c>
       <c r="H270" s="3" t="inlineStr">
@@ -22063,29 +22081,29 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>NPD.CHECK.MUST</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr"/>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>1344950</v>
+        <v>1382017</v>
       </c>
       <c r="E271" s="3" t="n">
-        <v>468</v>
+        <v>8495</v>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>Pointer 'exponent_string' will be dereferenced at line 8495 after having been checked for NULL.</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>mdns_build_dnssd_domain</t>
+          <t>convert_number_to_mantissa_exponent</t>
         </is>
       </c>
       <c r="H271" s="3" t="inlineStr">
@@ -22136,29 +22154,29 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>FUNCRET.GEN</t>
+          <t>UNINIT.STACK.ARRAY.MIGHT</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr"/>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
+          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/drv/dctrl/dss_dctrlExtended.c</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
-        <v>1344951</v>
+        <v>1382992</v>
       </c>
       <c r="E272" s="3" t="n">
-        <v>494</v>
+        <v>749</v>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Non-void function does not return value</t>
+          <t>'sinkList' array elements might be used uninitialized in this function.</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>mdns_build_service_domain</t>
+          <t>Dss_dctrlDrvDpStartVideo</t>
         </is>
       </c>
       <c r="H272" s="3" t="inlineStr">
@@ -22206,3173 +22224,8 @@
       <c r="T272" s="3" t="inlineStr"/>
       <c r="U272" s="3" t="inlineStr"/>
     </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>FUNCRET.GEN</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr"/>
-      <c r="C273" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/mdns/mdns_domain.c</t>
-        </is>
-      </c>
-      <c r="D273" s="3" t="n">
-        <v>1344952</v>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>520</v>
-      </c>
-      <c r="F273" s="3" t="inlineStr">
-        <is>
-          <t>Non-void function does not return value</t>
-        </is>
-      </c>
-      <c r="G273" s="3" t="inlineStr">
-        <is>
-          <t>mdns_build_request_domain</t>
-        </is>
-      </c>
-      <c r="H273" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I273" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J273" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K273" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L273" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M273" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N273" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O273" s="3" t="inlineStr"/>
-      <c r="P273" s="3" t="inlineStr"/>
-      <c r="Q273" s="3" t="inlineStr"/>
-      <c r="R273" s="3" t="inlineStr"/>
-      <c r="S273" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T273" s="3" t="inlineStr"/>
-      <c r="U273" s="3" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t>FUNCRET.GEN</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr"/>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/memp.c</t>
-        </is>
-      </c>
-      <c r="D274" s="3" t="n">
-        <v>1344953</v>
-      </c>
-      <c r="E274" s="3" t="n">
-        <v>356</v>
-      </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>Non-void function does not return value</t>
-        </is>
-      </c>
-      <c r="G274" s="3" t="inlineStr">
-        <is>
-          <t>memp_malloc</t>
-        </is>
-      </c>
-      <c r="H274" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I274" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J274" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K274" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L274" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M274" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N274" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O274" s="3" t="inlineStr"/>
-      <c r="P274" s="3" t="inlineStr"/>
-      <c r="Q274" s="3" t="inlineStr"/>
-      <c r="R274" s="3" t="inlineStr"/>
-      <c r="S274" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T274" s="3" t="inlineStr"/>
-      <c r="U274" s="3" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="3" t="inlineStr">
-        <is>
-          <t>FUNCRET.GEN</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="inlineStr"/>
-      <c r="C275" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/pbuf.c</t>
-        </is>
-      </c>
-      <c r="D275" s="3" t="n">
-        <v>1344959</v>
-      </c>
-      <c r="E275" s="3" t="n">
-        <v>616</v>
-      </c>
-      <c r="F275" s="3" t="inlineStr">
-        <is>
-          <t>Non-void function does not return value</t>
-        </is>
-      </c>
-      <c r="G275" s="3" t="inlineStr">
-        <is>
-          <t>pbuf_remove_header</t>
-        </is>
-      </c>
-      <c r="H275" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I275" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J275" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K275" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L275" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M275" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N275" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O275" s="3" t="inlineStr"/>
-      <c r="P275" s="3" t="inlineStr"/>
-      <c r="Q275" s="3" t="inlineStr"/>
-      <c r="R275" s="3" t="inlineStr"/>
-      <c r="S275" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T275" s="3" t="inlineStr"/>
-      <c r="U275" s="3" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t>FUNCRET.GEN</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="inlineStr"/>
-      <c r="C276" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/core/pbuf.c</t>
-        </is>
-      </c>
-      <c r="D276" s="3" t="n">
-        <v>1344960</v>
-      </c>
-      <c r="E276" s="3" t="n">
-        <v>1043</v>
-      </c>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>Non-void function does not return value</t>
-        </is>
-      </c>
-      <c r="G276" s="3" t="inlineStr">
-        <is>
-          <t>pbuf_copy_partial_pbuf</t>
-        </is>
-      </c>
-      <c r="H276" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I276" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J276" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K276" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L276" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M276" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N276" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O276" s="3" t="inlineStr"/>
-      <c r="P276" s="3" t="inlineStr"/>
-      <c r="Q276" s="3" t="inlineStr"/>
-      <c r="R276" s="3" t="inlineStr"/>
-      <c r="S276" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T276" s="3" t="inlineStr"/>
-      <c r="U276" s="3" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="3" t="inlineStr">
-        <is>
-          <t>NPD.CHECK.MUST</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="inlineStr"/>
-      <c r="C277" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
-        </is>
-      </c>
-      <c r="D277" s="3" t="n">
-        <v>1344966</v>
-      </c>
-      <c r="E277" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="F277" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 's' will be dereferenced at line 234 after having been checked for NULL.</t>
-        </is>
-      </c>
-      <c r="G277" s="3" t="inlineStr">
-        <is>
-          <t>strlength</t>
-        </is>
-      </c>
-      <c r="H277" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I277" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J277" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K277" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L277" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M277" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N277" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O277" s="3" t="inlineStr"/>
-      <c r="P277" s="3" t="inlineStr"/>
-      <c r="Q277" s="3" t="inlineStr"/>
-      <c r="R277" s="3" t="inlineStr"/>
-      <c r="S277" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T277" s="3" t="inlineStr"/>
-      <c r="U277" s="3" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="3" t="inlineStr">
-        <is>
-          <t>NPD.CHECK.MUST</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="inlineStr"/>
-      <c r="C278" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
-        </is>
-      </c>
-      <c r="D278" s="3" t="n">
-        <v>1344967</v>
-      </c>
-      <c r="E278" s="3" t="n">
-        <v>246</v>
-      </c>
-      <c r="F278" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'src' will be dereferenced at line 246 after having been checked for NULL.</t>
-        </is>
-      </c>
-      <c r="G278" s="3" t="inlineStr">
-        <is>
-          <t>strequal</t>
-        </is>
-      </c>
-      <c r="H278" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I278" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J278" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K278" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L278" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M278" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N278" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O278" s="3" t="inlineStr"/>
-      <c r="P278" s="3" t="inlineStr"/>
-      <c r="Q278" s="3" t="inlineStr"/>
-      <c r="R278" s="3" t="inlineStr"/>
-      <c r="S278" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T278" s="3" t="inlineStr"/>
-      <c r="U278" s="3" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="3" t="inlineStr">
-        <is>
-          <t>NPD.CHECK.MUST</t>
-        </is>
-      </c>
-      <c r="B279" s="3" t="inlineStr"/>
-      <c r="C279" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
-        </is>
-      </c>
-      <c r="D279" s="3" t="n">
-        <v>1344968</v>
-      </c>
-      <c r="E279" s="3" t="n">
-        <v>246</v>
-      </c>
-      <c r="F279" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'dst' will be dereferenced at line 246 after having been checked for NULL.</t>
-        </is>
-      </c>
-      <c r="G279" s="3" t="inlineStr">
-        <is>
-          <t>strequal</t>
-        </is>
-      </c>
-      <c r="H279" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I279" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J279" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K279" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L279" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M279" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N279" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O279" s="3" t="inlineStr"/>
-      <c r="P279" s="3" t="inlineStr"/>
-      <c r="Q279" s="3" t="inlineStr"/>
-      <c r="R279" s="3" t="inlineStr"/>
-      <c r="S279" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T279" s="3" t="inlineStr"/>
-      <c r="U279" s="3" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="3" t="inlineStr">
-        <is>
-          <t>NPD.CHECK.MUST</t>
-        </is>
-      </c>
-      <c r="B280" s="3" t="inlineStr"/>
-      <c r="C280" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="n">
-        <v>1344969</v>
-      </c>
-      <c r="E280" s="3" t="n">
-        <v>269</v>
-      </c>
-      <c r="F280" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'end' will be dereferenced at line 269 after having been checked for NULL.</t>
-        </is>
-      </c>
-      <c r="G280" s="3" t="inlineStr">
-        <is>
-          <t>strlength_wide</t>
-        </is>
-      </c>
-      <c r="H280" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I280" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J280" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K280" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L280" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M280" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N280" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O280" s="3" t="inlineStr"/>
-      <c r="P280" s="3" t="inlineStr"/>
-      <c r="Q280" s="3" t="inlineStr"/>
-      <c r="R280" s="3" t="inlineStr"/>
-      <c r="S280" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T280" s="3" t="inlineStr"/>
-      <c r="U280" s="3" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="3" t="inlineStr">
-        <is>
-          <t>NPD.CHECK.MUST</t>
-        </is>
-      </c>
-      <c r="B281" s="3" t="inlineStr"/>
-      <c r="C281" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
-        </is>
-      </c>
-      <c r="D281" s="3" t="n">
-        <v>1344970</v>
-      </c>
-      <c r="E281" s="3" t="n">
-        <v>7953</v>
-      </c>
-      <c r="F281" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'cur' will be dereferenced at line 7953 after having been checked for NULL.</t>
-        </is>
-      </c>
-      <c r="G281" s="3" t="inlineStr">
-        <is>
-          <t>release</t>
-        </is>
-      </c>
-      <c r="H281" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I281" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J281" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K281" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L281" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M281" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N281" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O281" s="3" t="inlineStr"/>
-      <c r="P281" s="3" t="inlineStr"/>
-      <c r="Q281" s="3" t="inlineStr"/>
-      <c r="R281" s="3" t="inlineStr"/>
-      <c r="S281" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T281" s="3" t="inlineStr"/>
-      <c r="U281" s="3" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="3" t="inlineStr">
-        <is>
-          <t>NPD.CHECK.MUST</t>
-        </is>
-      </c>
-      <c r="B282" s="3" t="inlineStr"/>
-      <c r="C282" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
-        </is>
-      </c>
-      <c r="D282" s="3" t="n">
-        <v>1344971</v>
-      </c>
-      <c r="E282" s="3" t="n">
-        <v>11398</v>
-      </c>
-      <c r="F282" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'this-&gt;_alloc-&gt;_error' will be dereferenced at line 11398 after having been checked for NULL.</t>
-        </is>
-      </c>
-      <c r="G282" s="3" t="inlineStr">
-        <is>
-          <t>error_oom</t>
-        </is>
-      </c>
-      <c r="H282" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I282" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J282" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K282" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L282" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M282" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N282" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O282" s="3" t="inlineStr"/>
-      <c r="P282" s="3" t="inlineStr"/>
-      <c r="Q282" s="3" t="inlineStr"/>
-      <c r="R282" s="3" t="inlineStr"/>
-      <c r="S282" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T282" s="3" t="inlineStr"/>
-      <c r="U282" s="3" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="3" t="inlineStr">
-        <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="inlineStr"/>
-      <c r="C283" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
-        </is>
-      </c>
-      <c r="D283" s="3" t="n">
-        <v>1344972</v>
-      </c>
-      <c r="E283" s="3" t="n">
-        <v>12780</v>
-      </c>
-      <c r="F283" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12780 may be NULL and will be dereferenced at line 12780.</t>
-        </is>
-      </c>
-      <c r="G283" s="3" t="inlineStr">
-        <is>
-          <t>_find</t>
-        </is>
-      </c>
-      <c r="H283" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I283" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J283" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K283" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L283" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M283" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N283" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O283" s="3" t="inlineStr"/>
-      <c r="P283" s="3" t="inlineStr"/>
-      <c r="Q283" s="3" t="inlineStr"/>
-      <c r="R283" s="3" t="inlineStr"/>
-      <c r="S283" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T283" s="3" t="inlineStr"/>
-      <c r="U283" s="3" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="3" t="inlineStr">
-        <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B284" s="3" t="inlineStr"/>
-      <c r="C284" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/utils/pugixml/src/pugixml.cpp</t>
-        </is>
-      </c>
-      <c r="D284" s="3" t="n">
-        <v>1344973</v>
-      </c>
-      <c r="E284" s="3" t="n">
-        <v>12832</v>
-      </c>
-      <c r="F284" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'var-&gt;name()' returned from call to function 'name' at line 12832 may be NULL and will be dereferenced at line 12832.</t>
-        </is>
-      </c>
-      <c r="G284" s="3" t="inlineStr">
-        <is>
-          <t>add</t>
-        </is>
-      </c>
-      <c r="H284" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I284" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J284" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K284" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L284" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M284" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N284" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O284" s="3" t="inlineStr"/>
-      <c r="P284" s="3" t="inlineStr"/>
-      <c r="Q284" s="3" t="inlineStr"/>
-      <c r="R284" s="3" t="inlineStr"/>
-      <c r="S284" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T284" s="3" t="inlineStr"/>
-      <c r="U284" s="3" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="3" t="inlineStr">
-        <is>
-          <t>ABV.STACK</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="inlineStr"/>
-      <c r="C285" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/snmp/snmp_core.c</t>
-        </is>
-      </c>
-      <c r="D285" s="3" t="n">
-        <v>1344976</v>
-      </c>
-      <c r="E285" s="3" t="n">
-        <v>847</v>
-      </c>
-      <c r="F285" s="3" t="inlineStr">
-        <is>
-          <t>Array 'node_oid-&gt;id' of size 50 may use index value(s) 0..50</t>
-        </is>
-      </c>
-      <c r="G285" s="3" t="inlineStr">
-        <is>
-          <t>snmp_get_next_node_instance_from_oid</t>
-        </is>
-      </c>
-      <c r="H285" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I285" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J285" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K285" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L285" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M285" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N285" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O285" s="3" t="inlineStr"/>
-      <c r="P285" s="3" t="inlineStr"/>
-      <c r="Q285" s="3" t="inlineStr"/>
-      <c r="R285" s="3" t="inlineStr"/>
-      <c r="S285" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T285" s="3" t="inlineStr"/>
-      <c r="U285" s="3" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="3" t="inlineStr">
-        <is>
-          <t>ABV.STACK</t>
-        </is>
-      </c>
-      <c r="B286" s="3" t="inlineStr"/>
-      <c r="C286" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/lwip/lwip-stack/src/apps/snmp/snmp_core.c</t>
-        </is>
-      </c>
-      <c r="D286" s="3" t="n">
-        <v>1344977</v>
-      </c>
-      <c r="E286" s="3" t="n">
-        <v>903</v>
-      </c>
-      <c r="F286" s="3" t="inlineStr">
-        <is>
-          <t>Array 'node_instance-&gt;instance_oid.id' of size 50 may use index value(s) 0..50</t>
-        </is>
-      </c>
-      <c r="G286" s="3" t="inlineStr">
-        <is>
-          <t>snmp_get_next_node_instance_from_oid</t>
-        </is>
-      </c>
-      <c r="H286" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I286" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J286" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K286" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L286" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M286" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N286" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O286" s="3" t="inlineStr"/>
-      <c r="P286" s="3" t="inlineStr"/>
-      <c r="Q286" s="3" t="inlineStr"/>
-      <c r="R286" s="3" t="inlineStr"/>
-      <c r="S286" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T286" s="3" t="inlineStr"/>
-      <c r="U286" s="3" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="3" t="inlineStr">
-        <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B287" s="3" t="inlineStr"/>
-      <c r="C287" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D287" s="3" t="n">
-        <v>1346141</v>
-      </c>
-      <c r="E287" s="3" t="n">
-        <v>540</v>
-      </c>
-      <c r="F287" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 537 may be NULL and will be dereferenced at line 540.</t>
-        </is>
-      </c>
-      <c r="G287" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H287" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I287" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J287" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K287" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L287" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M287" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N287" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O287" s="3" t="inlineStr"/>
-      <c r="P287" s="3" t="inlineStr"/>
-      <c r="Q287" s="3" t="inlineStr"/>
-      <c r="R287" s="3" t="inlineStr"/>
-      <c r="S287" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T287" s="3" t="inlineStr"/>
-      <c r="U287" s="3" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="3" t="inlineStr">
-        <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B288" s="3" t="inlineStr"/>
-      <c r="C288" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D288" s="3" t="n">
-        <v>1346142</v>
-      </c>
-      <c r="E288" s="3" t="n">
-        <v>518</v>
-      </c>
-      <c r="F288" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 515 may be NULL and will be dereferenced at line 518.</t>
-        </is>
-      </c>
-      <c r="G288" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H288" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I288" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J288" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K288" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L288" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M288" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N288" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O288" s="3" t="inlineStr"/>
-      <c r="P288" s="3" t="inlineStr"/>
-      <c r="Q288" s="3" t="inlineStr"/>
-      <c r="R288" s="3" t="inlineStr"/>
-      <c r="S288" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T288" s="3" t="inlineStr"/>
-      <c r="U288" s="3" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="3" t="inlineStr">
-        <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B289" s="3" t="inlineStr"/>
-      <c r="C289" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D289" s="3" t="n">
-        <v>1346143</v>
-      </c>
-      <c r="E289" s="3" t="n">
-        <v>565</v>
-      </c>
-      <c r="F289" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 562 may be NULL and will be dereferenced at line 565.</t>
-        </is>
-      </c>
-      <c r="G289" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H289" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I289" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J289" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K289" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L289" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M289" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N289" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O289" s="3" t="inlineStr"/>
-      <c r="P289" s="3" t="inlineStr"/>
-      <c r="Q289" s="3" t="inlineStr"/>
-      <c r="R289" s="3" t="inlineStr"/>
-      <c r="S289" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T289" s="3" t="inlineStr"/>
-      <c r="U289" s="3" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="3" t="inlineStr">
-        <is>
-          <t>NPD.FUNC.MUST</t>
-        </is>
-      </c>
-      <c r="B290" s="3" t="inlineStr"/>
-      <c r="C290" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D290" s="3" t="n">
-        <v>1346144</v>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>589</v>
-      </c>
-      <c r="F290" s="3" t="inlineStr">
-        <is>
-          <t>Pointer 'parameter' returned from call to function 'EnetCli_getParameter' at line 586 may be NULL and will be dereferenced at line 589.</t>
-        </is>
-      </c>
-      <c r="G290" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H290" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J290" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K290" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L290" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M290" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N290" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O290" s="3" t="inlineStr"/>
-      <c r="P290" s="3" t="inlineStr"/>
-      <c r="Q290" s="3" t="inlineStr"/>
-      <c r="R290" s="3" t="inlineStr"/>
-      <c r="S290" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T290" s="3" t="inlineStr"/>
-      <c r="U290" s="3" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B291" s="3" t="inlineStr"/>
-      <c r="C291" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D291" s="3" t="n">
-        <v>1346153</v>
-      </c>
-      <c r="E291" s="3" t="n">
-        <v>247</v>
-      </c>
-      <c r="F291" s="3" t="inlineStr">
-        <is>
-          <t>'remapType' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G291" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_priorityMap</t>
-        </is>
-      </c>
-      <c r="H291" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I291" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J291" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K291" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L291" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M291" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N291" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O291" s="3" t="inlineStr"/>
-      <c r="P291" s="3" t="inlineStr"/>
-      <c r="Q291" s="3" t="inlineStr"/>
-      <c r="R291" s="3" t="inlineStr"/>
-      <c r="S291" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T291" s="3" t="inlineStr"/>
-      <c r="U291" s="3" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B292" s="3" t="inlineStr"/>
-      <c r="C292" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
-        </is>
-      </c>
-      <c r="D292" s="3" t="n">
-        <v>1347582</v>
-      </c>
-      <c r="E292" s="3" t="n">
-        <v>1465</v>
-      </c>
-      <c r="F292" s="3" t="inlineStr">
-        <is>
-          <t>'dpPll' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G292" s="3" t="inlineStr">
-        <is>
-          <t>ml100MhzPhyPmaCmnVcoCfg</t>
-        </is>
-      </c>
-      <c r="H292" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I292" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J292" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K292" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L292" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M292" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N292" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O292" s="3" t="inlineStr"/>
-      <c r="P292" s="3" t="inlineStr"/>
-      <c r="Q292" s="3" t="inlineStr"/>
-      <c r="R292" s="3" t="inlineStr"/>
-      <c r="S292" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T292" s="3" t="inlineStr"/>
-      <c r="U292" s="3" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B293" s="3" t="inlineStr"/>
-      <c r="C293" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
-        </is>
-      </c>
-      <c r="D293" s="3" t="n">
-        <v>1347583</v>
-      </c>
-      <c r="E293" s="3" t="n">
-        <v>1468</v>
-      </c>
-      <c r="F293" s="3" t="inlineStr">
-        <is>
-          <t>'dpPll' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G293" s="3" t="inlineStr">
-        <is>
-          <t>ml100MhzPhyPmaCmnVcoCfg</t>
-        </is>
-      </c>
-      <c r="H293" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I293" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J293" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K293" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L293" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M293" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N293" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O293" s="3" t="inlineStr"/>
-      <c r="P293" s="3" t="inlineStr"/>
-      <c r="Q293" s="3" t="inlineStr"/>
-      <c r="R293" s="3" t="inlineStr"/>
-      <c r="S293" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T293" s="3" t="inlineStr"/>
-      <c r="U293" s="3" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B294" s="3" t="inlineStr"/>
-      <c r="C294" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
-        </is>
-      </c>
-      <c r="D294" s="3" t="n">
-        <v>1347584</v>
-      </c>
-      <c r="E294" s="3" t="n">
-        <v>1471</v>
-      </c>
-      <c r="F294" s="3" t="inlineStr">
-        <is>
-          <t>'dpPll' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G294" s="3" t="inlineStr">
-        <is>
-          <t>ml100MhzPhyPmaCmnVcoCfg</t>
-        </is>
-      </c>
-      <c r="H294" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I294" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J294" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K294" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L294" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M294" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N294" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O294" s="3" t="inlineStr"/>
-      <c r="P294" s="3" t="inlineStr"/>
-      <c r="Q294" s="3" t="inlineStr"/>
-      <c r="R294" s="3" t="inlineStr"/>
-      <c r="S294" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T294" s="3" t="inlineStr"/>
-      <c r="U294" s="3" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B295" s="3" t="inlineStr"/>
-      <c r="C295" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/dss/src/csl/dp_sd0801/src/specific/dp_sd0801_spec.c</t>
-        </is>
-      </c>
-      <c r="D295" s="3" t="n">
-        <v>1347585</v>
-      </c>
-      <c r="E295" s="3" t="n">
-        <v>1474</v>
-      </c>
-      <c r="F295" s="3" t="inlineStr">
-        <is>
-          <t>'dpPll' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G295" s="3" t="inlineStr">
-        <is>
-          <t>ml100MhzPhyPmaCmnVcoCfg</t>
-        </is>
-      </c>
-      <c r="H295" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I295" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J295" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K295" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L295" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M295" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N295" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O295" s="3" t="inlineStr"/>
-      <c r="P295" s="3" t="inlineStr"/>
-      <c r="Q295" s="3" t="inlineStr"/>
-      <c r="R295" s="3" t="inlineStr"/>
-      <c r="S295" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T295" s="3" t="inlineStr"/>
-      <c r="U295" s="3" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B296" s="3" t="inlineStr"/>
-      <c r="C296" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D296" s="3" t="n">
-        <v>1347871</v>
-      </c>
-      <c r="E296" s="3" t="n">
-        <v>470</v>
-      </c>
-      <c r="F296" s="3" t="inlineStr">
-        <is>
-          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G296" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H296" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I296" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J296" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K296" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L296" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M296" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N296" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O296" s="3" t="inlineStr"/>
-      <c r="P296" s="3" t="inlineStr"/>
-      <c r="Q296" s="3" t="inlineStr"/>
-      <c r="R296" s="3" t="inlineStr"/>
-      <c r="S296" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T296" s="3" t="inlineStr"/>
-      <c r="U296" s="3" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B297" s="3" t="inlineStr"/>
-      <c r="C297" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D297" s="3" t="n">
-        <v>1347872</v>
-      </c>
-      <c r="E297" s="3" t="n">
-        <v>489</v>
-      </c>
-      <c r="F297" s="3" t="inlineStr">
-        <is>
-          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G297" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H297" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I297" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J297" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K297" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L297" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M297" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N297" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O297" s="3" t="inlineStr"/>
-      <c r="P297" s="3" t="inlineStr"/>
-      <c r="Q297" s="3" t="inlineStr"/>
-      <c r="R297" s="3" t="inlineStr"/>
-      <c r="S297" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T297" s="3" t="inlineStr"/>
-      <c r="U297" s="3" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B298" s="3" t="inlineStr"/>
-      <c r="C298" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D298" s="3" t="n">
-        <v>1347873</v>
-      </c>
-      <c r="E298" s="3" t="n">
-        <v>514</v>
-      </c>
-      <c r="F298" s="3" t="inlineStr">
-        <is>
-          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G298" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H298" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I298" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J298" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K298" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L298" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M298" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N298" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O298" s="3" t="inlineStr"/>
-      <c r="P298" s="3" t="inlineStr"/>
-      <c r="Q298" s="3" t="inlineStr"/>
-      <c r="R298" s="3" t="inlineStr"/>
-      <c r="S298" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T298" s="3" t="inlineStr"/>
-      <c r="U298" s="3" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B299" s="3" t="inlineStr"/>
-      <c r="C299" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D299" s="3" t="n">
-        <v>1347874</v>
-      </c>
-      <c r="E299" s="3" t="n">
-        <v>583</v>
-      </c>
-      <c r="F299" s="3" t="inlineStr">
-        <is>
-          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G299" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H299" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I299" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J299" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K299" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L299" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M299" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N299" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O299" s="3" t="inlineStr"/>
-      <c r="P299" s="3" t="inlineStr"/>
-      <c r="Q299" s="3" t="inlineStr"/>
-      <c r="R299" s="3" t="inlineStr"/>
-      <c r="S299" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T299" s="3" t="inlineStr"/>
-      <c r="U299" s="3" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B300" s="3" t="inlineStr"/>
-      <c r="C300" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D300" s="3" t="n">
-        <v>1347875</v>
-      </c>
-      <c r="E300" s="3" t="n">
-        <v>559</v>
-      </c>
-      <c r="F300" s="3" t="inlineStr">
-        <is>
-          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G300" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H300" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I300" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J300" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K300" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L300" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M300" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N300" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O300" s="3" t="inlineStr"/>
-      <c r="P300" s="3" t="inlineStr"/>
-      <c r="Q300" s="3" t="inlineStr"/>
-      <c r="R300" s="3" t="inlineStr"/>
-      <c r="S300" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T300" s="3" t="inlineStr"/>
-      <c r="U300" s="3" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B301" s="3" t="inlineStr"/>
-      <c r="C301" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D301" s="3" t="n">
-        <v>1347876</v>
-      </c>
-      <c r="E301" s="3" t="n">
-        <v>536</v>
-      </c>
-      <c r="F301" s="3" t="inlineStr">
-        <is>
-          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G301" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H301" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I301" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J301" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K301" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L301" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M301" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N301" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O301" s="3" t="inlineStr"/>
-      <c r="P301" s="3" t="inlineStr"/>
-      <c r="Q301" s="3" t="inlineStr"/>
-      <c r="R301" s="3" t="inlineStr"/>
-      <c r="S301" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T301" s="3" t="inlineStr"/>
-      <c r="U301" s="3" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B302" s="3" t="inlineStr"/>
-      <c r="C302" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D302" s="3" t="n">
-        <v>1347877</v>
-      </c>
-      <c r="E302" s="3" t="n">
-        <v>605</v>
-      </c>
-      <c r="F302" s="3" t="inlineStr">
-        <is>
-          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G302" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H302" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I302" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J302" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K302" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L302" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M302" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N302" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O302" s="3" t="inlineStr"/>
-      <c r="P302" s="3" t="inlineStr"/>
-      <c r="Q302" s="3" t="inlineStr"/>
-      <c r="R302" s="3" t="inlineStr"/>
-      <c r="S302" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T302" s="3" t="inlineStr"/>
-      <c r="U302" s="3" t="inlineStr"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B303" s="3" t="inlineStr"/>
-      <c r="C303" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D303" s="3" t="n">
-        <v>1347878</v>
-      </c>
-      <c r="E303" s="3" t="n">
-        <v>629</v>
-      </c>
-      <c r="F303" s="3" t="inlineStr">
-        <is>
-          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G303" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H303" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I303" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J303" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K303" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L303" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M303" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N303" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O303" s="3" t="inlineStr"/>
-      <c r="P303" s="3" t="inlineStr"/>
-      <c r="Q303" s="3" t="inlineStr"/>
-      <c r="R303" s="3" t="inlineStr"/>
-      <c r="S303" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T303" s="3" t="inlineStr"/>
-      <c r="U303" s="3" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MIGHT</t>
-        </is>
-      </c>
-      <c r="B304" s="3" t="inlineStr"/>
-      <c r="C304" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/enet_cli/enet_cli_core/src/enet_cli_config.c</t>
-        </is>
-      </c>
-      <c r="D304" s="3" t="n">
-        <v>1347879</v>
-      </c>
-      <c r="E304" s="3" t="n">
-        <v>653</v>
-      </c>
-      <c r="F304" s="3" t="inlineStr">
-        <is>
-          <t>'setPolicerInArgs.policerMatch.policerMatchEnMask' might be used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G304" s="3" t="inlineStr">
-        <is>
-          <t>EnetCli_classifier</t>
-        </is>
-      </c>
-      <c r="H304" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I304" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J304" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K304" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L304" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M304" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N304" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O304" s="3" t="inlineStr"/>
-      <c r="P304" s="3" t="inlineStr"/>
-      <c r="Q304" s="3" t="inlineStr"/>
-      <c r="R304" s="3" t="inlineStr"/>
-      <c r="S304" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T304" s="3" t="inlineStr"/>
-      <c r="U304" s="3" t="inlineStr"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="3" t="inlineStr">
-        <is>
-          <t>ABV.MEMBER</t>
-        </is>
-      </c>
-      <c r="B305" s="3" t="inlineStr">
-        <is>
-          <t>Waiver id: PSDKRA_SA_DR_001 (Usecase 1)</t>
-        </is>
-      </c>
-      <c r="C305" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/client/src/cpsw_proxy.c</t>
-        </is>
-      </c>
-      <c r="D305" s="3" t="n">
-        <v>1349271</v>
-      </c>
-      <c r="E305" s="3" t="n">
-        <v>1456</v>
-      </c>
-      <c r="F305" s="3" t="inlineStr">
-        <is>
-          <t>Array '&amp;(req.hdr)' of size 20 may use index value(s) 20..23</t>
-        </is>
-      </c>
-      <c r="G305" s="3" t="inlineStr">
-        <is>
-          <t>CpswProxy_freeHwPushInst</t>
-        </is>
-      </c>
-      <c r="H305" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I305" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J305" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K305" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L305" s="3" t="inlineStr">
-        <is>
-          <t>Not a Problem</t>
-        </is>
-      </c>
-      <c r="M305" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N305" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O305" s="3" t="inlineStr"/>
-      <c r="P305" s="3" t="inlineStr"/>
-      <c r="Q305" s="3" t="inlineStr"/>
-      <c r="R305" s="3" t="inlineStr"/>
-      <c r="S305" s="3" t="inlineStr">
-        <is>
-          <t>EthFw</t>
-        </is>
-      </c>
-      <c r="T305" s="3" t="inlineStr"/>
-      <c r="U305" s="3" t="inlineStr"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MUST</t>
-        </is>
-      </c>
-      <c r="B306" s="3" t="inlineStr">
-        <is>
-          <t>Waiver ID: PSDKRA_SA_DR_012</t>
-        </is>
-      </c>
-      <c r="C306" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/perf_stats/src/app_perf_stats_rtos.c</t>
-        </is>
-      </c>
-      <c r="D306" s="3" t="n">
-        <v>1350498</v>
-      </c>
-      <c r="E306" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="F306" s="3" t="inlineStr">
-        <is>
-          <t>'rtos_load_stat.totalTime' is used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G306" s="3" t="inlineStr">
-        <is>
-          <t>appPerfStatsTaskLoadUpdate</t>
-        </is>
-      </c>
-      <c r="H306" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I306" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J306" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K306" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L306" s="3" t="inlineStr">
-        <is>
-          <t>Not a Problem</t>
-        </is>
-      </c>
-      <c r="M306" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N306" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O306" s="3" t="inlineStr"/>
-      <c r="P306" s="3" t="inlineStr"/>
-      <c r="Q306" s="3" t="inlineStr"/>
-      <c r="R306" s="3" t="inlineStr"/>
-      <c r="S306" s="3" t="inlineStr">
-        <is>
-          <t>EthFw</t>
-        </is>
-      </c>
-      <c r="T306" s="3" t="inlineStr"/>
-      <c r="U306" s="3" t="inlineStr"/>
-    </row>
-    <row r="307">
-      <c r="A307" s="3" t="inlineStr">
-        <is>
-          <t>UNINIT.STACK.MUST</t>
-        </is>
-      </c>
-      <c r="B307" s="3" t="inlineStr">
-        <is>
-          <t>Waiver ID: PSDKRA_SA_DR_012</t>
-        </is>
-      </c>
-      <c r="C307" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/utils/perf_stats/src/app_perf_stats_rtos.c</t>
-        </is>
-      </c>
-      <c r="D307" s="3" t="n">
-        <v>1350499</v>
-      </c>
-      <c r="E307" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="F307" s="3" t="inlineStr">
-        <is>
-          <t>'rtos_load_stat.threadTime' is used uninitialized in this function.</t>
-        </is>
-      </c>
-      <c r="G307" s="3" t="inlineStr">
-        <is>
-          <t>appPerfStatsTaskLoadUpdate</t>
-        </is>
-      </c>
-      <c r="H307" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I307" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J307" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K307" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L307" s="3" t="inlineStr">
-        <is>
-          <t>Not a Problem</t>
-        </is>
-      </c>
-      <c r="M307" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N307" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O307" s="3" t="inlineStr"/>
-      <c r="P307" s="3" t="inlineStr"/>
-      <c r="Q307" s="3" t="inlineStr"/>
-      <c r="R307" s="3" t="inlineStr"/>
-      <c r="S307" s="3" t="inlineStr">
-        <is>
-          <t>EthFw</t>
-        </is>
-      </c>
-      <c r="T307" s="3" t="inlineStr"/>
-      <c r="U307" s="3" t="inlineStr"/>
-    </row>
-    <row r="308">
-      <c r="A308" s="3" t="inlineStr">
-        <is>
-          <t>ABV.GENERAL</t>
-        </is>
-      </c>
-      <c r="B308" s="3" t="inlineStr">
-        <is>
-          <t>Waiver ID: PSDKRA_SA_DR_001
-Out of bounds will never happen</t>
-        </is>
-      </c>
-      <c r="C308" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_tsn.c</t>
-        </is>
-      </c>
-      <c r="D308" s="3" t="n">
-        <v>1350598</v>
-      </c>
-      <c r="E308" s="3" t="n">
-        <v>619</v>
-      </c>
-      <c r="F308" s="3" t="inlineStr">
-        <is>
-          <t>Array 'netdevs' of size 16 may use index value(s) INT_MIN..254</t>
-        </is>
-      </c>
-      <c r="G308" s="3" t="inlineStr">
-        <is>
-          <t>EthFwTsn_gptpTask</t>
-        </is>
-      </c>
-      <c r="H308" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I308" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J308" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K308" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L308" s="3" t="inlineStr">
-        <is>
-          <t>Not a Problem</t>
-        </is>
-      </c>
-      <c r="M308" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N308" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O308" s="3" t="inlineStr"/>
-      <c r="P308" s="3" t="inlineStr"/>
-      <c r="Q308" s="3" t="inlineStr"/>
-      <c r="R308" s="3" t="inlineStr"/>
-      <c r="S308" s="3" t="inlineStr">
-        <is>
-          <t>EthFw</t>
-        </is>
-      </c>
-      <c r="T308" s="3" t="inlineStr"/>
-      <c r="U308" s="3" t="inlineStr"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="3" t="inlineStr">
-        <is>
-          <t>ABV.GENERAL</t>
-        </is>
-      </c>
-      <c r="B309" s="3" t="inlineStr">
-        <is>
-          <t>Waiver ID: PSDKRA_SA_DR_001
-Out of bounds will never happen</t>
-        </is>
-      </c>
-      <c r="C309" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/server/src/ethfw_tsn.c</t>
-        </is>
-      </c>
-      <c r="D309" s="3" t="n">
-        <v>1350599</v>
-      </c>
-      <c r="E309" s="3" t="n">
-        <v>619</v>
-      </c>
-      <c r="F309" s="3" t="inlineStr">
-        <is>
-          <t>Array 'netdevs' of size 16 may use index value(s) INT_MIN..INT_MAX-1</t>
-        </is>
-      </c>
-      <c r="G309" s="3" t="inlineStr">
-        <is>
-          <t>EthFwTsn_gptpTask</t>
-        </is>
-      </c>
-      <c r="H309" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I309" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J309" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K309" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L309" s="3" t="inlineStr">
-        <is>
-          <t>Not a Problem</t>
-        </is>
-      </c>
-      <c r="M309" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N309" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O309" s="3" t="inlineStr"/>
-      <c r="P309" s="3" t="inlineStr"/>
-      <c r="Q309" s="3" t="inlineStr"/>
-      <c r="R309" s="3" t="inlineStr"/>
-      <c r="S309" s="3" t="inlineStr">
-        <is>
-          <t>EthFw</t>
-        </is>
-      </c>
-      <c r="T309" s="3" t="inlineStr"/>
-      <c r="U309" s="3" t="inlineStr"/>
-    </row>
-    <row r="310">
-      <c r="A310" s="3" t="inlineStr">
-        <is>
-          <t>NPD.GEN.CALL.MUST</t>
-        </is>
-      </c>
-      <c r="B310" s="3" t="inlineStr"/>
-      <c r="C310" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_gptp/gptpconf/gptpgcfg.c</t>
-        </is>
-      </c>
-      <c r="D310" s="3" t="n">
-        <v>1350992</v>
-      </c>
-      <c r="E310" s="3" t="n">
-        <v>462</v>
-      </c>
-      <c r="F310" s="3" t="inlineStr">
-        <is>
-          <t>Null pointer '...?&amp;(gycd-&gt;nonyangsem):( (void* )0)' that comes from line 462 will be passed to function and can be dereferenced there by passing argument 7 to function 'uc_nc_notice_register' at line 462.</t>
-        </is>
-      </c>
-      <c r="G310" s="3" t="inlineStr">
-        <is>
-          <t>gptp_nonyang_init_notice</t>
-        </is>
-      </c>
-      <c r="H310" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I310" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J310" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K310" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L310" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M310" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N310" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O310" s="3" t="inlineStr"/>
-      <c r="P310" s="3" t="inlineStr"/>
-      <c r="Q310" s="3" t="inlineStr"/>
-      <c r="R310" s="3" t="inlineStr"/>
-      <c r="S310" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T310" s="3" t="inlineStr"/>
-      <c r="U310" s="3" t="inlineStr"/>
-    </row>
-    <row r="311">
-      <c r="A311" s="3" t="inlineStr">
-        <is>
-          <t>ABV.GENERAL</t>
-        </is>
-      </c>
-      <c r="B311" s="3" t="inlineStr"/>
-      <c r="C311" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/yang_db_runtime.c</t>
-        </is>
-      </c>
-      <c r="D311" s="3" t="n">
-        <v>1352585</v>
-      </c>
-      <c r="E311" s="3" t="n">
-        <v>1559</v>
-      </c>
-      <c r="F311" s="3" t="inlineStr">
-        <is>
-          <t>Array 'aps' of size 18 may use index value(s) 18</t>
-        </is>
-      </c>
-      <c r="G311" s="3" t="inlineStr">
-        <is>
-          <t>yang_db_runtime_state_keyvkstr</t>
-        </is>
-      </c>
-      <c r="H311" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I311" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J311" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K311" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L311" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M311" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N311" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O311" s="3" t="inlineStr"/>
-      <c r="P311" s="3" t="inlineStr"/>
-      <c r="Q311" s="3" t="inlineStr"/>
-      <c r="R311" s="3" t="inlineStr"/>
-      <c r="S311" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T311" s="3" t="inlineStr"/>
-      <c r="U311" s="3" t="inlineStr"/>
-    </row>
-    <row r="312">
-      <c r="A312" s="3" t="inlineStr">
-        <is>
-          <t>LOCRET.ARG</t>
-        </is>
-      </c>
-      <c r="B312" s="3" t="inlineStr"/>
-      <c r="C312" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/tsnconf/excelfore-config-uni_access.c</t>
-        </is>
-      </c>
-      <c r="D312" s="3" t="n">
-        <v>1353264</v>
-      </c>
-      <c r="E312" s="3" t="n">
-        <v>441</v>
-      </c>
-      <c r="F312" s="3" t="inlineStr">
-        <is>
-          <t>Address of a local variable is returned through formal argument 'ydbia-&gt;dbpara.value'.</t>
-        </is>
-      </c>
-      <c r="G312" s="3" t="inlineStr">
-        <is>
-          <t>ydbi_get_mac_in_pool</t>
-        </is>
-      </c>
-      <c r="H312" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I312" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J312" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K312" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L312" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M312" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N312" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O312" s="3" t="inlineStr"/>
-      <c r="P312" s="3" t="inlineStr"/>
-      <c r="Q312" s="3" t="inlineStr"/>
-      <c r="R312" s="3" t="inlineStr"/>
-      <c r="S312" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T312" s="3" t="inlineStr"/>
-      <c r="U312" s="3" t="inlineStr"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="3" t="inlineStr">
-        <is>
-          <t>LOCRET.ARG</t>
-        </is>
-      </c>
-      <c r="B313" s="3" t="inlineStr"/>
-      <c r="C313" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/transport/tsn/tsn-stack/tsn_uniconf/yangs/tsnconf/excelfore-config-uni_access.c</t>
-        </is>
-      </c>
-      <c r="D313" s="3" t="n">
-        <v>1353265</v>
-      </c>
-      <c r="E313" s="3" t="n">
-        <v>509</v>
-      </c>
-      <c r="F313" s="3" t="inlineStr">
-        <is>
-          <t>Address of a local variable is returned through formal argument 'ydbia-&gt;dbpara.value'.</t>
-        </is>
-      </c>
-      <c r="G313" s="3" t="inlineStr">
-        <is>
-          <t>ydbi_rel_mac_in_pool</t>
-        </is>
-      </c>
-      <c r="H313" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I313" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J313" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K313" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L313" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M313" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N313" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O313" s="3" t="inlineStr"/>
-      <c r="P313" s="3" t="inlineStr"/>
-      <c r="Q313" s="3" t="inlineStr"/>
-      <c r="R313" s="3" t="inlineStr"/>
-      <c r="S313" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T313" s="3" t="inlineStr"/>
-      <c r="U313" s="3" t="inlineStr"/>
-    </row>
-    <row r="314">
-      <c r="A314" s="3" t="inlineStr">
-        <is>
-          <t>INFINITE_LOOP.LOCAL</t>
-        </is>
-      </c>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>PSDKRA_SA_DR_006 (INFINITE_LOOP.LOCAL)</t>
-        </is>
-      </c>
-      <c r="C314" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/ethfw/ethremotecfg/client/src/ts_coupler_client.c</t>
-        </is>
-      </c>
-      <c r="D314" s="3" t="n">
-        <v>1356124</v>
-      </c>
-      <c r="E314" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="F314" s="3" t="inlineStr">
-        <is>
-          <t>Infinite loop</t>
-        </is>
-      </c>
-      <c r="G314" s="3" t="inlineStr">
-        <is>
-          <t>TsCouplerClient_task</t>
-        </is>
-      </c>
-      <c r="H314" s="3" t="inlineStr">
-        <is>
-          <t>a0502541</t>
-        </is>
-      </c>
-      <c r="I314" s="3" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="J314" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K314" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L314" s="3" t="inlineStr">
-        <is>
-          <t>Not a Problem</t>
-        </is>
-      </c>
-      <c r="M314" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N314" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O314" s="3" t="inlineStr"/>
-      <c r="P314" s="3" t="inlineStr"/>
-      <c r="Q314" s="3" t="inlineStr"/>
-      <c r="R314" s="3" t="inlineStr"/>
-      <c r="S314" s="3" t="inlineStr">
-        <is>
-          <t>EthFw</t>
-        </is>
-      </c>
-      <c r="T314" s="3" t="inlineStr"/>
-      <c r="U314" s="3" t="inlineStr"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="3" t="inlineStr">
-        <is>
-          <t>ABV.GENERAL</t>
-        </is>
-      </c>
-      <c r="B315" s="3" t="inlineStr"/>
-      <c r="C315" s="3" t="inlineStr">
-        <is>
-          <t>/nightlybuilds/repo_manifests/scripts/jenkins/workarea/pdk_10_00_00_00/packages/ti/drv/enet/lwipif/src/lwip2enet.c</t>
-        </is>
-      </c>
-      <c r="D315" s="3" t="n">
-        <v>1364364</v>
-      </c>
-      <c r="E315" s="3" t="n">
-        <v>311</v>
-      </c>
-      <c r="F315" s="3" t="inlineStr">
-        <is>
-          <t>Array 'rxInfo' of size 2 may use index value(s) 2</t>
-        </is>
-      </c>
-      <c r="G315" s="3" t="inlineStr">
-        <is>
-          <t>Lwip2Enet_open</t>
-        </is>
-      </c>
-      <c r="H315" s="3" t="inlineStr">
-        <is>
-          <t>unowned</t>
-        </is>
-      </c>
-      <c r="I315" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J315" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K315" s="3" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="L315" s="3" t="inlineStr">
-        <is>
-          <t>Analyze</t>
-        </is>
-      </c>
-      <c r="M315" s="3" t="inlineStr">
-        <is>
-          <t>C and C++</t>
-        </is>
-      </c>
-      <c r="N315" s="3" t="inlineStr">
-        <is>
-          <t>KW Issue Link</t>
-        </is>
-      </c>
-      <c r="O315" s="3" t="inlineStr"/>
-      <c r="P315" s="3" t="inlineStr"/>
-      <c r="Q315" s="3" t="inlineStr"/>
-      <c r="R315" s="3" t="inlineStr"/>
-      <c r="S315" s="3" t="inlineStr">
-        <is>
-          <t>No Module</t>
-        </is>
-      </c>
-      <c r="T315" s="3" t="inlineStr"/>
-      <c r="U315" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:U315"/>
+  <autoFilter ref="A1:U272"/>
   <hyperlinks>
     <hyperlink ref="N2" r:id="rId1"/>
     <hyperlink ref="N3" r:id="rId2"/>
@@ -25645,49 +22498,6 @@
     <hyperlink ref="N270" r:id="rId269"/>
     <hyperlink ref="N271" r:id="rId270"/>
     <hyperlink ref="N272" r:id="rId271"/>
-    <hyperlink ref="N273" r:id="rId272"/>
-    <hyperlink ref="N274" r:id="rId273"/>
-    <hyperlink ref="N275" r:id="rId274"/>
-    <hyperlink ref="N276" r:id="rId275"/>
-    <hyperlink ref="N277" r:id="rId276"/>
-    <hyperlink ref="N278" r:id="rId277"/>
-    <hyperlink ref="N279" r:id="rId278"/>
-    <hyperlink ref="N280" r:id="rId279"/>
-    <hyperlink ref="N281" r:id="rId280"/>
-    <hyperlink ref="N282" r:id="rId281"/>
-    <hyperlink ref="N283" r:id="rId282"/>
-    <hyperlink ref="N284" r:id="rId283"/>
-    <hyperlink ref="N285" r:id="rId284"/>
-    <hyperlink ref="N286" r:id="rId285"/>
-    <hyperlink ref="N287" r:id="rId286"/>
-    <hyperlink ref="N288" r:id="rId287"/>
-    <hyperlink ref="N289" r:id="rId288"/>
-    <hyperlink ref="N290" r:id="rId289"/>
-    <hyperlink ref="N291" r:id="rId290"/>
-    <hyperlink ref="N292" r:id="rId291"/>
-    <hyperlink ref="N293" r:id="rId292"/>
-    <hyperlink ref="N294" r:id="rId293"/>
-    <hyperlink ref="N295" r:id="rId294"/>
-    <hyperlink ref="N296" r:id="rId295"/>
-    <hyperlink ref="N297" r:id="rId296"/>
-    <hyperlink ref="N298" r:id="rId297"/>
-    <hyperlink ref="N299" r:id="rId298"/>
-    <hyperlink ref="N300" r:id="rId299"/>
-    <hyperlink ref="N301" r:id="rId300"/>
-    <hyperlink ref="N302" r:id="rId301"/>
-    <hyperlink ref="N303" r:id="rId302"/>
-    <hyperlink ref="N304" r:id="rId303"/>
-    <hyperlink ref="N305" r:id="rId304"/>
-    <hyperlink ref="N306" r:id="rId305"/>
-    <hyperlink ref="N307" r:id="rId306"/>
-    <hyperlink ref="N308" r:id="rId307"/>
-    <hyperlink ref="N309" r:id="rId308"/>
-    <hyperlink ref="N310" r:id="rId309"/>
-    <hyperlink ref="N311" r:id="rId310"/>
-    <hyperlink ref="N312" r:id="rId311"/>
-    <hyperlink ref="N313" r:id="rId312"/>
-    <hyperlink ref="N314" r:id="rId313"/>
-    <hyperlink ref="N315" r:id="rId314"/>
   </hyperlinks>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
